--- a/plate3d/PLATE3D_HARBOUR.xlsx
+++ b/plate3d/PLATE3D_HARBOUR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="134">
   <si>
     <t>SYDNEY HARBOUR BRIDGE  ·  503 m arch, 1,149 m overall  ·  mm, Z up</t>
   </si>
@@ -220,12 +220,18 @@
     <t>BASE</t>
   </si>
   <si>
+    <t>sc.uc_1</t>
+  </si>
+  <si>
     <t>CROSS BRACING AND HANGERS - one half, mirrored about the crown</t>
   </si>
   <si>
     <t>md.brc</t>
   </si>
   <si>
+    <t>sc.cs_1</t>
+  </si>
+  <si>
     <t>THE CROWN - the four members that stand ON the mirror plane, so they are placed once</t>
   </si>
   <si>
@@ -235,6 +241,9 @@
     <t>md.crn</t>
   </si>
   <si>
+    <t>sc.av_1</t>
+  </si>
+  <si>
     <t>ONE DECK BAY - a cross girder and seven stringers, copied sixty-four times</t>
   </si>
   <si>
@@ -244,16 +253,25 @@
     <t>md.dkb</t>
   </si>
   <si>
+    <t>sc.cg_1</t>
+  </si>
+  <si>
     <t>ONE PYLON - 89 m of granite over a steel frame, and it carries nothing</t>
   </si>
   <si>
     <t>md.pyl</t>
   </si>
   <si>
+    <t>sc.pc_1</t>
+  </si>
+  <si>
     <t>ONE APPROACH PIER - six a side, every third bay, the last one the abutment</t>
   </si>
   <si>
     <t>md.pie</t>
+  </si>
+  <si>
+    <t>sc.ic_1</t>
   </si>
   <si>
     <t>nine drawings. VIEW on a module draws every place it is put</t>
@@ -1476,13 +1494,13 @@
         <v>-15000</v>
       </c>
       <c r="K21">
-        <v>123280.6</v>
+        <v>121607.1</v>
       </c>
       <c r="L21">
-        <v>264.1</v>
+        <v>185</v>
       </c>
       <c r="M21">
-        <v>201.3</v>
+        <v>184.9</v>
       </c>
       <c r="N21" t="s">
         <v>3</v>
@@ -1520,13 +1538,13 @@
         <v>-15000</v>
       </c>
       <c r="K22">
-        <v>101566.3</v>
+        <v>103239.8</v>
       </c>
       <c r="L22">
-        <v>380.3</v>
+        <v>221.9</v>
       </c>
       <c r="M22">
-        <v>203.1</v>
+        <v>221.4</v>
       </c>
       <c r="N22" t="s">
         <v>3</v>
@@ -1564,13 +1582,13 @@
         <v>-17800</v>
       </c>
       <c r="K23">
-        <v>123280.6</v>
+        <v>121607.1</v>
       </c>
       <c r="L23">
-        <v>2237.5</v>
+        <v>2139.6</v>
       </c>
       <c r="M23">
-        <v>2068.2</v>
+        <v>2062.5</v>
       </c>
       <c r="N23" t="s">
         <v>3</v>
@@ -1599,7 +1617,7 @@
         <v>-15000</v>
       </c>
       <c r="H24">
-        <v>123280.6</v>
+        <v>121607.1</v>
       </c>
       <c r="I24">
         <v>-35928.6</v>
@@ -1608,13 +1626,13 @@
         <v>-15000</v>
       </c>
       <c r="K24">
-        <v>123408.1</v>
+        <v>120428.5</v>
       </c>
       <c r="L24">
-        <v>201.3</v>
+        <v>184.9</v>
       </c>
       <c r="M24">
-        <v>201.4</v>
+        <v>184.7</v>
       </c>
       <c r="N24" t="s">
         <v>3</v>
@@ -1643,7 +1661,7 @@
         <v>-15000</v>
       </c>
       <c r="H25">
-        <v>101566.3</v>
+        <v>103239.8</v>
       </c>
       <c r="I25">
         <v>-35928.6</v>
@@ -1652,13 +1670,13 @@
         <v>-15000</v>
       </c>
       <c r="K25">
-        <v>97979.7</v>
+        <v>100959.2</v>
       </c>
       <c r="L25">
-        <v>203.1</v>
+        <v>221.4</v>
       </c>
       <c r="M25">
-        <v>201.7</v>
+        <v>219.9</v>
       </c>
       <c r="N25" t="s">
         <v>3</v>
@@ -1687,7 +1705,7 @@
         <v>-17800</v>
       </c>
       <c r="H26">
-        <v>101566.3</v>
+        <v>103239.8</v>
       </c>
       <c r="I26">
         <v>-35928.6</v>
@@ -1696,13 +1714,13 @@
         <v>-17800</v>
       </c>
       <c r="K26">
-        <v>123408.1</v>
+        <v>120428.5</v>
       </c>
       <c r="L26">
-        <v>2313.2</v>
+        <v>2227.9</v>
       </c>
       <c r="M26">
-        <v>2054</v>
+        <v>2108</v>
       </c>
       <c r="N26" t="s">
         <v>3</v>
@@ -1731,7 +1749,7 @@
         <v>-15000</v>
       </c>
       <c r="H27">
-        <v>123408.1</v>
+        <v>120428.5</v>
       </c>
       <c r="I27">
         <v>-53892.9</v>
@@ -1740,13 +1758,13 @@
         <v>-15000</v>
       </c>
       <c r="K27">
-        <v>122381.7</v>
+        <v>118463.7</v>
       </c>
       <c r="L27">
-        <v>201.4</v>
+        <v>184.7</v>
       </c>
       <c r="M27">
-        <v>201.1</v>
+        <v>184.5</v>
       </c>
       <c r="N27" t="s">
         <v>3</v>
@@ -1775,7 +1793,7 @@
         <v>-15000</v>
       </c>
       <c r="H28">
-        <v>97979.7</v>
+        <v>100959.2</v>
       </c>
       <c r="I28">
         <v>-53892.9</v>
@@ -1784,13 +1802,13 @@
         <v>-15000</v>
       </c>
       <c r="K28">
-        <v>93240.8</v>
+        <v>97158.8</v>
       </c>
       <c r="L28">
-        <v>201.7</v>
+        <v>219.9</v>
       </c>
       <c r="M28">
-        <v>200</v>
+        <v>217.5</v>
       </c>
       <c r="N28" t="s">
         <v>3</v>
@@ -1819,7 +1837,7 @@
         <v>-17800</v>
       </c>
       <c r="H29">
-        <v>97979.7</v>
+        <v>100959.2</v>
       </c>
       <c r="I29">
         <v>-53892.9</v>
@@ -1828,13 +1846,13 @@
         <v>-17800</v>
       </c>
       <c r="K29">
-        <v>122381.7</v>
+        <v>118463.7</v>
       </c>
       <c r="L29">
-        <v>2395.6</v>
+        <v>2328</v>
       </c>
       <c r="M29">
-        <v>2121.2</v>
+        <v>2156.6</v>
       </c>
       <c r="N29" t="s">
         <v>3</v>
@@ -1863,7 +1881,7 @@
         <v>-15000</v>
       </c>
       <c r="H30">
-        <v>122381.7</v>
+        <v>118463.7</v>
       </c>
       <c r="I30">
         <v>-71857.1</v>
@@ -1872,13 +1890,13 @@
         <v>-15000</v>
       </c>
       <c r="K30">
-        <v>120197.6</v>
+        <v>115710.2</v>
       </c>
       <c r="L30">
-        <v>201.1</v>
+        <v>184.5</v>
       </c>
       <c r="M30">
-        <v>200.9</v>
+        <v>184.4</v>
       </c>
       <c r="N30" t="s">
         <v>3</v>
@@ -1907,7 +1925,7 @@
         <v>-15000</v>
       </c>
       <c r="H31">
-        <v>93240.8</v>
+        <v>97158.8</v>
       </c>
       <c r="I31">
         <v>-71857.1</v>
@@ -1916,13 +1934,13 @@
         <v>-15000</v>
       </c>
       <c r="K31">
-        <v>87353.4</v>
+        <v>91840.8</v>
       </c>
       <c r="L31">
-        <v>200</v>
+        <v>217.5</v>
       </c>
       <c r="M31">
-        <v>197.6</v>
+        <v>214.1</v>
       </c>
       <c r="N31" t="s">
         <v>3</v>
@@ -1951,7 +1969,7 @@
         <v>-17800</v>
       </c>
       <c r="H32">
-        <v>93240.8</v>
+        <v>97158.8</v>
       </c>
       <c r="I32">
         <v>-71857.1</v>
@@ -1960,13 +1978,13 @@
         <v>-17800</v>
       </c>
       <c r="K32">
-        <v>120197.6</v>
+        <v>115710.2</v>
       </c>
       <c r="L32">
-        <v>2483.9</v>
+        <v>2439.4</v>
       </c>
       <c r="M32">
-        <v>2195.7</v>
+        <v>2208.8</v>
       </c>
       <c r="N32" t="s">
         <v>3</v>
@@ -1995,7 +2013,7 @@
         <v>-15000</v>
       </c>
       <c r="H33">
-        <v>120197.6</v>
+        <v>115710.2</v>
       </c>
       <c r="I33">
         <v>-89821.4</v>
@@ -2004,13 +2022,13 @@
         <v>-15000</v>
       </c>
       <c r="K33">
-        <v>116843.8</v>
+        <v>112159.7</v>
       </c>
       <c r="L33">
-        <v>200.9</v>
+        <v>184.4</v>
       </c>
       <c r="M33">
-        <v>200.9</v>
+        <v>184.9</v>
       </c>
       <c r="N33" t="s">
         <v>3</v>
@@ -2039,7 +2057,7 @@
         <v>-15000</v>
       </c>
       <c r="H34">
-        <v>87353.4</v>
+        <v>91840.8</v>
       </c>
       <c r="I34">
         <v>-89821.4</v>
@@ -2048,13 +2066,13 @@
         <v>-15000</v>
       </c>
       <c r="K34">
-        <v>80329.6</v>
+        <v>85013.8</v>
       </c>
       <c r="L34">
-        <v>197.6</v>
+        <v>214.1</v>
       </c>
       <c r="M34">
-        <v>194.5</v>
+        <v>209.7</v>
       </c>
       <c r="N34" t="s">
         <v>3</v>
@@ -2083,7 +2101,7 @@
         <v>-17800</v>
       </c>
       <c r="H35">
-        <v>87353.4</v>
+        <v>91840.8</v>
       </c>
       <c r="I35">
         <v>-89821.4</v>
@@ -2092,13 +2110,13 @@
         <v>-17800</v>
       </c>
       <c r="K35">
-        <v>116843.8</v>
+        <v>112159.7</v>
       </c>
       <c r="L35">
-        <v>2577.2</v>
+        <v>2560.7</v>
       </c>
       <c r="M35">
-        <v>2278.7</v>
+        <v>2265.7</v>
       </c>
       <c r="N35" t="s">
         <v>3</v>
@@ -2127,7 +2145,7 @@
         <v>-15000</v>
       </c>
       <c r="H36">
-        <v>116843.8</v>
+        <v>112159.7</v>
       </c>
       <c r="I36">
         <v>-107785.7</v>
@@ -2136,13 +2154,13 @@
         <v>-15000</v>
       </c>
       <c r="K36">
-        <v>112290.8</v>
+        <v>107788.3</v>
       </c>
       <c r="L36">
-        <v>200.9</v>
+        <v>184.9</v>
       </c>
       <c r="M36">
-        <v>201.9</v>
+        <v>186.5</v>
       </c>
       <c r="N36" t="s">
         <v>3</v>
@@ -2171,7 +2189,7 @@
         <v>-15000</v>
       </c>
       <c r="H37">
-        <v>80329.6</v>
+        <v>85013.8</v>
       </c>
       <c r="I37">
         <v>-107785.7</v>
@@ -2180,13 +2198,13 @@
         <v>-15000</v>
       </c>
       <c r="K37">
-        <v>72199</v>
+        <v>76701.5</v>
       </c>
       <c r="L37">
-        <v>194.5</v>
+        <v>209.7</v>
       </c>
       <c r="M37">
-        <v>190.1</v>
+        <v>204</v>
       </c>
       <c r="N37" t="s">
         <v>3</v>
@@ -2215,7 +2233,7 @@
         <v>-17800</v>
       </c>
       <c r="H38">
-        <v>80329.6</v>
+        <v>85013.8</v>
       </c>
       <c r="I38">
         <v>-107785.7</v>
@@ -2224,13 +2242,13 @@
         <v>-17800</v>
       </c>
       <c r="K38">
-        <v>112290.8</v>
+        <v>107788.3</v>
       </c>
       <c r="L38">
-        <v>2673.4</v>
+        <v>2689.6</v>
       </c>
       <c r="M38">
-        <v>2373</v>
+        <v>2329.9</v>
       </c>
       <c r="N38" t="s">
         <v>3</v>
@@ -2259,7 +2277,7 @@
         <v>-15000</v>
       </c>
       <c r="H39">
-        <v>112290.8</v>
+        <v>107788.3</v>
       </c>
       <c r="I39">
         <v>-125750</v>
@@ -2268,13 +2286,13 @@
         <v>-15000</v>
       </c>
       <c r="K39">
-        <v>106476.6</v>
+        <v>102539.1</v>
       </c>
       <c r="L39">
-        <v>201.9</v>
+        <v>186.5</v>
       </c>
       <c r="M39">
-        <v>204.2</v>
+        <v>190.3</v>
       </c>
       <c r="N39" t="s">
         <v>3</v>
@@ -2303,7 +2321,7 @@
         <v>-15000</v>
       </c>
       <c r="H40">
-        <v>72199</v>
+        <v>76701.5</v>
       </c>
       <c r="I40">
         <v>-125750</v>
@@ -2312,13 +2330,13 @@
         <v>-15000</v>
       </c>
       <c r="K40">
-        <v>63023.4</v>
+        <v>66960.9</v>
       </c>
       <c r="L40">
-        <v>190.1</v>
+        <v>204</v>
       </c>
       <c r="M40">
-        <v>184.1</v>
+        <v>196.4</v>
       </c>
       <c r="N40" t="s">
         <v>3</v>
@@ -2347,7 +2365,7 @@
         <v>-17800</v>
       </c>
       <c r="H41">
-        <v>72199</v>
+        <v>76701.5</v>
       </c>
       <c r="I41">
         <v>-125750</v>
@@ -2356,13 +2374,13 @@
         <v>-17800</v>
       </c>
       <c r="K41">
-        <v>106476.6</v>
+        <v>102539.1</v>
       </c>
       <c r="L41">
-        <v>2768.6</v>
+        <v>2821.8</v>
       </c>
       <c r="M41">
-        <v>2483.7</v>
+        <v>2407</v>
       </c>
       <c r="N41" t="s">
         <v>3</v>
@@ -2391,7 +2409,7 @@
         <v>-15000</v>
       </c>
       <c r="H42">
-        <v>106476.6</v>
+        <v>102539.1</v>
       </c>
       <c r="I42">
         <v>-143714.3</v>
@@ -2400,13 +2418,13 @@
         <v>-15000</v>
       </c>
       <c r="K42">
-        <v>99285.3</v>
+        <v>96291.2</v>
       </c>
       <c r="L42">
-        <v>204.2</v>
+        <v>190.3</v>
       </c>
       <c r="M42">
-        <v>208.6</v>
+        <v>197.9</v>
       </c>
       <c r="N42" t="s">
         <v>3</v>
@@ -2435,7 +2453,7 @@
         <v>-15000</v>
       </c>
       <c r="H43">
-        <v>63023.4</v>
+        <v>66960.9</v>
       </c>
       <c r="I43">
         <v>-143714.3</v>
@@ -2444,13 +2462,13 @@
         <v>-15000</v>
       </c>
       <c r="K43">
-        <v>52918.8</v>
+        <v>55912.9</v>
       </c>
       <c r="L43">
-        <v>184.1</v>
+        <v>196.4</v>
       </c>
       <c r="M43">
-        <v>175.8</v>
+        <v>185.9</v>
       </c>
       <c r="N43" t="s">
         <v>3</v>
@@ -2479,7 +2497,7 @@
         <v>-17800</v>
       </c>
       <c r="H44">
-        <v>63023.4</v>
+        <v>66960.9</v>
       </c>
       <c r="I44">
         <v>-143714.3</v>
@@ -2488,13 +2506,13 @@
         <v>-17800</v>
       </c>
       <c r="K44">
-        <v>99285.3</v>
+        <v>96291.2</v>
       </c>
       <c r="L44">
-        <v>2856.7</v>
+        <v>2949.3</v>
       </c>
       <c r="M44">
-        <v>2619.6</v>
+        <v>2507.9</v>
       </c>
       <c r="N44" t="s">
         <v>3</v>
@@ -2523,7 +2541,7 @@
         <v>-15000</v>
       </c>
       <c r="H45">
-        <v>99285.3</v>
+        <v>96291.2</v>
       </c>
       <c r="I45">
         <v>-161678.6</v>
@@ -2532,13 +2550,13 @@
         <v>-15000</v>
       </c>
       <c r="K45">
-        <v>90518</v>
+        <v>88810.9</v>
       </c>
       <c r="L45">
-        <v>208.6</v>
+        <v>197.9</v>
       </c>
       <c r="M45">
-        <v>215.4</v>
+        <v>210.7</v>
       </c>
       <c r="N45" t="s">
         <v>3</v>
@@ -2567,7 +2585,7 @@
         <v>-15000</v>
       </c>
       <c r="H46">
-        <v>52918.8</v>
+        <v>55912.9</v>
       </c>
       <c r="I46">
         <v>-161678.6</v>
@@ -2576,13 +2594,13 @@
         <v>-15000</v>
       </c>
       <c r="K46">
-        <v>42084.1</v>
+        <v>43791.2</v>
       </c>
       <c r="L46">
-        <v>175.8</v>
+        <v>185.9</v>
       </c>
       <c r="M46">
-        <v>164.1</v>
+        <v>170.9</v>
       </c>
       <c r="N46" t="s">
         <v>3</v>
@@ -2611,7 +2629,7 @@
         <v>-17800</v>
       </c>
       <c r="H47">
-        <v>52918.8</v>
+        <v>55912.9</v>
       </c>
       <c r="I47">
         <v>-161678.6</v>
@@ -2620,13 +2638,13 @@
         <v>-17800</v>
       </c>
       <c r="K47">
-        <v>90518</v>
+        <v>88810.9</v>
       </c>
       <c r="L47">
-        <v>2928.1</v>
+        <v>3058.1</v>
       </c>
       <c r="M47">
-        <v>2794.9</v>
+        <v>2652.5</v>
       </c>
       <c r="N47" t="s">
         <v>3</v>
@@ -2655,7 +2673,7 @@
         <v>-15000</v>
       </c>
       <c r="H48">
-        <v>90518</v>
+        <v>88810.9</v>
       </c>
       <c r="I48">
         <v>-179642.9</v>
@@ -2664,13 +2682,13 @@
         <v>-15000</v>
       </c>
       <c r="K48">
-        <v>79854.2</v>
+        <v>79677.3</v>
       </c>
       <c r="L48">
-        <v>215.4</v>
+        <v>210.7</v>
       </c>
       <c r="M48">
-        <v>224.1</v>
+        <v>229.3</v>
       </c>
       <c r="N48" t="s">
         <v>3</v>
@@ -2699,7 +2717,7 @@
         <v>-15000</v>
       </c>
       <c r="H49">
-        <v>42084.1</v>
+        <v>43791.2</v>
       </c>
       <c r="I49">
         <v>-179642.9</v>
@@ -2708,13 +2726,13 @@
         <v>-15000</v>
       </c>
       <c r="K49">
-        <v>30839.6</v>
+        <v>31016.6</v>
       </c>
       <c r="L49">
-        <v>164.1</v>
+        <v>170.9</v>
       </c>
       <c r="M49">
-        <v>152.8</v>
+        <v>151.9</v>
       </c>
       <c r="N49" t="s">
         <v>3</v>
@@ -2743,7 +2761,7 @@
         <v>-17800</v>
       </c>
       <c r="H50">
-        <v>42084.1</v>
+        <v>43791.2</v>
       </c>
       <c r="I50">
         <v>-179642.9</v>
@@ -2752,13 +2770,13 @@
         <v>-17800</v>
       </c>
       <c r="K50">
-        <v>79854.2</v>
+        <v>79677.3</v>
       </c>
       <c r="L50">
-        <v>2968.9</v>
+        <v>3126</v>
       </c>
       <c r="M50">
-        <v>3031.5</v>
+        <v>2876</v>
       </c>
       <c r="N50" t="s">
         <v>3</v>
@@ -2787,7 +2805,7 @@
         <v>-15000</v>
       </c>
       <c r="H51">
-        <v>79854.2</v>
+        <v>79677.3</v>
       </c>
       <c r="I51">
         <v>-197607.1</v>
@@ -2796,13 +2814,13 @@
         <v>-15000</v>
       </c>
       <c r="K51">
-        <v>66803.1</v>
+        <v>68176.5</v>
       </c>
       <c r="L51">
-        <v>224.1</v>
+        <v>229.3</v>
       </c>
       <c r="M51">
-        <v>233.5</v>
+        <v>251.7</v>
       </c>
       <c r="N51" t="s">
         <v>3</v>
@@ -2831,7 +2849,7 @@
         <v>-15000</v>
       </c>
       <c r="H52">
-        <v>30839.6</v>
+        <v>31016.6</v>
       </c>
       <c r="I52">
         <v>-197607.1</v>
@@ -2840,13 +2858,13 @@
         <v>-15000</v>
       </c>
       <c r="K52">
-        <v>19676.5</v>
+        <v>18303.1</v>
       </c>
       <c r="L52">
-        <v>152.8</v>
+        <v>151.9</v>
       </c>
       <c r="M52">
-        <v>178</v>
+        <v>189.5</v>
       </c>
       <c r="N52" t="s">
         <v>3</v>
@@ -2875,7 +2893,7 @@
         <v>-17800</v>
       </c>
       <c r="H53">
-        <v>30839.6</v>
+        <v>31016.6</v>
       </c>
       <c r="I53">
         <v>-197607.1</v>
@@ -2884,13 +2902,13 @@
         <v>-17800</v>
       </c>
       <c r="K53">
-        <v>66803.1</v>
+        <v>68176.5</v>
       </c>
       <c r="L53">
-        <v>2968.9</v>
+        <v>3126</v>
       </c>
       <c r="M53">
-        <v>3361.7</v>
+        <v>3238.2</v>
       </c>
       <c r="N53" t="s">
         <v>3</v>
@@ -2919,7 +2937,7 @@
         <v>-15000</v>
       </c>
       <c r="H54">
-        <v>66803.1</v>
+        <v>68176.5</v>
       </c>
       <c r="I54">
         <v>-215571.4</v>
@@ -2928,13 +2946,13 @@
         <v>-15000</v>
       </c>
       <c r="K54">
-        <v>50642.9</v>
+        <v>53155.2</v>
       </c>
       <c r="L54">
-        <v>233.5</v>
+        <v>251.7</v>
       </c>
       <c r="M54">
-        <v>241</v>
+        <v>270.8</v>
       </c>
       <c r="N54" t="s">
         <v>3</v>
@@ -2963,7 +2981,7 @@
         <v>-15000</v>
       </c>
       <c r="H55">
-        <v>19676.5</v>
+        <v>18303.1</v>
       </c>
       <c r="I55">
         <v>-215571.4</v>
@@ -2972,13 +2990,13 @@
         <v>-15000</v>
       </c>
       <c r="K55">
-        <v>9316.3</v>
+        <v>6804</v>
       </c>
       <c r="L55">
-        <v>178</v>
+        <v>189.5</v>
       </c>
       <c r="M55">
-        <v>217.8</v>
+        <v>258.7</v>
       </c>
       <c r="N55" t="s">
         <v>3</v>
@@ -3007,7 +3025,7 @@
         <v>-17800</v>
       </c>
       <c r="H56">
-        <v>19676.5</v>
+        <v>18303.1</v>
       </c>
       <c r="I56">
         <v>-215571.4</v>
@@ -3016,13 +3034,13 @@
         <v>-17800</v>
       </c>
       <c r="K56">
-        <v>50642.9</v>
+        <v>53155.2</v>
       </c>
       <c r="L56">
-        <v>2960.8</v>
+        <v>3119.6</v>
       </c>
       <c r="M56">
-        <v>3830.8</v>
+        <v>3835</v>
       </c>
       <c r="N56" t="s">
         <v>3</v>
@@ -3051,7 +3069,7 @@
         <v>-15000</v>
       </c>
       <c r="H57">
-        <v>50642.9</v>
+        <v>53155.2</v>
       </c>
       <c r="I57">
         <v>-233535.7</v>
@@ -3060,13 +3078,13 @@
         <v>-15000</v>
       </c>
       <c r="K57">
-        <v>30347.7</v>
+        <v>32823.7</v>
       </c>
       <c r="L57">
-        <v>241</v>
+        <v>270.8</v>
       </c>
       <c r="M57">
-        <v>243.9</v>
+        <v>277</v>
       </c>
       <c r="N57" t="s">
         <v>3</v>
@@ -3095,7 +3113,7 @@
         <v>-15000</v>
       </c>
       <c r="H58">
-        <v>9316.3</v>
+        <v>6804</v>
       </c>
       <c r="I58">
         <v>-233535.7</v>
@@ -3104,13 +3122,13 @@
         <v>-15000</v>
       </c>
       <c r="K58">
-        <v>785</v>
+        <v>-1691</v>
       </c>
       <c r="L58">
-        <v>217.8</v>
+        <v>258.7</v>
       </c>
       <c r="M58">
-        <v>283.9</v>
+        <v>395.3</v>
       </c>
       <c r="N58" t="s">
         <v>3</v>
@@ -3139,7 +3157,7 @@
         <v>-17800</v>
       </c>
       <c r="H59">
-        <v>9316.3</v>
+        <v>6804</v>
       </c>
       <c r="I59">
         <v>-233535.7</v>
@@ -3148,13 +3166,13 @@
         <v>-17800</v>
       </c>
       <c r="K59">
-        <v>30347.7</v>
+        <v>32823.7</v>
       </c>
       <c r="L59">
-        <v>2881.5</v>
+        <v>2994.5</v>
       </c>
       <c r="M59">
-        <v>4498.5</v>
+        <v>4806.3</v>
       </c>
       <c r="N59" t="s">
         <v>3</v>
@@ -3183,7 +3201,7 @@
         <v>-15000</v>
       </c>
       <c r="H60">
-        <v>30347.7</v>
+        <v>32823.7</v>
       </c>
       <c r="I60">
         <v>-251500</v>
@@ -3195,7 +3213,7 @@
         <v>4500</v>
       </c>
       <c r="L60">
-        <v>243.9</v>
+        <v>277</v>
       </c>
       <c r="M60">
         <v>150</v>
@@ -3227,7 +3245,7 @@
         <v>-15000</v>
       </c>
       <c r="H61">
-        <v>785</v>
+        <v>-1691</v>
       </c>
       <c r="I61">
         <v>-251500</v>
@@ -3239,7 +3257,7 @@
         <v>-4500</v>
       </c>
       <c r="L61">
-        <v>283.9</v>
+        <v>395.3</v>
       </c>
       <c r="M61">
         <v>150</v>
@@ -3271,7 +3289,7 @@
         <v>-17800</v>
       </c>
       <c r="H62">
-        <v>785</v>
+        <v>-1691</v>
       </c>
       <c r="I62">
         <v>-251500</v>
@@ -3283,10 +3301,10 @@
         <v>4500</v>
       </c>
       <c r="L62">
-        <v>2709.4</v>
+        <v>2706.1</v>
       </c>
       <c r="M62">
-        <v>4498.5</v>
+        <v>4806.3</v>
       </c>
       <c r="N62" t="s">
         <v>3</v>
@@ -3315,7 +3333,7 @@
         <v>-15000</v>
       </c>
       <c r="H63">
-        <v>101566.3</v>
+        <v>103239.8</v>
       </c>
       <c r="I63">
         <v>-17964.3</v>
@@ -3324,13 +3342,13 @@
         <v>-15000</v>
       </c>
       <c r="K63">
-        <v>123280.6</v>
+        <v>121607.1</v>
       </c>
       <c r="L63">
-        <v>2293.3</v>
+        <v>2215.2</v>
       </c>
       <c r="M63">
-        <v>2061.1</v>
+        <v>2055.9</v>
       </c>
       <c r="N63" t="s">
         <v>3</v>
@@ -3359,7 +3377,7 @@
         <v>-15000</v>
       </c>
       <c r="H64">
-        <v>97979.7</v>
+        <v>100959.2</v>
       </c>
       <c r="I64">
         <v>-35928.6</v>
@@ -3368,13 +3386,13 @@
         <v>-15000</v>
       </c>
       <c r="K64">
-        <v>123408.1</v>
+        <v>120428.5</v>
       </c>
       <c r="L64">
-        <v>2369.2</v>
+        <v>2306.9</v>
       </c>
       <c r="M64">
-        <v>2048.3</v>
+        <v>2097</v>
       </c>
       <c r="N64" t="s">
         <v>3</v>
@@ -3403,7 +3421,7 @@
         <v>-15000</v>
       </c>
       <c r="H65">
-        <v>93240.8</v>
+        <v>97158.8</v>
       </c>
       <c r="I65">
         <v>-53892.9</v>
@@ -3412,13 +3430,13 @@
         <v>-15000</v>
       </c>
       <c r="K65">
-        <v>122381.7</v>
+        <v>118463.7</v>
       </c>
       <c r="L65">
-        <v>2451.1</v>
+        <v>2409.7</v>
       </c>
       <c r="M65">
-        <v>2109</v>
+        <v>2141.3</v>
       </c>
       <c r="N65" t="s">
         <v>3</v>
@@ -3447,7 +3465,7 @@
         <v>-15000</v>
       </c>
       <c r="H66">
-        <v>87353.4</v>
+        <v>91840.8</v>
       </c>
       <c r="I66">
         <v>-71857.1</v>
@@ -3456,13 +3474,13 @@
         <v>-15000</v>
       </c>
       <c r="K66">
-        <v>120197.6</v>
+        <v>115710.2</v>
       </c>
       <c r="L66">
-        <v>2538.1</v>
+        <v>2522.6</v>
       </c>
       <c r="M66">
-        <v>2177</v>
+        <v>2189.1</v>
       </c>
       <c r="N66" t="s">
         <v>3</v>
@@ -3491,7 +3509,7 @@
         <v>-15000</v>
       </c>
       <c r="H67">
-        <v>80329.6</v>
+        <v>85013.8</v>
       </c>
       <c r="I67">
         <v>-89821.4</v>
@@ -3500,13 +3518,13 @@
         <v>-15000</v>
       </c>
       <c r="K67">
-        <v>116843.8</v>
+        <v>112159.7</v>
       </c>
       <c r="L67">
-        <v>2628.1</v>
+        <v>2643.3</v>
       </c>
       <c r="M67">
-        <v>2253.3</v>
+        <v>2241.4</v>
       </c>
       <c r="N67" t="s">
         <v>3</v>
@@ -3535,7 +3553,7 @@
         <v>-15000</v>
       </c>
       <c r="H68">
-        <v>72199</v>
+        <v>76701.5</v>
       </c>
       <c r="I68">
         <v>-107785.7</v>
@@ -3544,13 +3562,13 @@
         <v>-15000</v>
       </c>
       <c r="K68">
-        <v>112290.8</v>
+        <v>107788.3</v>
       </c>
       <c r="L68">
-        <v>2717.5</v>
+        <v>2767.6</v>
       </c>
       <c r="M68">
-        <v>2340.6</v>
+        <v>2300.7</v>
       </c>
       <c r="N68" t="s">
         <v>3</v>
@@ -3579,7 +3597,7 @@
         <v>-15000</v>
       </c>
       <c r="H69">
-        <v>63023.4</v>
+        <v>66960.9</v>
       </c>
       <c r="I69">
         <v>-125750</v>
@@ -3588,13 +3606,13 @@
         <v>-15000</v>
       </c>
       <c r="K69">
-        <v>106476.6</v>
+        <v>102539.1</v>
       </c>
       <c r="L69">
-        <v>2800.5</v>
+        <v>2887.8</v>
       </c>
       <c r="M69">
-        <v>2443.7</v>
+        <v>2372.2</v>
       </c>
       <c r="N69" t="s">
         <v>3</v>
@@ -3623,7 +3641,7 @@
         <v>-15000</v>
       </c>
       <c r="H70">
-        <v>52918.8</v>
+        <v>55912.9</v>
       </c>
       <c r="I70">
         <v>-143714.3</v>
@@ -3632,13 +3650,13 @@
         <v>-15000</v>
       </c>
       <c r="K70">
-        <v>99285.3</v>
+        <v>96291.2</v>
       </c>
       <c r="L70">
-        <v>2867.8</v>
+        <v>2990.6</v>
       </c>
       <c r="M70">
-        <v>2570.8</v>
+        <v>2466.3</v>
       </c>
       <c r="N70" t="s">
         <v>3</v>
@@ -3667,7 +3685,7 @@
         <v>-15000</v>
       </c>
       <c r="H71">
-        <v>42084.1</v>
+        <v>43791.2</v>
       </c>
       <c r="I71">
         <v>-161678.6</v>
@@ -3676,13 +3694,13 @@
         <v>-15000</v>
       </c>
       <c r="K71">
-        <v>90518</v>
+        <v>88810.9</v>
       </c>
       <c r="L71">
-        <v>2906.3</v>
+        <v>3054.9</v>
       </c>
       <c r="M71">
-        <v>2735.5</v>
+        <v>2601.7</v>
       </c>
       <c r="N71" t="s">
         <v>3</v>
@@ -3711,7 +3729,7 @@
         <v>-15000</v>
       </c>
       <c r="H72">
-        <v>30839.6</v>
+        <v>31016.6</v>
       </c>
       <c r="I72">
         <v>-179642.9</v>
@@ -3720,13 +3738,13 @@
         <v>-15000</v>
       </c>
       <c r="K72">
-        <v>79854.2</v>
+        <v>79677.3</v>
       </c>
       <c r="L72">
-        <v>2906.3</v>
+        <v>3054.9</v>
       </c>
       <c r="M72">
-        <v>2958.9</v>
+        <v>2812</v>
       </c>
       <c r="N72" t="s">
         <v>3</v>
@@ -3755,7 +3773,7 @@
         <v>-15000</v>
       </c>
       <c r="H73">
-        <v>19676.5</v>
+        <v>18303.1</v>
       </c>
       <c r="I73">
         <v>-197607.1</v>
@@ -3764,13 +3782,13 @@
         <v>-15000</v>
       </c>
       <c r="K73">
-        <v>66803.1</v>
+        <v>68176.5</v>
       </c>
       <c r="L73">
-        <v>2898.6</v>
+        <v>3048.8</v>
       </c>
       <c r="M73">
-        <v>3271.8</v>
+        <v>3154.6</v>
       </c>
       <c r="N73" t="s">
         <v>3</v>
@@ -3799,7 +3817,7 @@
         <v>-15000</v>
       </c>
       <c r="H74">
-        <v>9316.3</v>
+        <v>6804</v>
       </c>
       <c r="I74">
         <v>-215571.4</v>
@@ -3808,13 +3826,13 @@
         <v>-15000</v>
       </c>
       <c r="K74">
-        <v>50642.9</v>
+        <v>53155.2</v>
       </c>
       <c r="L74">
-        <v>2823.8</v>
+        <v>2930.5</v>
       </c>
       <c r="M74">
-        <v>3717.8</v>
+        <v>3721.8</v>
       </c>
       <c r="N74" t="s">
         <v>3</v>
@@ -3843,7 +3861,7 @@
         <v>-15000</v>
       </c>
       <c r="H75">
-        <v>785</v>
+        <v>-1691</v>
       </c>
       <c r="I75">
         <v>-233535.7</v>
@@ -3852,13 +3870,13 @@
         <v>-15000</v>
       </c>
       <c r="K75">
-        <v>30347.7</v>
+        <v>32823.7</v>
       </c>
       <c r="L75">
-        <v>2661.9</v>
+        <v>2658.8</v>
       </c>
       <c r="M75">
-        <v>4354.6</v>
+        <v>4648.6</v>
       </c>
       <c r="N75" t="s">
         <v>3</v>
@@ -3899,10 +3917,10 @@
         <v>4500</v>
       </c>
       <c r="L76">
-        <v>2407.4</v>
+        <v>2245.7</v>
       </c>
       <c r="M76">
-        <v>4354.6</v>
+        <v>4648.6</v>
       </c>
       <c r="N76" t="s">
         <v>3</v>
@@ -3972,7 +3990,7 @@
         <v>68</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F78" t="s">
         <v>22</v>
@@ -3986,7 +4004,7 @@
         <v>40</v>
       </c>
       <c r="C80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -4053,7 +4071,7 @@
         <v>59</v>
       </c>
       <c r="C82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D82" t="s">
         <v>27</v>
@@ -4068,7 +4086,7 @@
         <v>-15000</v>
       </c>
       <c r="H82">
-        <v>123280.6</v>
+        <v>121607.1</v>
       </c>
       <c r="I82">
         <v>-17964.3</v>
@@ -4077,7 +4095,7 @@
         <v>15000</v>
       </c>
       <c r="K82">
-        <v>123280.6</v>
+        <v>121607.1</v>
       </c>
       <c r="L82">
         <v>2900</v>
@@ -4097,7 +4115,7 @@
         <v>59</v>
       </c>
       <c r="C83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D83" t="s">
         <v>27</v>
@@ -4112,7 +4130,7 @@
         <v>-15000</v>
       </c>
       <c r="H83">
-        <v>101566.3</v>
+        <v>103239.8</v>
       </c>
       <c r="I83">
         <v>-17964.3</v>
@@ -4121,7 +4139,7 @@
         <v>15000</v>
       </c>
       <c r="K83">
-        <v>101566.3</v>
+        <v>103239.8</v>
       </c>
       <c r="L83">
         <v>3000</v>
@@ -4141,7 +4159,7 @@
         <v>59</v>
       </c>
       <c r="C84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D84" t="s">
         <v>27</v>
@@ -4156,7 +4174,7 @@
         <v>-15000</v>
       </c>
       <c r="H84">
-        <v>123408.1</v>
+        <v>120428.5</v>
       </c>
       <c r="I84">
         <v>-35928.6</v>
@@ -4165,7 +4183,7 @@
         <v>15000</v>
       </c>
       <c r="K84">
-        <v>123408.1</v>
+        <v>120428.5</v>
       </c>
       <c r="L84">
         <v>2900</v>
@@ -4185,7 +4203,7 @@
         <v>59</v>
       </c>
       <c r="C85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D85" t="s">
         <v>27</v>
@@ -4200,7 +4218,7 @@
         <v>-15000</v>
       </c>
       <c r="H85">
-        <v>97979.7</v>
+        <v>100959.2</v>
       </c>
       <c r="I85">
         <v>-35928.6</v>
@@ -4209,7 +4227,7 @@
         <v>15000</v>
       </c>
       <c r="K85">
-        <v>97979.7</v>
+        <v>100959.2</v>
       </c>
       <c r="L85">
         <v>3000</v>
@@ -4229,7 +4247,7 @@
         <v>59</v>
       </c>
       <c r="C86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D86" t="s">
         <v>27</v>
@@ -4244,7 +4262,7 @@
         <v>-15000</v>
       </c>
       <c r="H86">
-        <v>122381.7</v>
+        <v>118463.7</v>
       </c>
       <c r="I86">
         <v>-53892.9</v>
@@ -4253,7 +4271,7 @@
         <v>15000</v>
       </c>
       <c r="K86">
-        <v>122381.7</v>
+        <v>118463.7</v>
       </c>
       <c r="L86">
         <v>2900</v>
@@ -4273,7 +4291,7 @@
         <v>59</v>
       </c>
       <c r="C87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D87" t="s">
         <v>27</v>
@@ -4288,7 +4306,7 @@
         <v>-15000</v>
       </c>
       <c r="H87">
-        <v>93240.8</v>
+        <v>97158.8</v>
       </c>
       <c r="I87">
         <v>-53892.9</v>
@@ -4297,7 +4315,7 @@
         <v>15000</v>
       </c>
       <c r="K87">
-        <v>93240.8</v>
+        <v>97158.8</v>
       </c>
       <c r="L87">
         <v>3000</v>
@@ -4317,7 +4335,7 @@
         <v>59</v>
       </c>
       <c r="C88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D88" t="s">
         <v>27</v>
@@ -4332,7 +4350,7 @@
         <v>-15000</v>
       </c>
       <c r="H88">
-        <v>120197.6</v>
+        <v>115710.2</v>
       </c>
       <c r="I88">
         <v>-71857.1</v>
@@ -4341,7 +4359,7 @@
         <v>15000</v>
       </c>
       <c r="K88">
-        <v>120197.6</v>
+        <v>115710.2</v>
       </c>
       <c r="L88">
         <v>2900</v>
@@ -4361,7 +4379,7 @@
         <v>59</v>
       </c>
       <c r="C89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D89" t="s">
         <v>27</v>
@@ -4376,7 +4394,7 @@
         <v>-15000</v>
       </c>
       <c r="H89">
-        <v>87353.4</v>
+        <v>91840.8</v>
       </c>
       <c r="I89">
         <v>-71857.1</v>
@@ -4385,7 +4403,7 @@
         <v>15000</v>
       </c>
       <c r="K89">
-        <v>87353.4</v>
+        <v>91840.8</v>
       </c>
       <c r="L89">
         <v>3000</v>
@@ -4405,7 +4423,7 @@
         <v>59</v>
       </c>
       <c r="C90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D90" t="s">
         <v>27</v>
@@ -4420,7 +4438,7 @@
         <v>-15000</v>
       </c>
       <c r="H90">
-        <v>116843.8</v>
+        <v>112159.7</v>
       </c>
       <c r="I90">
         <v>-89821.4</v>
@@ -4429,7 +4447,7 @@
         <v>15000</v>
       </c>
       <c r="K90">
-        <v>116843.8</v>
+        <v>112159.7</v>
       </c>
       <c r="L90">
         <v>2900</v>
@@ -4449,7 +4467,7 @@
         <v>59</v>
       </c>
       <c r="C91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D91" t="s">
         <v>27</v>
@@ -4464,7 +4482,7 @@
         <v>-15000</v>
       </c>
       <c r="H91">
-        <v>80329.6</v>
+        <v>85013.8</v>
       </c>
       <c r="I91">
         <v>-89821.4</v>
@@ -4473,7 +4491,7 @@
         <v>15000</v>
       </c>
       <c r="K91">
-        <v>80329.6</v>
+        <v>85013.8</v>
       </c>
       <c r="L91">
         <v>3000</v>
@@ -4493,7 +4511,7 @@
         <v>59</v>
       </c>
       <c r="C92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D92" t="s">
         <v>27</v>
@@ -4508,7 +4526,7 @@
         <v>-15000</v>
       </c>
       <c r="H92">
-        <v>112290.8</v>
+        <v>107788.3</v>
       </c>
       <c r="I92">
         <v>-107785.7</v>
@@ -4517,7 +4535,7 @@
         <v>15000</v>
       </c>
       <c r="K92">
-        <v>112290.8</v>
+        <v>107788.3</v>
       </c>
       <c r="L92">
         <v>2900</v>
@@ -4537,7 +4555,7 @@
         <v>59</v>
       </c>
       <c r="C93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D93" t="s">
         <v>27</v>
@@ -4552,7 +4570,7 @@
         <v>-15000</v>
       </c>
       <c r="H93">
-        <v>72199</v>
+        <v>76701.5</v>
       </c>
       <c r="I93">
         <v>-107785.7</v>
@@ -4561,7 +4579,7 @@
         <v>15000</v>
       </c>
       <c r="K93">
-        <v>72199</v>
+        <v>76701.5</v>
       </c>
       <c r="L93">
         <v>3000</v>
@@ -4581,7 +4599,7 @@
         <v>59</v>
       </c>
       <c r="C94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D94" t="s">
         <v>27</v>
@@ -4596,7 +4614,7 @@
         <v>-15000</v>
       </c>
       <c r="H94">
-        <v>106476.6</v>
+        <v>102539.1</v>
       </c>
       <c r="I94">
         <v>-125750</v>
@@ -4605,7 +4623,7 @@
         <v>15000</v>
       </c>
       <c r="K94">
-        <v>106476.6</v>
+        <v>102539.1</v>
       </c>
       <c r="L94">
         <v>2900</v>
@@ -4625,7 +4643,7 @@
         <v>59</v>
       </c>
       <c r="C95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D95" t="s">
         <v>27</v>
@@ -4640,7 +4658,7 @@
         <v>-15000</v>
       </c>
       <c r="H95">
-        <v>63023.4</v>
+        <v>66960.9</v>
       </c>
       <c r="I95">
         <v>-125750</v>
@@ -4649,7 +4667,7 @@
         <v>15000</v>
       </c>
       <c r="K95">
-        <v>63023.4</v>
+        <v>66960.9</v>
       </c>
       <c r="L95">
         <v>3000</v>
@@ -4669,7 +4687,7 @@
         <v>59</v>
       </c>
       <c r="C96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D96" t="s">
         <v>27</v>
@@ -4684,7 +4702,7 @@
         <v>-15000</v>
       </c>
       <c r="H96">
-        <v>99285.3</v>
+        <v>96291.2</v>
       </c>
       <c r="I96">
         <v>-143714.3</v>
@@ -4693,7 +4711,7 @@
         <v>15000</v>
       </c>
       <c r="K96">
-        <v>99285.3</v>
+        <v>96291.2</v>
       </c>
       <c r="L96">
         <v>2900</v>
@@ -4713,7 +4731,7 @@
         <v>59</v>
       </c>
       <c r="C97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D97" t="s">
         <v>27</v>
@@ -4728,7 +4746,7 @@
         <v>-15000</v>
       </c>
       <c r="H97">
-        <v>52918.8</v>
+        <v>55912.9</v>
       </c>
       <c r="I97">
         <v>-143714.3</v>
@@ -4737,7 +4755,7 @@
         <v>15000</v>
       </c>
       <c r="K97">
-        <v>52918.8</v>
+        <v>55912.9</v>
       </c>
       <c r="L97">
         <v>3000</v>
@@ -4757,7 +4775,7 @@
         <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D98" t="s">
         <v>27</v>
@@ -4772,7 +4790,7 @@
         <v>-15000</v>
       </c>
       <c r="H98">
-        <v>90518</v>
+        <v>88810.9</v>
       </c>
       <c r="I98">
         <v>-161678.6</v>
@@ -4781,7 +4799,7 @@
         <v>15000</v>
       </c>
       <c r="K98">
-        <v>90518</v>
+        <v>88810.9</v>
       </c>
       <c r="L98">
         <v>2900</v>
@@ -4801,7 +4819,7 @@
         <v>59</v>
       </c>
       <c r="C99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D99" t="s">
         <v>27</v>
@@ -4810,28 +4828,28 @@
         <v>3</v>
       </c>
       <c r="F99">
-        <v>-179642.9</v>
+        <v>-161678.6</v>
       </c>
       <c r="G99">
         <v>-15000</v>
       </c>
       <c r="H99">
-        <v>79854.2</v>
+        <v>43791.2</v>
       </c>
       <c r="I99">
-        <v>-179642.9</v>
+        <v>-161678.6</v>
       </c>
       <c r="J99">
         <v>15000</v>
       </c>
       <c r="K99">
-        <v>79854.2</v>
+        <v>43791.2</v>
       </c>
       <c r="L99">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="M99">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="N99" t="s">
         <v>3</v>
@@ -4845,7 +4863,7 @@
         <v>59</v>
       </c>
       <c r="C100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D100" t="s">
         <v>27</v>
@@ -4860,7 +4878,7 @@
         <v>-15000</v>
       </c>
       <c r="H100">
-        <v>30839.6</v>
+        <v>79677.3</v>
       </c>
       <c r="I100">
         <v>-179642.9</v>
@@ -4869,13 +4887,13 @@
         <v>15000</v>
       </c>
       <c r="K100">
-        <v>30839.6</v>
+        <v>79677.3</v>
       </c>
       <c r="L100">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="M100">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="N100" t="s">
         <v>3</v>
@@ -4889,7 +4907,7 @@
         <v>59</v>
       </c>
       <c r="C101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D101" t="s">
         <v>27</v>
@@ -4898,28 +4916,28 @@
         <v>3</v>
       </c>
       <c r="F101">
-        <v>-197607.1</v>
+        <v>-179642.9</v>
       </c>
       <c r="G101">
         <v>-15000</v>
       </c>
       <c r="H101">
-        <v>66803.1</v>
+        <v>31016.6</v>
       </c>
       <c r="I101">
-        <v>-197607.1</v>
+        <v>-179642.9</v>
       </c>
       <c r="J101">
         <v>15000</v>
       </c>
       <c r="K101">
-        <v>66803.1</v>
+        <v>31016.6</v>
       </c>
       <c r="L101">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="M101">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="N101" t="s">
         <v>3</v>
@@ -4933,7 +4951,7 @@
         <v>59</v>
       </c>
       <c r="C102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D102" t="s">
         <v>27</v>
@@ -4948,7 +4966,7 @@
         <v>-15000</v>
       </c>
       <c r="H102">
-        <v>19676.5</v>
+        <v>68176.5</v>
       </c>
       <c r="I102">
         <v>-197607.1</v>
@@ -4957,13 +4975,13 @@
         <v>15000</v>
       </c>
       <c r="K102">
-        <v>19676.5</v>
+        <v>68176.5</v>
       </c>
       <c r="L102">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="M102">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="N102" t="s">
         <v>3</v>
@@ -4977,7 +4995,7 @@
         <v>59</v>
       </c>
       <c r="C103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D103" t="s">
         <v>27</v>
@@ -4986,28 +5004,28 @@
         <v>3</v>
       </c>
       <c r="F103">
-        <v>-215571.4</v>
+        <v>-197607.1</v>
       </c>
       <c r="G103">
         <v>-15000</v>
       </c>
       <c r="H103">
-        <v>50642.9</v>
+        <v>18303.1</v>
       </c>
       <c r="I103">
-        <v>-215571.4</v>
+        <v>-197607.1</v>
       </c>
       <c r="J103">
         <v>15000</v>
       </c>
       <c r="K103">
-        <v>50642.9</v>
+        <v>18303.1</v>
       </c>
       <c r="L103">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="M103">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="N103" t="s">
         <v>3</v>
@@ -5021,7 +5039,7 @@
         <v>59</v>
       </c>
       <c r="C104" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D104" t="s">
         <v>27</v>
@@ -5036,7 +5054,7 @@
         <v>-15000</v>
       </c>
       <c r="H104">
-        <v>9316.3</v>
+        <v>53155.2</v>
       </c>
       <c r="I104">
         <v>-215571.4</v>
@@ -5045,13 +5063,13 @@
         <v>15000</v>
       </c>
       <c r="K104">
-        <v>9316.3</v>
+        <v>53155.2</v>
       </c>
       <c r="L104">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="M104">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="N104" t="s">
         <v>3</v>
@@ -5065,7 +5083,7 @@
         <v>59</v>
       </c>
       <c r="C105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D105" t="s">
         <v>27</v>
@@ -5074,28 +5092,28 @@
         <v>3</v>
       </c>
       <c r="F105">
-        <v>-233535.7</v>
+        <v>-215571.4</v>
       </c>
       <c r="G105">
         <v>-15000</v>
       </c>
       <c r="H105">
-        <v>30347.7</v>
+        <v>6804</v>
       </c>
       <c r="I105">
-        <v>-233535.7</v>
+        <v>-215571.4</v>
       </c>
       <c r="J105">
         <v>15000</v>
       </c>
       <c r="K105">
-        <v>30347.7</v>
+        <v>6804</v>
       </c>
       <c r="L105">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="M105">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="N105" t="s">
         <v>3</v>
@@ -5109,7 +5127,7 @@
         <v>59</v>
       </c>
       <c r="C106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D106" t="s">
         <v>27</v>
@@ -5124,7 +5142,7 @@
         <v>-15000</v>
       </c>
       <c r="H106">
-        <v>785</v>
+        <v>-1691</v>
       </c>
       <c r="I106">
         <v>-233535.7</v>
@@ -5133,7 +5151,7 @@
         <v>15000</v>
       </c>
       <c r="K106">
-        <v>785</v>
+        <v>-1691</v>
       </c>
       <c r="L106">
         <v>3000</v>
@@ -5153,7 +5171,7 @@
         <v>59</v>
       </c>
       <c r="C107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D107" t="s">
         <v>27</v>
@@ -5197,7 +5215,7 @@
         <v>59</v>
       </c>
       <c r="C108" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D108" t="s">
         <v>27</v>
@@ -5241,7 +5259,7 @@
         <v>59</v>
       </c>
       <c r="C109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D109" t="s">
         <v>28</v>
@@ -5256,7 +5274,7 @@
         <v>-15000</v>
       </c>
       <c r="H109">
-        <v>119395.9</v>
+        <v>119399.6</v>
       </c>
       <c r="I109">
         <v>-17964.3</v>
@@ -5265,7 +5283,7 @@
         <v>15000</v>
       </c>
       <c r="K109">
-        <v>120676.5</v>
+        <v>119003.7</v>
       </c>
       <c r="L109">
         <v>2913.9</v>
@@ -5285,7 +5303,7 @@
         <v>59</v>
       </c>
       <c r="C110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D110" t="s">
         <v>28</v>
@@ -5300,7 +5318,7 @@
         <v>15000</v>
       </c>
       <c r="H110">
-        <v>120676.5</v>
+        <v>119003.7</v>
       </c>
       <c r="I110">
         <v>-35928.6</v>
@@ -5309,7 +5327,7 @@
         <v>-15000</v>
       </c>
       <c r="K110">
-        <v>120805.5</v>
+        <v>117819</v>
       </c>
       <c r="L110">
         <v>2913.9</v>
@@ -5329,7 +5347,7 @@
         <v>59</v>
       </c>
       <c r="C111" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D111" t="s">
         <v>28</v>
@@ -5344,7 +5362,7 @@
         <v>-15000</v>
       </c>
       <c r="H111">
-        <v>120805.5</v>
+        <v>117819</v>
       </c>
       <c r="I111">
         <v>-53892.9</v>
@@ -5353,7 +5371,7 @@
         <v>15000</v>
       </c>
       <c r="K111">
-        <v>119769.9</v>
+        <v>115845</v>
       </c>
       <c r="L111">
         <v>2913.9</v>
@@ -5373,7 +5391,7 @@
         <v>59</v>
       </c>
       <c r="C112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D112" t="s">
         <v>28</v>
@@ -5388,7 +5406,7 @@
         <v>15000</v>
       </c>
       <c r="H112">
-        <v>119769.9</v>
+        <v>115845</v>
       </c>
       <c r="I112">
         <v>-71857.1</v>
@@ -5397,7 +5415,7 @@
         <v>-15000</v>
       </c>
       <c r="K112">
-        <v>117570</v>
+        <v>113079.2</v>
       </c>
       <c r="L112">
         <v>2913.9</v>
@@ -5417,7 +5435,7 @@
         <v>59</v>
       </c>
       <c r="C113" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D113" t="s">
         <v>28</v>
@@ -5432,7 +5450,7 @@
         <v>-15000</v>
       </c>
       <c r="H113">
-        <v>117570</v>
+        <v>113079.2</v>
       </c>
       <c r="I113">
         <v>-89821.4</v>
@@ -5441,7 +5459,7 @@
         <v>15000</v>
       </c>
       <c r="K113">
-        <v>114193.2</v>
+        <v>109513</v>
       </c>
       <c r="L113">
         <v>2913.9</v>
@@ -5461,7 +5479,7 @@
         <v>59</v>
       </c>
       <c r="C114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D114" t="s">
         <v>28</v>
@@ -5476,7 +5494,7 @@
         <v>15000</v>
       </c>
       <c r="H114">
-        <v>114193.2</v>
+        <v>109513</v>
       </c>
       <c r="I114">
         <v>-107785.7</v>
@@ -5485,7 +5503,7 @@
         <v>-15000</v>
       </c>
       <c r="K114">
-        <v>109609.1</v>
+        <v>105121.4</v>
       </c>
       <c r="L114">
         <v>2913.9</v>
@@ -5505,7 +5523,7 @@
         <v>59</v>
       </c>
       <c r="C115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D115" t="s">
         <v>28</v>
@@ -5520,7 +5538,7 @@
         <v>-15000</v>
       </c>
       <c r="H115">
-        <v>109609.1</v>
+        <v>105121.4</v>
       </c>
       <c r="I115">
         <v>-125750</v>
@@ -5529,7 +5547,7 @@
         <v>15000</v>
       </c>
       <c r="K115">
-        <v>103753.2</v>
+        <v>99845.1</v>
       </c>
       <c r="L115">
         <v>2913.9</v>
@@ -5549,7 +5567,7 @@
         <v>59</v>
       </c>
       <c r="C116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D116" t="s">
         <v>28</v>
@@ -5564,7 +5582,7 @@
         <v>15000</v>
       </c>
       <c r="H116">
-        <v>103753.2</v>
+        <v>99845.1</v>
       </c>
       <c r="I116">
         <v>-143714.3</v>
@@ -5573,7 +5591,7 @@
         <v>-15000</v>
       </c>
       <c r="K116">
-        <v>96504.9</v>
+        <v>93558</v>
       </c>
       <c r="L116">
         <v>2913.9</v>
@@ -5593,7 +5611,7 @@
         <v>59</v>
       </c>
       <c r="C117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D117" t="s">
         <v>28</v>
@@ -5608,7 +5626,7 @@
         <v>-15000</v>
       </c>
       <c r="H117">
-        <v>96504.9</v>
+        <v>93558</v>
       </c>
       <c r="I117">
         <v>-161678.6</v>
@@ -5617,7 +5635,7 @@
         <v>15000</v>
       </c>
       <c r="K117">
-        <v>87657.3</v>
+        <v>86016</v>
       </c>
       <c r="L117">
         <v>2913.9</v>
@@ -5637,7 +5655,7 @@
         <v>59</v>
       </c>
       <c r="C118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D118" t="s">
         <v>28</v>
@@ -5652,7 +5670,7 @@
         <v>15000</v>
       </c>
       <c r="H118">
-        <v>87657.3</v>
+        <v>86016</v>
       </c>
       <c r="I118">
         <v>-179642.9</v>
@@ -5661,7 +5679,7 @@
         <v>-15000</v>
       </c>
       <c r="K118">
-        <v>76876.5</v>
+        <v>76777.5</v>
       </c>
       <c r="L118">
         <v>2913.9</v>
@@ -5681,7 +5699,7 @@
         <v>59</v>
       </c>
       <c r="C119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D119" t="s">
         <v>28</v>
@@ -5696,7 +5714,7 @@
         <v>-15000</v>
       </c>
       <c r="H119">
-        <v>76876.5</v>
+        <v>76777.5</v>
       </c>
       <c r="I119">
         <v>-197607.1</v>
@@ -5705,7 +5723,7 @@
         <v>15000</v>
       </c>
       <c r="K119">
-        <v>63651</v>
+        <v>65090.8</v>
       </c>
       <c r="L119">
         <v>2913.9</v>
@@ -5725,7 +5743,7 @@
         <v>59</v>
       </c>
       <c r="C120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D120" t="s">
         <v>28</v>
@@ -5740,7 +5758,7 @@
         <v>15000</v>
       </c>
       <c r="H120">
-        <v>63651</v>
+        <v>65090.8</v>
       </c>
       <c r="I120">
         <v>-215571.4</v>
@@ -5749,7 +5767,7 @@
         <v>-15000</v>
       </c>
       <c r="K120">
-        <v>47228.9</v>
+        <v>49738.8</v>
       </c>
       <c r="L120">
         <v>2913.9</v>
@@ -5769,7 +5787,7 @@
         <v>59</v>
       </c>
       <c r="C121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D121" t="s">
         <v>28</v>
@@ -5784,7 +5802,7 @@
         <v>15000</v>
       </c>
       <c r="H121">
-        <v>26544.2</v>
+        <v>28836.4</v>
       </c>
       <c r="I121">
         <v>-251500</v>
@@ -5793,7 +5811,7 @@
         <v>-15000</v>
       </c>
       <c r="K121">
-        <v>696.5</v>
+        <v>512.7</v>
       </c>
       <c r="L121">
         <v>2913.9</v>
@@ -5813,7 +5831,7 @@
         <v>59</v>
       </c>
       <c r="C122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D122" t="s">
         <v>30</v>
@@ -5828,7 +5846,7 @@
         <v>-15000</v>
       </c>
       <c r="H122">
-        <v>101566.3</v>
+        <v>103239.8</v>
       </c>
       <c r="I122">
         <v>-17964.3</v>
@@ -5840,7 +5858,7 @@
         <v>35950</v>
       </c>
       <c r="L122">
-        <v>2223.4</v>
+        <v>2170.8</v>
       </c>
       <c r="M122">
         <v>100</v>
@@ -5857,7 +5875,7 @@
         <v>59</v>
       </c>
       <c r="C123" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D123" t="s">
         <v>30</v>
@@ -5872,7 +5890,7 @@
         <v>15000</v>
       </c>
       <c r="H123">
-        <v>101566.3</v>
+        <v>103239.8</v>
       </c>
       <c r="I123">
         <v>-17964.3</v>
@@ -5884,7 +5902,7 @@
         <v>35950</v>
       </c>
       <c r="L123">
-        <v>2223.4</v>
+        <v>2170.8</v>
       </c>
       <c r="M123">
         <v>100</v>
@@ -5901,7 +5919,7 @@
         <v>59</v>
       </c>
       <c r="C124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D124" t="s">
         <v>30</v>
@@ -5916,7 +5934,7 @@
         <v>-15000</v>
       </c>
       <c r="H124">
-        <v>97979.7</v>
+        <v>100959.2</v>
       </c>
       <c r="I124">
         <v>-35928.6</v>
@@ -5928,7 +5946,7 @@
         <v>35950</v>
       </c>
       <c r="L124">
-        <v>2276.9</v>
+        <v>2232.8</v>
       </c>
       <c r="M124">
         <v>100</v>
@@ -5945,7 +5963,7 @@
         <v>59</v>
       </c>
       <c r="C125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D125" t="s">
         <v>30</v>
@@ -5960,7 +5978,7 @@
         <v>15000</v>
       </c>
       <c r="H125">
-        <v>97979.7</v>
+        <v>100959.2</v>
       </c>
       <c r="I125">
         <v>-35928.6</v>
@@ -5972,7 +5990,7 @@
         <v>35950</v>
       </c>
       <c r="L125">
-        <v>2276.9</v>
+        <v>2232.8</v>
       </c>
       <c r="M125">
         <v>100</v>
@@ -5989,7 +6007,7 @@
         <v>59</v>
       </c>
       <c r="C126" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D126" t="s">
         <v>30</v>
@@ -6004,7 +6022,7 @@
         <v>-15000</v>
       </c>
       <c r="H126">
-        <v>93240.8</v>
+        <v>97158.8</v>
       </c>
       <c r="I126">
         <v>-53892.9</v>
@@ -6016,7 +6034,7 @@
         <v>35950</v>
       </c>
       <c r="L126">
-        <v>2336.4</v>
+        <v>2306.1</v>
       </c>
       <c r="M126">
         <v>100</v>
@@ -6033,7 +6051,7 @@
         <v>59</v>
       </c>
       <c r="C127" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D127" t="s">
         <v>30</v>
@@ -6048,7 +6066,7 @@
         <v>15000</v>
       </c>
       <c r="H127">
-        <v>93240.8</v>
+        <v>97158.8</v>
       </c>
       <c r="I127">
         <v>-53892.9</v>
@@ -6060,7 +6078,7 @@
         <v>35950</v>
       </c>
       <c r="L127">
-        <v>2336.4</v>
+        <v>2306.1</v>
       </c>
       <c r="M127">
         <v>100</v>
@@ -6077,7 +6095,7 @@
         <v>59</v>
       </c>
       <c r="C128" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D128" t="s">
         <v>30</v>
@@ -6092,7 +6110,7 @@
         <v>-15000</v>
       </c>
       <c r="H128">
-        <v>87353.4</v>
+        <v>91840.8</v>
       </c>
       <c r="I128">
         <v>-71857.1</v>
@@ -6104,7 +6122,7 @@
         <v>35950</v>
       </c>
       <c r="L128">
-        <v>2401.3</v>
+        <v>2389.6</v>
       </c>
       <c r="M128">
         <v>100</v>
@@ -6121,7 +6139,7 @@
         <v>59</v>
       </c>
       <c r="C129" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D129" t="s">
         <v>30</v>
@@ -6136,7 +6154,7 @@
         <v>15000</v>
       </c>
       <c r="H129">
-        <v>87353.4</v>
+        <v>91840.8</v>
       </c>
       <c r="I129">
         <v>-71857.1</v>
@@ -6148,7 +6166,7 @@
         <v>35950</v>
       </c>
       <c r="L129">
-        <v>2401.3</v>
+        <v>2389.6</v>
       </c>
       <c r="M129">
         <v>100</v>
@@ -6165,7 +6183,7 @@
         <v>59</v>
       </c>
       <c r="C130" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D130" t="s">
         <v>30</v>
@@ -6180,7 +6198,7 @@
         <v>-15000</v>
       </c>
       <c r="H130">
-        <v>80329.6</v>
+        <v>85013.8</v>
       </c>
       <c r="I130">
         <v>-89821.4</v>
@@ -6192,7 +6210,7 @@
         <v>35950</v>
       </c>
       <c r="L130">
-        <v>2469.7</v>
+        <v>2481.4</v>
       </c>
       <c r="M130">
         <v>100</v>
@@ -6209,7 +6227,7 @@
         <v>59</v>
       </c>
       <c r="C131" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D131" t="s">
         <v>30</v>
@@ -6224,7 +6242,7 @@
         <v>15000</v>
       </c>
       <c r="H131">
-        <v>80329.6</v>
+        <v>85013.8</v>
       </c>
       <c r="I131">
         <v>-89821.4</v>
@@ -6236,7 +6254,7 @@
         <v>35950</v>
       </c>
       <c r="L131">
-        <v>2469.7</v>
+        <v>2481.4</v>
       </c>
       <c r="M131">
         <v>100</v>
@@ -6253,7 +6271,7 @@
         <v>59</v>
       </c>
       <c r="C132" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D132" t="s">
         <v>30</v>
@@ -6268,7 +6286,7 @@
         <v>-15000</v>
       </c>
       <c r="H132">
-        <v>72199</v>
+        <v>76701.5</v>
       </c>
       <c r="I132">
         <v>-107785.7</v>
@@ -6280,7 +6298,7 @@
         <v>35950</v>
       </c>
       <c r="L132">
-        <v>2538.8</v>
+        <v>2577.8</v>
       </c>
       <c r="M132">
         <v>100</v>
@@ -6297,7 +6315,7 @@
         <v>59</v>
       </c>
       <c r="C133" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D133" t="s">
         <v>30</v>
@@ -6312,7 +6330,7 @@
         <v>15000</v>
       </c>
       <c r="H133">
-        <v>72199</v>
+        <v>76701.5</v>
       </c>
       <c r="I133">
         <v>-107785.7</v>
@@ -6324,7 +6342,7 @@
         <v>35950</v>
       </c>
       <c r="L133">
-        <v>2538.8</v>
+        <v>2577.8</v>
       </c>
       <c r="M133">
         <v>100</v>
@@ -6341,7 +6359,7 @@
         <v>59</v>
       </c>
       <c r="C134" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D134" t="s">
         <v>30</v>
@@ -6356,7 +6374,7 @@
         <v>-15000</v>
       </c>
       <c r="H134">
-        <v>63023.4</v>
+        <v>66960.9</v>
       </c>
       <c r="I134">
         <v>-125750</v>
@@ -6368,7 +6386,7 @@
         <v>35950</v>
       </c>
       <c r="L134">
-        <v>2603.6</v>
+        <v>2672.5</v>
       </c>
       <c r="M134">
         <v>100</v>
@@ -6385,7 +6403,7 @@
         <v>59</v>
       </c>
       <c r="C135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D135" t="s">
         <v>30</v>
@@ -6400,7 +6418,7 @@
         <v>15000</v>
       </c>
       <c r="H135">
-        <v>63023.4</v>
+        <v>66960.9</v>
       </c>
       <c r="I135">
         <v>-125750</v>
@@ -6412,7 +6430,7 @@
         <v>35950</v>
       </c>
       <c r="L135">
-        <v>2603.6</v>
+        <v>2672.5</v>
       </c>
       <c r="M135">
         <v>100</v>
@@ -6429,7 +6447,7 @@
         <v>59</v>
       </c>
       <c r="C136" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D136" t="s">
         <v>30</v>
@@ -6444,7 +6462,7 @@
         <v>-15000</v>
       </c>
       <c r="H136">
-        <v>52918.8</v>
+        <v>55912.9</v>
       </c>
       <c r="I136">
         <v>-143714.3</v>
@@ -6456,7 +6474,7 @@
         <v>35950</v>
       </c>
       <c r="L136">
-        <v>2656.7</v>
+        <v>2754.5</v>
       </c>
       <c r="M136">
         <v>100</v>
@@ -6473,7 +6491,7 @@
         <v>59</v>
       </c>
       <c r="C137" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D137" t="s">
         <v>30</v>
@@ -6488,7 +6506,7 @@
         <v>15000</v>
       </c>
       <c r="H137">
-        <v>52918.8</v>
+        <v>55912.9</v>
       </c>
       <c r="I137">
         <v>-143714.3</v>
@@ -6500,7 +6518,7 @@
         <v>35950</v>
       </c>
       <c r="L137">
-        <v>2656.7</v>
+        <v>2754.5</v>
       </c>
       <c r="M137">
         <v>100</v>
@@ -6517,7 +6535,7 @@
         <v>59</v>
       </c>
       <c r="C138" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D138" t="s">
         <v>30</v>
@@ -6532,7 +6550,7 @@
         <v>-15000</v>
       </c>
       <c r="H138">
-        <v>42084.1</v>
+        <v>43791.2</v>
       </c>
       <c r="I138">
         <v>-161678.6</v>
@@ -6544,7 +6562,7 @@
         <v>35950</v>
       </c>
       <c r="L138">
-        <v>2687.2</v>
+        <v>2806</v>
       </c>
       <c r="M138">
         <v>100</v>
@@ -6561,7 +6579,7 @@
         <v>59</v>
       </c>
       <c r="C139" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D139" t="s">
         <v>30</v>
@@ -6576,7 +6594,7 @@
         <v>15000</v>
       </c>
       <c r="H139">
-        <v>42084.1</v>
+        <v>43791.2</v>
       </c>
       <c r="I139">
         <v>-161678.6</v>
@@ -6588,7 +6606,7 @@
         <v>35950</v>
       </c>
       <c r="L139">
-        <v>2687.2</v>
+        <v>2806</v>
       </c>
       <c r="M139">
         <v>100</v>
@@ -6605,7 +6623,7 @@
         <v>59</v>
       </c>
       <c r="C140" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D140" t="s">
         <v>31</v>
@@ -6620,7 +6638,7 @@
         <v>-15000</v>
       </c>
       <c r="H140">
-        <v>19676.5</v>
+        <v>18303.1</v>
       </c>
       <c r="I140">
         <v>-197607.1</v>
@@ -6632,7 +6650,7 @@
         <v>33550</v>
       </c>
       <c r="L140">
-        <v>2836.5</v>
+        <v>2978.1</v>
       </c>
       <c r="M140">
         <v>100</v>
@@ -6649,7 +6667,7 @@
         <v>59</v>
       </c>
       <c r="C141" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D141" t="s">
         <v>31</v>
@@ -6664,7 +6682,7 @@
         <v>15000</v>
       </c>
       <c r="H141">
-        <v>19676.5</v>
+        <v>18303.1</v>
       </c>
       <c r="I141">
         <v>-197607.1</v>
@@ -6676,7 +6694,7 @@
         <v>33550</v>
       </c>
       <c r="L141">
-        <v>2836.5</v>
+        <v>2978.1</v>
       </c>
       <c r="M141">
         <v>100</v>
@@ -6693,7 +6711,7 @@
         <v>59</v>
       </c>
       <c r="C142" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D142" t="s">
         <v>31</v>
@@ -6708,7 +6726,7 @@
         <v>-15000</v>
       </c>
       <c r="H142">
-        <v>9316.3</v>
+        <v>6804</v>
       </c>
       <c r="I142">
         <v>-215571.4</v>
@@ -6720,7 +6738,7 @@
         <v>33550</v>
       </c>
       <c r="L142">
-        <v>2766.1</v>
+        <v>2866.5</v>
       </c>
       <c r="M142">
         <v>100</v>
@@ -6737,7 +6755,7 @@
         <v>59</v>
       </c>
       <c r="C143" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D143" t="s">
         <v>31</v>
@@ -6752,7 +6770,7 @@
         <v>15000</v>
       </c>
       <c r="H143">
-        <v>9316.3</v>
+        <v>6804</v>
       </c>
       <c r="I143">
         <v>-215571.4</v>
@@ -6764,7 +6782,7 @@
         <v>33550</v>
       </c>
       <c r="L143">
-        <v>2766.1</v>
+        <v>2866.5</v>
       </c>
       <c r="M143">
         <v>100</v>
@@ -6781,7 +6799,7 @@
         <v>59</v>
       </c>
       <c r="C144" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D144" t="s">
         <v>31</v>
@@ -6808,7 +6826,7 @@
         <v>33550</v>
       </c>
       <c r="L144">
-        <v>4210.7</v>
+        <v>4490.9</v>
       </c>
       <c r="M144">
         <v>100</v>
@@ -6825,7 +6843,7 @@
         <v>59</v>
       </c>
       <c r="C145" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D145" t="s">
         <v>31</v>
@@ -6852,7 +6870,7 @@
         <v>33550</v>
       </c>
       <c r="L145">
-        <v>4210.7</v>
+        <v>4490.9</v>
       </c>
       <c r="M145">
         <v>100</v>
@@ -6919,13 +6937,13 @@
         <v>59</v>
       </c>
       <c r="C147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D147" t="s">
         <v>68</v>
       </c>
       <c r="E147" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F147" t="s">
         <v>22</v>
@@ -6939,12 +6957,12 @@
         <v>40</v>
       </c>
       <c r="C149" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>43</v>
@@ -7006,7 +7024,7 @@
         <v>59</v>
       </c>
       <c r="C151" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D151" t="s">
         <v>25</v>
@@ -7033,10 +7051,10 @@
         <v>122000</v>
       </c>
       <c r="L151">
-        <v>2223.9</v>
+        <v>2135.4</v>
       </c>
       <c r="M151">
-        <v>2061.1</v>
+        <v>2017.9</v>
       </c>
       <c r="N151" t="s">
         <v>3</v>
@@ -7050,7 +7068,7 @@
         <v>59</v>
       </c>
       <c r="C152" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D152" t="s">
         <v>25</v>
@@ -7077,10 +7095,10 @@
         <v>122000</v>
       </c>
       <c r="L152">
-        <v>2223.9</v>
+        <v>2135.4</v>
       </c>
       <c r="M152">
-        <v>2061.1</v>
+        <v>2017.9</v>
       </c>
       <c r="N152" t="s">
         <v>3</v>
@@ -7094,7 +7112,7 @@
         <v>59</v>
       </c>
       <c r="C153" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D153" t="s">
         <v>27</v>
@@ -7138,7 +7156,7 @@
         <v>59</v>
       </c>
       <c r="C154" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D154" t="s">
         <v>27</v>
@@ -7182,7 +7200,7 @@
         <v>59</v>
       </c>
       <c r="C155" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D155" t="s">
         <v>30</v>
@@ -7209,7 +7227,7 @@
         <v>35950</v>
       </c>
       <c r="L155">
-        <v>2176.5</v>
+        <v>2120.6</v>
       </c>
       <c r="M155">
         <v>100</v>
@@ -7226,7 +7244,7 @@
         <v>59</v>
       </c>
       <c r="C156" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D156" t="s">
         <v>30</v>
@@ -7253,7 +7271,7 @@
         <v>35950</v>
       </c>
       <c r="L156">
-        <v>2176.5</v>
+        <v>2120.6</v>
       </c>
       <c r="M156">
         <v>100</v>
@@ -7320,13 +7338,13 @@
         <v>59</v>
       </c>
       <c r="C158" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D158" t="s">
         <v>68</v>
       </c>
       <c r="E158" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="F158" t="s">
         <v>22</v>
@@ -7340,12 +7358,12 @@
         <v>40</v>
       </c>
       <c r="C160" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>43</v>
@@ -7407,7 +7425,7 @@
         <v>59</v>
       </c>
       <c r="C162" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D162" t="s">
         <v>33</v>
@@ -7451,7 +7469,7 @@
         <v>59</v>
       </c>
       <c r="C163" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D163" t="s">
         <v>33</v>
@@ -7495,7 +7513,7 @@
         <v>59</v>
       </c>
       <c r="C164" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D164" t="s">
         <v>33</v>
@@ -7539,7 +7557,7 @@
         <v>59</v>
       </c>
       <c r="C165" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D165" t="s">
         <v>35</v>
@@ -7583,7 +7601,7 @@
         <v>59</v>
       </c>
       <c r="C166" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D166" t="s">
         <v>35</v>
@@ -7627,7 +7645,7 @@
         <v>59</v>
       </c>
       <c r="C167" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D167" t="s">
         <v>35</v>
@@ -7671,7 +7689,7 @@
         <v>59</v>
       </c>
       <c r="C168" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D168" t="s">
         <v>35</v>
@@ -7715,7 +7733,7 @@
         <v>59</v>
       </c>
       <c r="C169" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D169" t="s">
         <v>35</v>
@@ -7759,7 +7777,7 @@
         <v>59</v>
       </c>
       <c r="C170" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D170" t="s">
         <v>35</v>
@@ -7803,7 +7821,7 @@
         <v>59</v>
       </c>
       <c r="C171" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D171" t="s">
         <v>35</v>
@@ -7847,7 +7865,7 @@
         <v>59</v>
       </c>
       <c r="C172" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D172" t="s">
         <v>35</v>
@@ -7891,7 +7909,7 @@
         <v>59</v>
       </c>
       <c r="C173" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D173" t="s">
         <v>35</v>
@@ -7985,13 +8003,13 @@
         <v>59</v>
       </c>
       <c r="C175" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D175" t="s">
         <v>68</v>
       </c>
       <c r="E175" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F175" t="s">
         <v>22</v>
@@ -8005,7 +8023,7 @@
         <v>40</v>
       </c>
       <c r="C177" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="178" spans="1:18" x14ac:dyDescent="0.25">
@@ -8072,7 +8090,7 @@
         <v>59</v>
       </c>
       <c r="C179" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D179" t="s">
         <v>36</v>
@@ -8116,7 +8134,7 @@
         <v>59</v>
       </c>
       <c r="C180" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D180" t="s">
         <v>36</v>
@@ -8160,7 +8178,7 @@
         <v>59</v>
       </c>
       <c r="C181" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D181" t="s">
         <v>36</v>
@@ -8204,7 +8222,7 @@
         <v>59</v>
       </c>
       <c r="C182" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D182" t="s">
         <v>36</v>
@@ -8248,7 +8266,7 @@
         <v>59</v>
       </c>
       <c r="C183" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D183" t="s">
         <v>37</v>
@@ -8292,7 +8310,7 @@
         <v>59</v>
       </c>
       <c r="C184" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D184" t="s">
         <v>37</v>
@@ -8336,7 +8354,7 @@
         <v>59</v>
       </c>
       <c r="C185" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D185" t="s">
         <v>37</v>
@@ -8380,7 +8398,7 @@
         <v>59</v>
       </c>
       <c r="C186" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D186" t="s">
         <v>37</v>
@@ -8424,7 +8442,7 @@
         <v>59</v>
       </c>
       <c r="C187" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D187" t="s">
         <v>37</v>
@@ -8468,7 +8486,7 @@
         <v>59</v>
       </c>
       <c r="C188" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D188" t="s">
         <v>37</v>
@@ -8512,7 +8530,7 @@
         <v>59</v>
       </c>
       <c r="C189" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D189" t="s">
         <v>37</v>
@@ -8556,7 +8574,7 @@
         <v>59</v>
       </c>
       <c r="C190" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D190" t="s">
         <v>37</v>
@@ -8600,7 +8618,7 @@
         <v>59</v>
       </c>
       <c r="C191" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D191" t="s">
         <v>37</v>
@@ -8644,7 +8662,7 @@
         <v>59</v>
       </c>
       <c r="C192" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D192" t="s">
         <v>37</v>
@@ -8688,7 +8706,7 @@
         <v>59</v>
       </c>
       <c r="C193" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D193" t="s">
         <v>37</v>
@@ -8732,7 +8750,7 @@
         <v>59</v>
       </c>
       <c r="C194" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D194" t="s">
         <v>37</v>
@@ -8776,7 +8794,7 @@
         <v>59</v>
       </c>
       <c r="C195" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D195" t="s">
         <v>37</v>
@@ -8820,7 +8838,7 @@
         <v>59</v>
       </c>
       <c r="C196" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D196" t="s">
         <v>37</v>
@@ -8864,7 +8882,7 @@
         <v>59</v>
       </c>
       <c r="C197" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D197" t="s">
         <v>37</v>
@@ -8908,7 +8926,7 @@
         <v>59</v>
       </c>
       <c r="C198" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D198" t="s">
         <v>37</v>
@@ -8952,7 +8970,7 @@
         <v>59</v>
       </c>
       <c r="C199" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D199" t="s">
         <v>37</v>
@@ -8996,7 +9014,7 @@
         <v>59</v>
       </c>
       <c r="C200" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D200" t="s">
         <v>37</v>
@@ -9040,7 +9058,7 @@
         <v>59</v>
       </c>
       <c r="C201" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D201" t="s">
         <v>37</v>
@@ -9084,7 +9102,7 @@
         <v>59</v>
       </c>
       <c r="C202" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D202" t="s">
         <v>37</v>
@@ -9128,7 +9146,7 @@
         <v>59</v>
       </c>
       <c r="C203" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D203" t="s">
         <v>37</v>
@@ -9172,7 +9190,7 @@
         <v>59</v>
       </c>
       <c r="C204" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D204" t="s">
         <v>37</v>
@@ -9216,7 +9234,7 @@
         <v>59</v>
       </c>
       <c r="C205" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D205" t="s">
         <v>37</v>
@@ -9260,7 +9278,7 @@
         <v>59</v>
       </c>
       <c r="C206" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D206" t="s">
         <v>37</v>
@@ -9354,13 +9372,13 @@
         <v>59</v>
       </c>
       <c r="C208" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D208" t="s">
         <v>68</v>
       </c>
       <c r="E208" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F208" t="s">
         <v>22</v>
@@ -9374,7 +9392,7 @@
         <v>40</v>
       </c>
       <c r="C210" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="211" spans="1:18" x14ac:dyDescent="0.25">
@@ -9441,7 +9459,7 @@
         <v>59</v>
       </c>
       <c r="C212" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D212" t="s">
         <v>38</v>
@@ -9485,7 +9503,7 @@
         <v>59</v>
       </c>
       <c r="C213" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D213" t="s">
         <v>38</v>
@@ -9529,7 +9547,7 @@
         <v>59</v>
       </c>
       <c r="C214" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D214" t="s">
         <v>38</v>
@@ -9573,7 +9591,7 @@
         <v>59</v>
       </c>
       <c r="C215" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D215" t="s">
         <v>38</v>
@@ -9617,7 +9635,7 @@
         <v>59</v>
       </c>
       <c r="C216" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D216" t="s">
         <v>39</v>
@@ -9661,7 +9679,7 @@
         <v>59</v>
       </c>
       <c r="C217" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D217" t="s">
         <v>39</v>
@@ -9705,7 +9723,7 @@
         <v>59</v>
       </c>
       <c r="C218" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D218" t="s">
         <v>39</v>
@@ -9749,7 +9767,7 @@
         <v>59</v>
       </c>
       <c r="C219" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D219" t="s">
         <v>39</v>
@@ -9793,7 +9811,7 @@
         <v>59</v>
       </c>
       <c r="C220" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D220" t="s">
         <v>39</v>
@@ -9837,7 +9855,7 @@
         <v>59</v>
       </c>
       <c r="C221" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D221" t="s">
         <v>39</v>
@@ -9881,7 +9899,7 @@
         <v>59</v>
       </c>
       <c r="C222" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D222" t="s">
         <v>39</v>
@@ -9925,7 +9943,7 @@
         <v>59</v>
       </c>
       <c r="C223" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D223" t="s">
         <v>39</v>
@@ -10019,13 +10037,13 @@
         <v>59</v>
       </c>
       <c r="C225" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D225" t="s">
         <v>68</v>
       </c>
       <c r="E225" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="F225" t="s">
         <v>22</v>
@@ -10033,28 +10051,28 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C227" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D227" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E227" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F227" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G227" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H227" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -10062,13 +10080,13 @@
         <v>3</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C228" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D228" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E228" t="s">
         <v>3</v>
@@ -10080,7 +10098,7 @@
         <v>2000</v>
       </c>
       <c r="H228" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -10088,13 +10106,13 @@
         <v>3</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C229" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D229" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E229" t="s">
         <v>3</v>
@@ -10106,7 +10124,7 @@
         <v>2000</v>
       </c>
       <c r="H229" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
@@ -10114,13 +10132,13 @@
         <v>3</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C230" t="s">
         <v>60</v>
       </c>
       <c r="D230" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E230" t="s">
         <v>3</v>
@@ -10132,7 +10150,7 @@
         <v>1000</v>
       </c>
       <c r="H230" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
@@ -10140,13 +10158,13 @@
         <v>3</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C231" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D231" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E231" t="s">
         <v>3</v>
@@ -10158,7 +10176,7 @@
         <v>1000</v>
       </c>
       <c r="H231" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
@@ -10166,13 +10184,13 @@
         <v>3</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C232" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D232" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E232" t="s">
         <v>3</v>
@@ -10184,7 +10202,7 @@
         <v>1000</v>
       </c>
       <c r="H232" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
@@ -10192,13 +10210,13 @@
         <v>3</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C233" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D233" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E233" t="s">
         <v>3</v>
@@ -10210,7 +10228,7 @@
         <v>100</v>
       </c>
       <c r="H233" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
@@ -10218,13 +10236,13 @@
         <v>3</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C234" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D234" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E234" t="s">
         <v>3</v>
@@ -10236,7 +10254,7 @@
         <v>200</v>
       </c>
       <c r="H234" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
@@ -10244,13 +10262,13 @@
         <v>3</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C235" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D235" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E235" t="s">
         <v>3</v>
@@ -10262,7 +10280,7 @@
         <v>200</v>
       </c>
       <c r="H235" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
@@ -10270,13 +10288,13 @@
         <v>3</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C236" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D236" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E236" t="s">
         <v>3</v>
@@ -10288,33 +10306,33 @@
         <v>200</v>
       </c>
       <c r="H236" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C238" t="s">
         <v>5</v>
       </c>
       <c r="D238" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E238" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F238" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G238" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H238" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I238" t="s">
         <v>64</v>
@@ -10328,7 +10346,7 @@
         <v>40</v>
       </c>
       <c r="C239" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
@@ -10336,16 +10354,16 @@
         <v>3</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C240" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D240" t="s">
         <v>60</v>
       </c>
       <c r="E240" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -10362,16 +10380,16 @@
         <v>3</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C241" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D241" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E241" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F241">
         <v>0</v>
@@ -10383,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="I241" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
@@ -10391,16 +10409,16 @@
         <v>3</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C242" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D242" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E242" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -10412,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="I242" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
@@ -10420,25 +10438,25 @@
         <v>3</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C244" t="s">
         <v>5</v>
       </c>
       <c r="D244" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E244" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F244" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G244" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H244" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I244" t="s">
         <v>64</v>
@@ -10452,7 +10470,7 @@
         <v>40</v>
       </c>
       <c r="C245" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
@@ -10460,16 +10478,16 @@
         <v>3</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C246" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D246" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E246" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F246">
         <v>-17964.3</v>
@@ -10478,7 +10496,7 @@
         <v>-15000</v>
       </c>
       <c r="H246">
-        <v>123280.6</v>
+        <v>121607.1</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -10486,16 +10504,16 @@
         <v>3</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C247" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D247" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E247" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -10507,7 +10525,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
@@ -10515,25 +10533,25 @@
         <v>3</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C249" t="s">
         <v>5</v>
       </c>
       <c r="D249" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E249" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F249" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G249" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H249" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -10544,7 +10562,7 @@
         <v>40</v>
       </c>
       <c r="C250" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
@@ -10552,16 +10570,16 @@
         <v>3</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C251" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D251" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E251" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F251">
         <v>0</v>
@@ -10578,25 +10596,25 @@
         <v>3</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C253" t="s">
         <v>5</v>
       </c>
       <c r="D253" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E253" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F253" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G253" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H253" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I253" t="s">
         <v>58</v>
@@ -10610,7 +10628,7 @@
         <v>40</v>
       </c>
       <c r="C254" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
@@ -10618,16 +10636,16 @@
         <v>3</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C255" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D255" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E255" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F255">
         <v>-574857.1</v>
@@ -10644,16 +10662,16 @@
         <v>3</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C256" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D256" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E256" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F256">
         <v>17964.3</v>
@@ -10673,25 +10691,25 @@
         <v>3</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C258" t="s">
         <v>5</v>
       </c>
       <c r="D258" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E258" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F258" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G258" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H258" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I258" t="s">
         <v>64</v>
@@ -10705,7 +10723,7 @@
         <v>40</v>
       </c>
       <c r="C259" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
@@ -10713,16 +10731,16 @@
         <v>3</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C260" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D260" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E260" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F260">
         <v>-273000</v>
@@ -10739,16 +10757,16 @@
         <v>3</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C261" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D261" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E261" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F261">
         <v>0</v>
@@ -10760,7 +10778,7 @@
         <v>0</v>
       </c>
       <c r="I261" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
@@ -10768,16 +10786,16 @@
         <v>3</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C262" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D262" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E262" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F262">
         <v>0</v>
@@ -10789,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="I262" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
@@ -10797,25 +10815,25 @@
         <v>3</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C264" t="s">
         <v>5</v>
       </c>
       <c r="D264" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E264" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F264" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G264" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H264" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I264" t="s">
         <v>58</v>
@@ -10829,7 +10847,7 @@
         <v>40</v>
       </c>
       <c r="C265" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
@@ -10837,16 +10855,16 @@
         <v>3</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C266" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D266" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E266" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F266">
         <v>-311392.9</v>
@@ -10863,16 +10881,16 @@
         <v>3</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C267" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D267" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E267" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F267">
         <v>-53892.9</v>
@@ -10892,16 +10910,16 @@
         <v>3</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C268" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D268" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E268" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F268">
         <v>0</v>
@@ -10913,7 +10931,7 @@
         <v>0</v>
       </c>
       <c r="I268" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
@@ -10921,7 +10939,7 @@
         <v>3</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_HARBOUR.xlsx
+++ b/plate3d/PLATE3D_HARBOUR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="139">
   <si>
     <t>SYDNEY HARBOUR BRIDGE  ·  503 m arch, 1,149 m overall  ·  mm, Z up</t>
   </si>
@@ -821,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R253"/>
+  <dimension ref="A1:R274"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -3098,7 +3098,7 @@
         <v>258.2</v>
       </c>
       <c r="M58">
-        <v>367.1</v>
+        <v>294.7</v>
       </c>
       <c r="N58" t="s">
         <v>3</v>
@@ -3142,7 +3142,7 @@
         <v>178.8</v>
       </c>
       <c r="M59">
-        <v>177</v>
+        <v>170.5</v>
       </c>
       <c r="N59" t="s">
         <v>3</v>
@@ -3186,7 +3186,7 @@
         <v>3122.6</v>
       </c>
       <c r="M60">
-        <v>3611.1</v>
+        <v>3275.9</v>
       </c>
       <c r="N60" t="s">
         <v>3</v>
@@ -3218,19 +3218,19 @@
         <v>66932</v>
       </c>
       <c r="I61">
-        <v>-233535.7</v>
+        <v>-224553.6</v>
       </c>
       <c r="J61">
         <v>-15000</v>
       </c>
       <c r="K61">
-        <v>48541.2</v>
+        <v>59246.1</v>
       </c>
       <c r="L61">
-        <v>367.1</v>
+        <v>294.7</v>
       </c>
       <c r="M61">
-        <v>422.6</v>
+        <v>282.2</v>
       </c>
       <c r="N61" t="s">
         <v>3</v>
@@ -3262,19 +3262,19 @@
         <v>18107.1</v>
       </c>
       <c r="I62">
-        <v>-233535.7</v>
+        <v>-224553.6</v>
       </c>
       <c r="J62">
         <v>-15000</v>
       </c>
       <c r="K62">
-        <v>4486.1</v>
+        <v>11405.6</v>
       </c>
       <c r="L62">
-        <v>177</v>
+        <v>170.5</v>
       </c>
       <c r="M62">
-        <v>175.4</v>
+        <v>163.1</v>
       </c>
       <c r="N62" t="s">
         <v>3</v>
@@ -3306,19 +3306,19 @@
         <v>18107.1</v>
       </c>
       <c r="I63">
-        <v>-233535.7</v>
+        <v>-224553.6</v>
       </c>
       <c r="J63">
         <v>-17800</v>
       </c>
       <c r="K63">
-        <v>48541.2</v>
+        <v>59246.1</v>
       </c>
       <c r="L63">
-        <v>3215.8</v>
+        <v>3192.5</v>
       </c>
       <c r="M63">
-        <v>6118.2</v>
+        <v>3961.8</v>
       </c>
       <c r="N63" t="s">
         <v>3</v>
@@ -3341,28 +3341,28 @@
         <v>3</v>
       </c>
       <c r="F64">
+        <v>-224553.6</v>
+      </c>
+      <c r="G64">
+        <v>-15000</v>
+      </c>
+      <c r="H64">
+        <v>59246.1</v>
+      </c>
+      <c r="I64">
         <v>-233535.7</v>
       </c>
-      <c r="G64">
-        <v>-15000</v>
-      </c>
-      <c r="H64">
+      <c r="J64">
+        <v>-15000</v>
+      </c>
+      <c r="K64">
         <v>48541.2</v>
       </c>
-      <c r="I64">
-        <v>-251500</v>
-      </c>
-      <c r="J64">
-        <v>-15000</v>
-      </c>
-      <c r="K64">
-        <v>10000</v>
-      </c>
       <c r="L64">
-        <v>422.6</v>
+        <v>282.2</v>
       </c>
       <c r="M64">
-        <v>150</v>
+        <v>264.7</v>
       </c>
       <c r="N64" t="s">
         <v>3</v>
@@ -3385,28 +3385,28 @@
         <v>3</v>
       </c>
       <c r="F65">
+        <v>-224553.6</v>
+      </c>
+      <c r="G65">
+        <v>-15000</v>
+      </c>
+      <c r="H65">
+        <v>11405.6</v>
+      </c>
+      <c r="I65">
         <v>-233535.7</v>
       </c>
-      <c r="G65">
-        <v>-15000</v>
-      </c>
-      <c r="H65">
+      <c r="J65">
+        <v>-15000</v>
+      </c>
+      <c r="K65">
         <v>4486.1</v>
       </c>
-      <c r="I65">
-        <v>-251500</v>
-      </c>
-      <c r="J65">
-        <v>-15000</v>
-      </c>
-      <c r="K65">
-        <v>-10000</v>
-      </c>
       <c r="L65">
-        <v>175.4</v>
+        <v>163.1</v>
       </c>
       <c r="M65">
-        <v>150</v>
+        <v>160.6</v>
       </c>
       <c r="N65" t="s">
         <v>3</v>
@@ -3429,28 +3429,28 @@
         <v>3</v>
       </c>
       <c r="F66">
-        <v>-233535.7</v>
+        <v>-224553.6</v>
       </c>
       <c r="G66">
         <v>-17800</v>
       </c>
       <c r="H66">
-        <v>4486.1</v>
+        <v>11405.6</v>
       </c>
       <c r="I66">
-        <v>-251500</v>
+        <v>-233535.7</v>
       </c>
       <c r="J66">
         <v>-17800</v>
       </c>
       <c r="K66">
-        <v>10000</v>
+        <v>48541.2</v>
       </c>
       <c r="L66">
-        <v>3309.6</v>
+        <v>3239.3</v>
       </c>
       <c r="M66">
-        <v>6118.2</v>
+        <v>4888.3</v>
       </c>
       <c r="N66" t="s">
         <v>3</v>
@@ -3467,34 +3467,34 @@
         <v>65</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E67" t="s">
         <v>3</v>
       </c>
       <c r="F67">
-        <v>-17964.3</v>
+        <v>-233535.7</v>
       </c>
       <c r="G67">
         <v>-15000</v>
       </c>
       <c r="H67">
-        <v>104996.7</v>
+        <v>48541.2</v>
       </c>
       <c r="I67">
-        <v>-17964.3</v>
+        <v>-239523.8</v>
       </c>
       <c r="J67">
         <v>-15000</v>
       </c>
       <c r="K67">
-        <v>121262</v>
+        <v>38882.2</v>
       </c>
       <c r="L67">
-        <v>2227.2</v>
+        <v>264.7</v>
       </c>
       <c r="M67">
-        <v>2082.6</v>
+        <v>237.1</v>
       </c>
       <c r="N67" t="s">
         <v>3</v>
@@ -3511,34 +3511,34 @@
         <v>65</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E68" t="s">
         <v>3</v>
       </c>
       <c r="F68">
-        <v>-35928.6</v>
+        <v>-233535.7</v>
       </c>
       <c r="G68">
         <v>-15000</v>
       </c>
       <c r="H68">
-        <v>102506.3</v>
+        <v>4486.1</v>
       </c>
       <c r="I68">
-        <v>-35928.6</v>
+        <v>-239523.8</v>
       </c>
       <c r="J68">
         <v>-15000</v>
       </c>
       <c r="K68">
-        <v>119567.6</v>
+        <v>-247.1</v>
       </c>
       <c r="L68">
-        <v>2303.9</v>
+        <v>160.6</v>
       </c>
       <c r="M68">
-        <v>2122.7</v>
+        <v>158.3</v>
       </c>
       <c r="N68" t="s">
         <v>3</v>
@@ -3555,34 +3555,34 @@
         <v>65</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E69" t="s">
         <v>3</v>
       </c>
       <c r="F69">
-        <v>-53892.9</v>
+        <v>-233535.7</v>
       </c>
       <c r="G69">
-        <v>-15000</v>
+        <v>-17800</v>
       </c>
       <c r="H69">
-        <v>98751.5</v>
+        <v>4486.1</v>
       </c>
       <c r="I69">
-        <v>-53892.9</v>
+        <v>-239523.8</v>
       </c>
       <c r="J69">
-        <v>-15000</v>
+        <v>-17800</v>
       </c>
       <c r="K69">
-        <v>117139.3</v>
+        <v>38882.2</v>
       </c>
       <c r="L69">
-        <v>2381.5</v>
+        <v>3278.3</v>
       </c>
       <c r="M69">
-        <v>2159.3</v>
+        <v>5989.6</v>
       </c>
       <c r="N69" t="s">
         <v>3</v>
@@ -3599,34 +3599,34 @@
         <v>65</v>
       </c>
       <c r="D70" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E70" t="s">
         <v>3</v>
       </c>
       <c r="F70">
-        <v>-71857.1</v>
+        <v>-239523.8</v>
       </c>
       <c r="G70">
         <v>-15000</v>
       </c>
       <c r="H70">
-        <v>93834.3</v>
+        <v>38882.2</v>
       </c>
       <c r="I70">
-        <v>-71857.1</v>
+        <v>-245511.9</v>
       </c>
       <c r="J70">
         <v>-15000</v>
       </c>
       <c r="K70">
-        <v>114079.2</v>
+        <v>26363.1</v>
       </c>
       <c r="L70">
-        <v>2460.5</v>
+        <v>237.1</v>
       </c>
       <c r="M70">
-        <v>2193.7</v>
+        <v>226.3</v>
       </c>
       <c r="N70" t="s">
         <v>3</v>
@@ -3643,34 +3643,34 @@
         <v>65</v>
       </c>
       <c r="D71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
         <v>3</v>
       </c>
       <c r="F71">
-        <v>-89821.4</v>
+        <v>-239523.8</v>
       </c>
       <c r="G71">
         <v>-15000</v>
       </c>
       <c r="H71">
-        <v>87820.9</v>
+        <v>-247.1</v>
       </c>
       <c r="I71">
-        <v>-89821.4</v>
+        <v>-245511.9</v>
       </c>
       <c r="J71">
         <v>-15000</v>
       </c>
       <c r="K71">
-        <v>110453.5</v>
+        <v>-5076</v>
       </c>
       <c r="L71">
-        <v>2541.1</v>
+        <v>158.3</v>
       </c>
       <c r="M71">
-        <v>2226.5</v>
+        <v>158.1</v>
       </c>
       <c r="N71" t="s">
         <v>3</v>
@@ -3687,34 +3687,34 @@
         <v>65</v>
       </c>
       <c r="D72" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E72" t="s">
         <v>3</v>
       </c>
       <c r="F72">
-        <v>-107785.7</v>
+        <v>-239523.8</v>
       </c>
       <c r="G72">
-        <v>-15000</v>
+        <v>-17800</v>
       </c>
       <c r="H72">
-        <v>80759.4</v>
+        <v>-247.1</v>
       </c>
       <c r="I72">
-        <v>-107785.7</v>
+        <v>-245511.9</v>
       </c>
       <c r="J72">
-        <v>-15000</v>
+        <v>-17800</v>
       </c>
       <c r="K72">
-        <v>106310.2</v>
+        <v>26363.1</v>
       </c>
       <c r="L72">
-        <v>2623.2</v>
+        <v>3309.7</v>
       </c>
       <c r="M72">
-        <v>2258.1</v>
+        <v>7515.1</v>
       </c>
       <c r="N72" t="s">
         <v>3</v>
@@ -3731,34 +3731,34 @@
         <v>65</v>
       </c>
       <c r="D73" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E73" t="s">
         <v>3</v>
       </c>
       <c r="F73">
-        <v>-125750</v>
+        <v>-245511.9</v>
       </c>
       <c r="G73">
         <v>-15000</v>
       </c>
       <c r="H73">
-        <v>72687.7</v>
+        <v>26363.1</v>
       </c>
       <c r="I73">
-        <v>-125750</v>
+        <v>-251500</v>
       </c>
       <c r="J73">
         <v>-15000</v>
       </c>
       <c r="K73">
-        <v>101685.6</v>
+        <v>10000</v>
       </c>
       <c r="L73">
-        <v>2706.6</v>
+        <v>226.3</v>
       </c>
       <c r="M73">
-        <v>2289.3</v>
+        <v>150</v>
       </c>
       <c r="N73" t="s">
         <v>3</v>
@@ -3775,34 +3775,34 @@
         <v>65</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E74" t="s">
         <v>3</v>
       </c>
       <c r="F74">
-        <v>-143714.3</v>
+        <v>-245511.9</v>
       </c>
       <c r="G74">
         <v>-15000</v>
       </c>
       <c r="H74">
-        <v>63636.7</v>
+        <v>-5076</v>
       </c>
       <c r="I74">
-        <v>-143714.3</v>
+        <v>-251500</v>
       </c>
       <c r="J74">
         <v>-15000</v>
       </c>
       <c r="K74">
-        <v>96600.6</v>
+        <v>-10000</v>
       </c>
       <c r="L74">
-        <v>2791.4</v>
+        <v>158.1</v>
       </c>
       <c r="M74">
-        <v>2322.9</v>
+        <v>150</v>
       </c>
       <c r="N74" t="s">
         <v>3</v>
@@ -3819,34 +3819,34 @@
         <v>65</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E75" t="s">
         <v>3</v>
       </c>
       <c r="F75">
-        <v>-161678.6</v>
+        <v>-245511.9</v>
       </c>
       <c r="G75">
-        <v>-15000</v>
+        <v>-17800</v>
       </c>
       <c r="H75">
-        <v>53632.2</v>
+        <v>-5076</v>
       </c>
       <c r="I75">
-        <v>-161678.6</v>
+        <v>-251500</v>
       </c>
       <c r="J75">
-        <v>-15000</v>
+        <v>-17800</v>
       </c>
       <c r="K75">
-        <v>91034.9</v>
+        <v>10000</v>
       </c>
       <c r="L75">
-        <v>2877.2</v>
+        <v>3341</v>
       </c>
       <c r="M75">
-        <v>2369.1</v>
+        <v>7515.1</v>
       </c>
       <c r="N75" t="s">
         <v>3</v>
@@ -3869,28 +3869,28 @@
         <v>3</v>
       </c>
       <c r="F76">
-        <v>-179642.9</v>
+        <v>-17964.3</v>
       </c>
       <c r="G76">
         <v>-15000</v>
       </c>
       <c r="H76">
-        <v>42696.5</v>
+        <v>104996.7</v>
       </c>
       <c r="I76">
-        <v>-179642.9</v>
+        <v>-17964.3</v>
       </c>
       <c r="J76">
         <v>-15000</v>
       </c>
       <c r="K76">
-        <v>84829.7</v>
+        <v>121262</v>
       </c>
       <c r="L76">
-        <v>2964</v>
+        <v>2227.2</v>
       </c>
       <c r="M76">
-        <v>2462.7</v>
+        <v>2082.6</v>
       </c>
       <c r="N76" t="s">
         <v>3</v>
@@ -3913,28 +3913,28 @@
         <v>3</v>
       </c>
       <c r="F77">
-        <v>-197607.1</v>
+        <v>-35928.6</v>
       </c>
       <c r="G77">
         <v>-15000</v>
       </c>
       <c r="H77">
-        <v>30849.1</v>
+        <v>102506.3</v>
       </c>
       <c r="I77">
-        <v>-197607.1</v>
+        <v>-35928.6</v>
       </c>
       <c r="J77">
         <v>-15000</v>
       </c>
       <c r="K77">
-        <v>77395.5</v>
+        <v>119567.6</v>
       </c>
       <c r="L77">
-        <v>3051.7</v>
+        <v>2303.9</v>
       </c>
       <c r="M77">
-        <v>2717.6</v>
+        <v>2122.7</v>
       </c>
       <c r="N77" t="s">
         <v>3</v>
@@ -3957,28 +3957,28 @@
         <v>3</v>
       </c>
       <c r="F78">
-        <v>-215571.4</v>
+        <v>-53892.9</v>
       </c>
       <c r="G78">
         <v>-15000</v>
       </c>
       <c r="H78">
-        <v>18107.1</v>
+        <v>98751.5</v>
       </c>
       <c r="I78">
-        <v>-215571.4</v>
+        <v>-53892.9</v>
       </c>
       <c r="J78">
         <v>-15000</v>
       </c>
       <c r="K78">
-        <v>66932</v>
+        <v>117139.3</v>
       </c>
       <c r="L78">
-        <v>3140</v>
+        <v>2381.5</v>
       </c>
       <c r="M78">
-        <v>3508.8</v>
+        <v>2159.3</v>
       </c>
       <c r="N78" t="s">
         <v>3</v>
@@ -4001,28 +4001,28 @@
         <v>3</v>
       </c>
       <c r="F79">
-        <v>-233535.7</v>
+        <v>-71857.1</v>
       </c>
       <c r="G79">
         <v>-15000</v>
       </c>
       <c r="H79">
-        <v>4486.1</v>
+        <v>93834.3</v>
       </c>
       <c r="I79">
-        <v>-233535.7</v>
+        <v>-71857.1</v>
       </c>
       <c r="J79">
         <v>-15000</v>
       </c>
       <c r="K79">
-        <v>48541.2</v>
+        <v>114079.2</v>
       </c>
       <c r="L79">
-        <v>3229</v>
+        <v>2460.5</v>
       </c>
       <c r="M79">
-        <v>5903.6</v>
+        <v>2193.7</v>
       </c>
       <c r="N79" t="s">
         <v>3</v>
@@ -4039,90 +4039,84 @@
         <v>65</v>
       </c>
       <c r="D80" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E80" t="s">
         <v>3</v>
       </c>
       <c r="F80">
-        <v>-251500</v>
+        <v>-89821.4</v>
       </c>
       <c r="G80">
         <v>-15000</v>
       </c>
       <c r="H80">
-        <v>-10000</v>
+        <v>87820.9</v>
       </c>
       <c r="I80">
-        <v>-251500</v>
+        <v>-89821.4</v>
       </c>
       <c r="J80">
         <v>-15000</v>
       </c>
       <c r="K80">
-        <v>10000</v>
+        <v>110453.5</v>
       </c>
       <c r="L80">
-        <v>4599.8</v>
+        <v>2541.1</v>
       </c>
       <c r="M80">
-        <v>9550.8</v>
+        <v>2226.5</v>
       </c>
       <c r="N80" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>48</v>
+      <c r="B81" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D81" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
-        <v>50</v>
-      </c>
-      <c r="F81" t="s">
-        <v>66</v>
-      </c>
-      <c r="G81" t="s">
-        <v>67</v>
-      </c>
-      <c r="H81" t="s">
-        <v>68</v>
-      </c>
-      <c r="I81" t="s">
-        <v>69</v>
-      </c>
-      <c r="J81" t="s">
-        <v>70</v>
-      </c>
-      <c r="K81" t="s">
-        <v>71</v>
-      </c>
-      <c r="L81" t="s">
-        <v>72</v>
-      </c>
-      <c r="M81" t="s">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="F81">
+        <v>-107785.7</v>
+      </c>
+      <c r="G81">
+        <v>-15000</v>
+      </c>
+      <c r="H81">
+        <v>80759.4</v>
+      </c>
+      <c r="I81">
+        <v>-107785.7</v>
+      </c>
+      <c r="J81">
+        <v>-15000</v>
+      </c>
+      <c r="K81">
+        <v>106310.2</v>
+      </c>
+      <c r="L81">
+        <v>2623.2</v>
+      </c>
+      <c r="M81">
+        <v>2258.1</v>
       </c>
       <c r="N81" t="s">
-        <v>61</v>
-      </c>
-      <c r="O81" t="s">
-        <v>62</v>
-      </c>
-      <c r="P81" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -4133,80 +4127,169 @@
         <v>65</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="E82" t="s">
-        <v>74</v>
-      </c>
-      <c r="F82" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="F82">
+        <v>-125750</v>
+      </c>
+      <c r="G82">
+        <v>-15000</v>
+      </c>
+      <c r="H82">
+        <v>72687.7</v>
+      </c>
+      <c r="I82">
+        <v>-125750</v>
+      </c>
+      <c r="J82">
+        <v>-15000</v>
+      </c>
+      <c r="K82">
+        <v>101685.6</v>
+      </c>
+      <c r="L82">
+        <v>2706.6</v>
+      </c>
+      <c r="M82">
+        <v>2289.3</v>
+      </c>
+      <c r="N82" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C83" t="s">
+        <v>65</v>
+      </c>
+      <c r="D83" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83">
+        <v>-143714.3</v>
+      </c>
+      <c r="G83">
+        <v>-15000</v>
+      </c>
+      <c r="H83">
+        <v>63636.7</v>
+      </c>
+      <c r="I83">
+        <v>-143714.3</v>
+      </c>
+      <c r="J83">
+        <v>-15000</v>
+      </c>
+      <c r="K83">
+        <v>96600.6</v>
+      </c>
+      <c r="L83">
+        <v>2791.4</v>
+      </c>
+      <c r="M83">
+        <v>2322.9</v>
+      </c>
+      <c r="N83" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>45</v>
+      <c r="B84" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C84" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="D84" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84">
+        <v>-161678.6</v>
+      </c>
+      <c r="G84">
+        <v>-15000</v>
+      </c>
+      <c r="H84">
+        <v>53632.2</v>
+      </c>
+      <c r="I84">
+        <v>-161678.6</v>
+      </c>
+      <c r="J84">
+        <v>-15000</v>
+      </c>
+      <c r="K84">
+        <v>91034.9</v>
+      </c>
+      <c r="L84">
+        <v>2877.2</v>
+      </c>
+      <c r="M84">
+        <v>2369.1</v>
+      </c>
+      <c r="N84" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>48</v>
+      <c r="B85" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C85" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D85" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>50</v>
-      </c>
-      <c r="F85" t="s">
-        <v>51</v>
-      </c>
-      <c r="G85" t="s">
-        <v>52</v>
-      </c>
-      <c r="H85" t="s">
-        <v>53</v>
-      </c>
-      <c r="I85" t="s">
-        <v>54</v>
-      </c>
-      <c r="J85" t="s">
-        <v>55</v>
-      </c>
-      <c r="K85" t="s">
-        <v>56</v>
-      </c>
-      <c r="L85" t="s">
-        <v>57</v>
-      </c>
-      <c r="M85" t="s">
-        <v>58</v>
+        <v>3</v>
+      </c>
+      <c r="F85">
+        <v>-179642.9</v>
+      </c>
+      <c r="G85">
+        <v>-15000</v>
+      </c>
+      <c r="H85">
+        <v>42696.5</v>
+      </c>
+      <c r="I85">
+        <v>-179642.9</v>
+      </c>
+      <c r="J85">
+        <v>-15000</v>
+      </c>
+      <c r="K85">
+        <v>84829.7</v>
+      </c>
+      <c r="L85">
+        <v>2964</v>
+      </c>
+      <c r="M85">
+        <v>2462.7</v>
       </c>
       <c r="N85" t="s">
-        <v>59</v>
-      </c>
-      <c r="O85" t="s">
-        <v>60</v>
-      </c>
-      <c r="P85" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>62</v>
-      </c>
-      <c r="R85" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
@@ -4217,37 +4300,37 @@
         <v>64</v>
       </c>
       <c r="C86" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E86" t="s">
         <v>3</v>
       </c>
       <c r="F86">
-        <v>-17964.3</v>
+        <v>-197607.1</v>
       </c>
       <c r="G86">
         <v>-15000</v>
       </c>
       <c r="H86">
-        <v>121262</v>
+        <v>30849.1</v>
       </c>
       <c r="I86">
-        <v>-17964.3</v>
+        <v>-197607.1</v>
       </c>
       <c r="J86">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K86">
-        <v>121262</v>
+        <v>77395.5</v>
       </c>
       <c r="L86">
-        <v>2900</v>
+        <v>3051.7</v>
       </c>
       <c r="M86">
-        <v>2900</v>
+        <v>2717.6</v>
       </c>
       <c r="N86" t="s">
         <v>3</v>
@@ -4261,37 +4344,37 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
         <v>3</v>
       </c>
       <c r="F87">
-        <v>-17964.3</v>
+        <v>-215571.4</v>
       </c>
       <c r="G87">
         <v>-15000</v>
       </c>
       <c r="H87">
-        <v>104996.7</v>
+        <v>18107.1</v>
       </c>
       <c r="I87">
-        <v>-17964.3</v>
+        <v>-215571.4</v>
       </c>
       <c r="J87">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K87">
-        <v>104996.7</v>
+        <v>66932</v>
       </c>
       <c r="L87">
-        <v>3000</v>
+        <v>3117.9</v>
       </c>
       <c r="M87">
-        <v>3000</v>
+        <v>3190.4</v>
       </c>
       <c r="N87" t="s">
         <v>3</v>
@@ -4305,37 +4388,37 @@
         <v>64</v>
       </c>
       <c r="C88" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E88" t="s">
         <v>3</v>
       </c>
       <c r="F88">
-        <v>-35928.6</v>
+        <v>-224553.6</v>
       </c>
       <c r="G88">
         <v>-15000</v>
       </c>
       <c r="H88">
-        <v>119567.6</v>
+        <v>11405.6</v>
       </c>
       <c r="I88">
-        <v>-35928.6</v>
+        <v>-224553.6</v>
       </c>
       <c r="J88">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K88">
-        <v>119567.6</v>
+        <v>59246.1</v>
       </c>
       <c r="L88">
-        <v>2900</v>
+        <v>3162.2</v>
       </c>
       <c r="M88">
-        <v>2900</v>
+        <v>3842.7</v>
       </c>
       <c r="N88" t="s">
         <v>3</v>
@@ -4349,37 +4432,37 @@
         <v>64</v>
       </c>
       <c r="C89" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
         <v>3</v>
       </c>
       <c r="F89">
-        <v>-35928.6</v>
+        <v>-233535.7</v>
       </c>
       <c r="G89">
         <v>-15000</v>
       </c>
       <c r="H89">
-        <v>102506.3</v>
+        <v>4486.1</v>
       </c>
       <c r="I89">
-        <v>-35928.6</v>
+        <v>-233535.7</v>
       </c>
       <c r="J89">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K89">
-        <v>102506.3</v>
+        <v>48541.2</v>
       </c>
       <c r="L89">
-        <v>3000</v>
+        <v>3199.3</v>
       </c>
       <c r="M89">
-        <v>3000</v>
+        <v>4727</v>
       </c>
       <c r="N89" t="s">
         <v>3</v>
@@ -4393,37 +4476,37 @@
         <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D90" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E90" t="s">
         <v>3</v>
       </c>
       <c r="F90">
-        <v>-53892.9</v>
+        <v>-239523.8</v>
       </c>
       <c r="G90">
         <v>-15000</v>
       </c>
       <c r="H90">
-        <v>117139.3</v>
+        <v>-247.1</v>
       </c>
       <c r="I90">
-        <v>-53892.9</v>
+        <v>-239523.8</v>
       </c>
       <c r="J90">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K90">
-        <v>117139.3</v>
+        <v>38882.2</v>
       </c>
       <c r="L90">
-        <v>2900</v>
+        <v>3229</v>
       </c>
       <c r="M90">
-        <v>2900</v>
+        <v>5780.5</v>
       </c>
       <c r="N90" t="s">
         <v>3</v>
@@ -4437,37 +4520,37 @@
         <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D91" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E91" t="s">
         <v>3</v>
       </c>
       <c r="F91">
-        <v>-53892.9</v>
+        <v>-245511.9</v>
       </c>
       <c r="G91">
         <v>-15000</v>
       </c>
       <c r="H91">
-        <v>98751.5</v>
+        <v>-5076</v>
       </c>
       <c r="I91">
-        <v>-53892.9</v>
+        <v>-245511.9</v>
       </c>
       <c r="J91">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K91">
-        <v>98751.5</v>
+        <v>26363.1</v>
       </c>
       <c r="L91">
-        <v>3000</v>
+        <v>3258.8</v>
       </c>
       <c r="M91">
-        <v>3000</v>
+        <v>7241.8</v>
       </c>
       <c r="N91" t="s">
         <v>3</v>
@@ -4481,87 +4564,93 @@
         <v>64</v>
       </c>
       <c r="C92" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D92" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E92" t="s">
         <v>3</v>
       </c>
       <c r="F92">
-        <v>-71857.1</v>
+        <v>-251500</v>
       </c>
       <c r="G92">
         <v>-15000</v>
       </c>
       <c r="H92">
-        <v>114079.2</v>
+        <v>-10000</v>
       </c>
       <c r="I92">
-        <v>-71857.1</v>
+        <v>-251500</v>
       </c>
       <c r="J92">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K92">
-        <v>114079.2</v>
+        <v>10000</v>
       </c>
       <c r="L92">
-        <v>2900</v>
+        <v>4656.7</v>
       </c>
       <c r="M92">
-        <v>2900</v>
+        <v>11887.3</v>
       </c>
       <c r="N92" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>64</v>
+      <c r="B93" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C93" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="D93" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E93" t="s">
-        <v>3</v>
-      </c>
-      <c r="F93">
-        <v>-71857.1</v>
-      </c>
-      <c r="G93">
-        <v>-15000</v>
-      </c>
-      <c r="H93">
-        <v>93834.3</v>
-      </c>
-      <c r="I93">
-        <v>-71857.1</v>
-      </c>
-      <c r="J93">
-        <v>15000</v>
-      </c>
-      <c r="K93">
-        <v>93834.3</v>
-      </c>
-      <c r="L93">
-        <v>3000</v>
-      </c>
-      <c r="M93">
-        <v>3000</v>
+        <v>50</v>
+      </c>
+      <c r="F93" t="s">
+        <v>66</v>
+      </c>
+      <c r="G93" t="s">
+        <v>67</v>
+      </c>
+      <c r="H93" t="s">
+        <v>68</v>
+      </c>
+      <c r="I93" t="s">
+        <v>69</v>
+      </c>
+      <c r="J93" t="s">
+        <v>70</v>
+      </c>
+      <c r="K93" t="s">
+        <v>71</v>
+      </c>
+      <c r="L93" t="s">
+        <v>72</v>
+      </c>
+      <c r="M93" t="s">
+        <v>60</v>
       </c>
       <c r="N93" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="O93" t="s">
+        <v>62</v>
+      </c>
+      <c r="P93" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -4569,172 +4658,83 @@
         <v>64</v>
       </c>
       <c r="C94" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D94" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="E94" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94">
-        <v>-89821.4</v>
-      </c>
-      <c r="G94">
-        <v>-15000</v>
-      </c>
-      <c r="H94">
-        <v>110453.5</v>
-      </c>
-      <c r="I94">
-        <v>-89821.4</v>
-      </c>
-      <c r="J94">
-        <v>15000</v>
-      </c>
-      <c r="K94">
-        <v>110453.5</v>
-      </c>
-      <c r="L94">
-        <v>2900</v>
-      </c>
-      <c r="M94">
-        <v>2900</v>
-      </c>
-      <c r="N94" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C95" t="s">
-        <v>76</v>
-      </c>
-      <c r="D95" t="s">
-        <v>28</v>
-      </c>
-      <c r="E95" t="s">
-        <v>3</v>
-      </c>
-      <c r="F95">
-        <v>-89821.4</v>
-      </c>
-      <c r="G95">
-        <v>-15000</v>
-      </c>
-      <c r="H95">
-        <v>87820.9</v>
-      </c>
-      <c r="I95">
-        <v>-89821.4</v>
-      </c>
-      <c r="J95">
-        <v>15000</v>
-      </c>
-      <c r="K95">
-        <v>87820.9</v>
-      </c>
-      <c r="L95">
-        <v>3000</v>
-      </c>
-      <c r="M95">
-        <v>3000</v>
-      </c>
-      <c r="N95" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="F94" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>64</v>
+      <c r="B96" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C96" t="s">
-        <v>76</v>
-      </c>
-      <c r="D96" t="s">
-        <v>28</v>
-      </c>
-      <c r="E96" t="s">
-        <v>3</v>
-      </c>
-      <c r="F96">
-        <v>-107785.7</v>
-      </c>
-      <c r="G96">
-        <v>-15000</v>
-      </c>
-      <c r="H96">
-        <v>106310.2</v>
-      </c>
-      <c r="I96">
-        <v>-107785.7</v>
-      </c>
-      <c r="J96">
-        <v>15000</v>
-      </c>
-      <c r="K96">
-        <v>106310.2</v>
-      </c>
-      <c r="L96">
-        <v>2900</v>
-      </c>
-      <c r="M96">
-        <v>2900</v>
-      </c>
-      <c r="N96" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>64</v>
+      <c r="B97" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C97" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E97" t="s">
-        <v>3</v>
-      </c>
-      <c r="F97">
-        <v>-107785.7</v>
-      </c>
-      <c r="G97">
-        <v>-15000</v>
-      </c>
-      <c r="H97">
-        <v>80759.4</v>
-      </c>
-      <c r="I97">
-        <v>-107785.7</v>
-      </c>
-      <c r="J97">
-        <v>15000</v>
-      </c>
-      <c r="K97">
-        <v>80759.4</v>
-      </c>
-      <c r="L97">
-        <v>3000</v>
-      </c>
-      <c r="M97">
-        <v>3000</v>
+        <v>50</v>
+      </c>
+      <c r="F97" t="s">
+        <v>51</v>
+      </c>
+      <c r="G97" t="s">
+        <v>52</v>
+      </c>
+      <c r="H97" t="s">
+        <v>53</v>
+      </c>
+      <c r="I97" t="s">
+        <v>54</v>
+      </c>
+      <c r="J97" t="s">
+        <v>55</v>
+      </c>
+      <c r="K97" t="s">
+        <v>56</v>
+      </c>
+      <c r="L97" t="s">
+        <v>57</v>
+      </c>
+      <c r="M97" t="s">
+        <v>58</v>
       </c>
       <c r="N97" t="s">
-        <v>3</v>
+        <v>59</v>
+      </c>
+      <c r="O97" t="s">
+        <v>60</v>
+      </c>
+      <c r="P97" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>62</v>
+      </c>
+      <c r="R97" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
@@ -4754,22 +4754,22 @@
         <v>3</v>
       </c>
       <c r="F98">
-        <v>-125750</v>
+        <v>-17964.3</v>
       </c>
       <c r="G98">
         <v>-15000</v>
       </c>
       <c r="H98">
-        <v>101685.6</v>
+        <v>121262</v>
       </c>
       <c r="I98">
-        <v>-125750</v>
+        <v>-17964.3</v>
       </c>
       <c r="J98">
         <v>15000</v>
       </c>
       <c r="K98">
-        <v>101685.6</v>
+        <v>121262</v>
       </c>
       <c r="L98">
         <v>2900</v>
@@ -4798,22 +4798,22 @@
         <v>3</v>
       </c>
       <c r="F99">
-        <v>-125750</v>
+        <v>-17964.3</v>
       </c>
       <c r="G99">
         <v>-15000</v>
       </c>
       <c r="H99">
-        <v>72687.7</v>
+        <v>104996.7</v>
       </c>
       <c r="I99">
-        <v>-125750</v>
+        <v>-17964.3</v>
       </c>
       <c r="J99">
         <v>15000</v>
       </c>
       <c r="K99">
-        <v>72687.7</v>
+        <v>104996.7</v>
       </c>
       <c r="L99">
         <v>3000</v>
@@ -4842,22 +4842,22 @@
         <v>3</v>
       </c>
       <c r="F100">
-        <v>-143714.3</v>
+        <v>-35928.6</v>
       </c>
       <c r="G100">
         <v>-15000</v>
       </c>
       <c r="H100">
-        <v>96600.6</v>
+        <v>119567.6</v>
       </c>
       <c r="I100">
-        <v>-143714.3</v>
+        <v>-35928.6</v>
       </c>
       <c r="J100">
         <v>15000</v>
       </c>
       <c r="K100">
-        <v>96600.6</v>
+        <v>119567.6</v>
       </c>
       <c r="L100">
         <v>2900</v>
@@ -4886,22 +4886,22 @@
         <v>3</v>
       </c>
       <c r="F101">
-        <v>-143714.3</v>
+        <v>-35928.6</v>
       </c>
       <c r="G101">
         <v>-15000</v>
       </c>
       <c r="H101">
-        <v>63636.7</v>
+        <v>102506.3</v>
       </c>
       <c r="I101">
-        <v>-143714.3</v>
+        <v>-35928.6</v>
       </c>
       <c r="J101">
         <v>15000</v>
       </c>
       <c r="K101">
-        <v>63636.7</v>
+        <v>102506.3</v>
       </c>
       <c r="L101">
         <v>3000</v>
@@ -4930,22 +4930,22 @@
         <v>3</v>
       </c>
       <c r="F102">
-        <v>-161678.6</v>
+        <v>-53892.9</v>
       </c>
       <c r="G102">
         <v>-15000</v>
       </c>
       <c r="H102">
-        <v>91034.9</v>
+        <v>117139.3</v>
       </c>
       <c r="I102">
-        <v>-161678.6</v>
+        <v>-53892.9</v>
       </c>
       <c r="J102">
         <v>15000</v>
       </c>
       <c r="K102">
-        <v>91034.9</v>
+        <v>117139.3</v>
       </c>
       <c r="L102">
         <v>2900</v>
@@ -4974,22 +4974,22 @@
         <v>3</v>
       </c>
       <c r="F103">
-        <v>-161678.6</v>
+        <v>-53892.9</v>
       </c>
       <c r="G103">
         <v>-15000</v>
       </c>
       <c r="H103">
-        <v>53632.2</v>
+        <v>98751.5</v>
       </c>
       <c r="I103">
-        <v>-161678.6</v>
+        <v>-53892.9</v>
       </c>
       <c r="J103">
         <v>15000</v>
       </c>
       <c r="K103">
-        <v>53632.2</v>
+        <v>98751.5</v>
       </c>
       <c r="L103">
         <v>3000</v>
@@ -5018,22 +5018,22 @@
         <v>3</v>
       </c>
       <c r="F104">
-        <v>-179642.9</v>
+        <v>-71857.1</v>
       </c>
       <c r="G104">
         <v>-15000</v>
       </c>
       <c r="H104">
-        <v>84829.7</v>
+        <v>114079.2</v>
       </c>
       <c r="I104">
-        <v>-179642.9</v>
+        <v>-71857.1</v>
       </c>
       <c r="J104">
         <v>15000</v>
       </c>
       <c r="K104">
-        <v>84829.7</v>
+        <v>114079.2</v>
       </c>
       <c r="L104">
         <v>2900</v>
@@ -5062,22 +5062,22 @@
         <v>3</v>
       </c>
       <c r="F105">
-        <v>-179642.9</v>
+        <v>-71857.1</v>
       </c>
       <c r="G105">
         <v>-15000</v>
       </c>
       <c r="H105">
-        <v>42696.5</v>
+        <v>93834.3</v>
       </c>
       <c r="I105">
-        <v>-179642.9</v>
+        <v>-71857.1</v>
       </c>
       <c r="J105">
         <v>15000</v>
       </c>
       <c r="K105">
-        <v>42696.5</v>
+        <v>93834.3</v>
       </c>
       <c r="L105">
         <v>3000</v>
@@ -5106,22 +5106,22 @@
         <v>3</v>
       </c>
       <c r="F106">
-        <v>-197607.1</v>
+        <v>-89821.4</v>
       </c>
       <c r="G106">
         <v>-15000</v>
       </c>
       <c r="H106">
-        <v>77395.5</v>
+        <v>110453.5</v>
       </c>
       <c r="I106">
-        <v>-197607.1</v>
+        <v>-89821.4</v>
       </c>
       <c r="J106">
         <v>15000</v>
       </c>
       <c r="K106">
-        <v>77395.5</v>
+        <v>110453.5</v>
       </c>
       <c r="L106">
         <v>2900</v>
@@ -5150,22 +5150,22 @@
         <v>3</v>
       </c>
       <c r="F107">
-        <v>-197607.1</v>
+        <v>-89821.4</v>
       </c>
       <c r="G107">
         <v>-15000</v>
       </c>
       <c r="H107">
-        <v>30849.1</v>
+        <v>87820.9</v>
       </c>
       <c r="I107">
-        <v>-197607.1</v>
+        <v>-89821.4</v>
       </c>
       <c r="J107">
         <v>15000</v>
       </c>
       <c r="K107">
-        <v>30849.1</v>
+        <v>87820.9</v>
       </c>
       <c r="L107">
         <v>3000</v>
@@ -5194,22 +5194,22 @@
         <v>3</v>
       </c>
       <c r="F108">
-        <v>-215571.4</v>
+        <v>-107785.7</v>
       </c>
       <c r="G108">
         <v>-15000</v>
       </c>
       <c r="H108">
-        <v>66932</v>
+        <v>106310.2</v>
       </c>
       <c r="I108">
-        <v>-215571.4</v>
+        <v>-107785.7</v>
       </c>
       <c r="J108">
         <v>15000</v>
       </c>
       <c r="K108">
-        <v>66932</v>
+        <v>106310.2</v>
       </c>
       <c r="L108">
         <v>2900</v>
@@ -5238,22 +5238,22 @@
         <v>3</v>
       </c>
       <c r="F109">
-        <v>-215571.4</v>
+        <v>-107785.7</v>
       </c>
       <c r="G109">
         <v>-15000</v>
       </c>
       <c r="H109">
-        <v>18107.1</v>
+        <v>80759.4</v>
       </c>
       <c r="I109">
-        <v>-215571.4</v>
+        <v>-107785.7</v>
       </c>
       <c r="J109">
         <v>15000</v>
       </c>
       <c r="K109">
-        <v>18107.1</v>
+        <v>80759.4</v>
       </c>
       <c r="L109">
         <v>3000</v>
@@ -5282,22 +5282,22 @@
         <v>3</v>
       </c>
       <c r="F110">
-        <v>-233535.7</v>
+        <v>-125750</v>
       </c>
       <c r="G110">
         <v>-15000</v>
       </c>
       <c r="H110">
-        <v>48541.2</v>
+        <v>101685.6</v>
       </c>
       <c r="I110">
-        <v>-233535.7</v>
+        <v>-125750</v>
       </c>
       <c r="J110">
         <v>15000</v>
       </c>
       <c r="K110">
-        <v>48541.2</v>
+        <v>101685.6</v>
       </c>
       <c r="L110">
         <v>2900</v>
@@ -5326,22 +5326,22 @@
         <v>3</v>
       </c>
       <c r="F111">
-        <v>-233535.7</v>
+        <v>-125750</v>
       </c>
       <c r="G111">
         <v>-15000</v>
       </c>
       <c r="H111">
-        <v>4486.1</v>
+        <v>72687.7</v>
       </c>
       <c r="I111">
-        <v>-233535.7</v>
+        <v>-125750</v>
       </c>
       <c r="J111">
         <v>15000</v>
       </c>
       <c r="K111">
-        <v>4486.1</v>
+        <v>72687.7</v>
       </c>
       <c r="L111">
         <v>3000</v>
@@ -5370,22 +5370,22 @@
         <v>3</v>
       </c>
       <c r="F112">
-        <v>-251500</v>
+        <v>-143714.3</v>
       </c>
       <c r="G112">
         <v>-15000</v>
       </c>
       <c r="H112">
-        <v>10000</v>
+        <v>96600.6</v>
       </c>
       <c r="I112">
-        <v>-251500</v>
+        <v>-143714.3</v>
       </c>
       <c r="J112">
         <v>15000</v>
       </c>
       <c r="K112">
-        <v>10000</v>
+        <v>96600.6</v>
       </c>
       <c r="L112">
         <v>2900</v>
@@ -5414,22 +5414,22 @@
         <v>3</v>
       </c>
       <c r="F113">
-        <v>-251500</v>
+        <v>-143714.3</v>
       </c>
       <c r="G113">
         <v>-15000</v>
       </c>
       <c r="H113">
-        <v>-10000</v>
+        <v>63636.7</v>
       </c>
       <c r="I113">
-        <v>-251500</v>
+        <v>-143714.3</v>
       </c>
       <c r="J113">
         <v>15000</v>
       </c>
       <c r="K113">
-        <v>-10000</v>
+        <v>63636.7</v>
       </c>
       <c r="L113">
         <v>3000</v>
@@ -5452,34 +5452,34 @@
         <v>76</v>
       </c>
       <c r="D114" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E114" t="s">
         <v>3</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>-161678.6</v>
       </c>
       <c r="G114">
         <v>-15000</v>
       </c>
       <c r="H114">
-        <v>118898.7</v>
+        <v>91034.9</v>
       </c>
       <c r="I114">
-        <v>-17964.3</v>
+        <v>-161678.6</v>
       </c>
       <c r="J114">
         <v>15000</v>
       </c>
       <c r="K114">
-        <v>118154.9</v>
+        <v>91034.9</v>
       </c>
       <c r="L114">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="M114">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="N114" t="s">
         <v>3</v>
@@ -5496,34 +5496,34 @@
         <v>76</v>
       </c>
       <c r="D115" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E115" t="s">
         <v>3</v>
       </c>
       <c r="F115">
-        <v>-17964.3</v>
+        <v>-161678.6</v>
       </c>
       <c r="G115">
+        <v>-15000</v>
+      </c>
+      <c r="H115">
+        <v>53632.2</v>
+      </c>
+      <c r="I115">
+        <v>-161678.6</v>
+      </c>
+      <c r="J115">
         <v>15000</v>
       </c>
-      <c r="H115">
-        <v>118154.9</v>
-      </c>
-      <c r="I115">
-        <v>-35928.6</v>
-      </c>
-      <c r="J115">
-        <v>-15000</v>
-      </c>
       <c r="K115">
-        <v>116453</v>
+        <v>53632.2</v>
       </c>
       <c r="L115">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="M115">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="N115" t="s">
         <v>3</v>
@@ -5540,34 +5540,34 @@
         <v>76</v>
       </c>
       <c r="D116" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E116" t="s">
         <v>3</v>
       </c>
       <c r="F116">
-        <v>-35928.6</v>
+        <v>-179642.9</v>
       </c>
       <c r="G116">
         <v>-15000</v>
       </c>
       <c r="H116">
-        <v>116453</v>
+        <v>84829.7</v>
       </c>
       <c r="I116">
-        <v>-53892.9</v>
+        <v>-179642.9</v>
       </c>
       <c r="J116">
         <v>15000</v>
       </c>
       <c r="K116">
-        <v>114016.3</v>
+        <v>84829.7</v>
       </c>
       <c r="L116">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="M116">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="N116" t="s">
         <v>3</v>
@@ -5584,34 +5584,34 @@
         <v>76</v>
       </c>
       <c r="D117" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E117" t="s">
         <v>3</v>
       </c>
       <c r="F117">
-        <v>-53892.9</v>
+        <v>-179642.9</v>
       </c>
       <c r="G117">
+        <v>-15000</v>
+      </c>
+      <c r="H117">
+        <v>42696.5</v>
+      </c>
+      <c r="I117">
+        <v>-179642.9</v>
+      </c>
+      <c r="J117">
         <v>15000</v>
       </c>
-      <c r="H117">
-        <v>114016.3</v>
-      </c>
-      <c r="I117">
-        <v>-71857.1</v>
-      </c>
-      <c r="J117">
-        <v>-15000</v>
-      </c>
       <c r="K117">
-        <v>110946.9</v>
+        <v>42696.5</v>
       </c>
       <c r="L117">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="M117">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="N117" t="s">
         <v>3</v>
@@ -5628,34 +5628,34 @@
         <v>76</v>
       </c>
       <c r="D118" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E118" t="s">
         <v>3</v>
       </c>
       <c r="F118">
-        <v>-71857.1</v>
+        <v>-197607.1</v>
       </c>
       <c r="G118">
         <v>-15000</v>
       </c>
       <c r="H118">
-        <v>110946.9</v>
+        <v>77395.5</v>
       </c>
       <c r="I118">
-        <v>-89821.4</v>
+        <v>-197607.1</v>
       </c>
       <c r="J118">
         <v>15000</v>
       </c>
       <c r="K118">
-        <v>107311.5</v>
+        <v>77395.5</v>
       </c>
       <c r="L118">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="M118">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="N118" t="s">
         <v>3</v>
@@ -5672,34 +5672,34 @@
         <v>76</v>
       </c>
       <c r="D119" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E119" t="s">
         <v>3</v>
       </c>
       <c r="F119">
-        <v>-89821.4</v>
+        <v>-197607.1</v>
       </c>
       <c r="G119">
+        <v>-15000</v>
+      </c>
+      <c r="H119">
+        <v>30849.1</v>
+      </c>
+      <c r="I119">
+        <v>-197607.1</v>
+      </c>
+      <c r="J119">
         <v>15000</v>
       </c>
-      <c r="H119">
-        <v>107311.5</v>
-      </c>
-      <c r="I119">
-        <v>-107785.7</v>
-      </c>
-      <c r="J119">
-        <v>-15000</v>
-      </c>
       <c r="K119">
-        <v>103158</v>
+        <v>30849.1</v>
       </c>
       <c r="L119">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="M119">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="N119" t="s">
         <v>3</v>
@@ -5716,34 +5716,34 @@
         <v>76</v>
       </c>
       <c r="D120" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E120" t="s">
         <v>3</v>
       </c>
       <c r="F120">
-        <v>-107785.7</v>
+        <v>-215571.4</v>
       </c>
       <c r="G120">
         <v>-15000</v>
       </c>
       <c r="H120">
-        <v>103158</v>
+        <v>66932</v>
       </c>
       <c r="I120">
-        <v>-125750</v>
+        <v>-215571.4</v>
       </c>
       <c r="J120">
         <v>15000</v>
       </c>
       <c r="K120">
-        <v>98522.7</v>
+        <v>66932</v>
       </c>
       <c r="L120">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="M120">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="N120" t="s">
         <v>3</v>
@@ -5760,34 +5760,34 @@
         <v>76</v>
       </c>
       <c r="D121" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E121" t="s">
         <v>3</v>
       </c>
       <c r="F121">
-        <v>-125750</v>
+        <v>-215571.4</v>
       </c>
       <c r="G121">
+        <v>-15000</v>
+      </c>
+      <c r="H121">
+        <v>18107.1</v>
+      </c>
+      <c r="I121">
+        <v>-215571.4</v>
+      </c>
+      <c r="J121">
         <v>15000</v>
       </c>
-      <c r="H121">
-        <v>98522.7</v>
-      </c>
-      <c r="I121">
-        <v>-143714.3</v>
-      </c>
-      <c r="J121">
-        <v>-15000</v>
-      </c>
       <c r="K121">
-        <v>93425.6</v>
+        <v>18107.1</v>
       </c>
       <c r="L121">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="M121">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="N121" t="s">
         <v>3</v>
@@ -5804,34 +5804,34 @@
         <v>76</v>
       </c>
       <c r="D122" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E122" t="s">
         <v>3</v>
       </c>
       <c r="F122">
-        <v>-143714.3</v>
+        <v>-224553.6</v>
       </c>
       <c r="G122">
         <v>-15000</v>
       </c>
       <c r="H122">
-        <v>93425.6</v>
+        <v>59246.1</v>
       </c>
       <c r="I122">
-        <v>-161678.6</v>
+        <v>-224553.6</v>
       </c>
       <c r="J122">
         <v>15000</v>
       </c>
       <c r="K122">
-        <v>87842.1</v>
+        <v>59246.1</v>
       </c>
       <c r="L122">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="M122">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="N122" t="s">
         <v>3</v>
@@ -5848,34 +5848,34 @@
         <v>76</v>
       </c>
       <c r="D123" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E123" t="s">
         <v>3</v>
       </c>
       <c r="F123">
-        <v>-161678.6</v>
+        <v>-224553.6</v>
       </c>
       <c r="G123">
+        <v>-15000</v>
+      </c>
+      <c r="H123">
+        <v>11405.6</v>
+      </c>
+      <c r="I123">
+        <v>-224553.6</v>
+      </c>
+      <c r="J123">
         <v>15000</v>
       </c>
-      <c r="H123">
-        <v>87842.1</v>
-      </c>
-      <c r="I123">
-        <v>-179642.9</v>
-      </c>
-      <c r="J123">
-        <v>-15000</v>
-      </c>
       <c r="K123">
-        <v>81598.1</v>
+        <v>11405.6</v>
       </c>
       <c r="L123">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="M123">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="N123" t="s">
         <v>3</v>
@@ -5892,34 +5892,34 @@
         <v>76</v>
       </c>
       <c r="D124" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E124" t="s">
         <v>3</v>
       </c>
       <c r="F124">
-        <v>-179642.9</v>
+        <v>-233535.7</v>
       </c>
       <c r="G124">
         <v>-15000</v>
       </c>
       <c r="H124">
-        <v>81598.1</v>
+        <v>48541.2</v>
       </c>
       <c r="I124">
-        <v>-197607.1</v>
+        <v>-233535.7</v>
       </c>
       <c r="J124">
         <v>15000</v>
       </c>
       <c r="K124">
-        <v>74043.9</v>
+        <v>48541.2</v>
       </c>
       <c r="L124">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="M124">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="N124" t="s">
         <v>3</v>
@@ -5936,34 +5936,34 @@
         <v>76</v>
       </c>
       <c r="D125" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E125" t="s">
         <v>3</v>
       </c>
       <c r="F125">
-        <v>-197607.1</v>
+        <v>-233535.7</v>
       </c>
       <c r="G125">
+        <v>-15000</v>
+      </c>
+      <c r="H125">
+        <v>4486.1</v>
+      </c>
+      <c r="I125">
+        <v>-233535.7</v>
+      </c>
+      <c r="J125">
         <v>15000</v>
       </c>
-      <c r="H125">
-        <v>74043.9</v>
-      </c>
-      <c r="I125">
-        <v>-215571.4</v>
-      </c>
-      <c r="J125">
-        <v>-15000</v>
-      </c>
       <c r="K125">
-        <v>63142.2</v>
+        <v>4486.1</v>
       </c>
       <c r="L125">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="M125">
-        <v>2913.9</v>
+        <v>3000</v>
       </c>
       <c r="N125" t="s">
         <v>3</v>
@@ -5980,34 +5980,34 @@
         <v>76</v>
       </c>
       <c r="D126" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E126" t="s">
         <v>3</v>
       </c>
       <c r="F126">
-        <v>-215571.4</v>
+        <v>-239523.8</v>
       </c>
       <c r="G126">
         <v>-15000</v>
       </c>
       <c r="H126">
-        <v>63142.2</v>
+        <v>38882.2</v>
       </c>
       <c r="I126">
-        <v>-233535.7</v>
+        <v>-239523.8</v>
       </c>
       <c r="J126">
         <v>15000</v>
       </c>
       <c r="K126">
-        <v>43253.9</v>
+        <v>38882.2</v>
       </c>
       <c r="L126">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="M126">
-        <v>2913.9</v>
+        <v>2900</v>
       </c>
       <c r="N126" t="s">
         <v>3</v>
@@ -6024,34 +6024,34 @@
         <v>76</v>
       </c>
       <c r="D127" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E127" t="s">
         <v>3</v>
       </c>
       <c r="F127">
-        <v>-17964.3</v>
+        <v>-239523.8</v>
       </c>
       <c r="G127">
         <v>-15000</v>
       </c>
       <c r="H127">
-        <v>104996.7</v>
+        <v>-247.1</v>
       </c>
       <c r="I127">
-        <v>-17964.3</v>
+        <v>-239523.8</v>
       </c>
       <c r="J127">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="K127">
-        <v>35950</v>
+        <v>-247.1</v>
       </c>
       <c r="L127">
-        <v>2178.6</v>
+        <v>3000</v>
       </c>
       <c r="M127">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="N127" t="s">
         <v>3</v>
@@ -6068,34 +6068,34 @@
         <v>76</v>
       </c>
       <c r="D128" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E128" t="s">
         <v>3</v>
       </c>
       <c r="F128">
-        <v>-17964.3</v>
+        <v>-245511.9</v>
       </c>
       <c r="G128">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H128">
-        <v>104996.7</v>
+        <v>26363.1</v>
       </c>
       <c r="I128">
-        <v>-17964.3</v>
+        <v>-245511.9</v>
       </c>
       <c r="J128">
         <v>15000</v>
       </c>
       <c r="K128">
-        <v>35950</v>
+        <v>26363.1</v>
       </c>
       <c r="L128">
-        <v>2178.6</v>
+        <v>2900</v>
       </c>
       <c r="M128">
-        <v>100</v>
+        <v>2900</v>
       </c>
       <c r="N128" t="s">
         <v>3</v>
@@ -6112,34 +6112,34 @@
         <v>76</v>
       </c>
       <c r="D129" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E129" t="s">
         <v>3</v>
       </c>
       <c r="F129">
-        <v>-35928.6</v>
+        <v>-245511.9</v>
       </c>
       <c r="G129">
         <v>-15000</v>
       </c>
       <c r="H129">
-        <v>102506.3</v>
+        <v>-5076</v>
       </c>
       <c r="I129">
-        <v>-35928.6</v>
+        <v>-245511.9</v>
       </c>
       <c r="J129">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="K129">
-        <v>35950</v>
+        <v>-5076</v>
       </c>
       <c r="L129">
-        <v>2230.8</v>
+        <v>3000</v>
       </c>
       <c r="M129">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="N129" t="s">
         <v>3</v>
@@ -6156,34 +6156,34 @@
         <v>76</v>
       </c>
       <c r="D130" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E130" t="s">
         <v>3</v>
       </c>
       <c r="F130">
-        <v>-35928.6</v>
+        <v>-251500</v>
       </c>
       <c r="G130">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H130">
-        <v>102506.3</v>
+        <v>10000</v>
       </c>
       <c r="I130">
-        <v>-35928.6</v>
+        <v>-251500</v>
       </c>
       <c r="J130">
         <v>15000</v>
       </c>
       <c r="K130">
-        <v>35950</v>
+        <v>10000</v>
       </c>
       <c r="L130">
-        <v>2230.8</v>
+        <v>2900</v>
       </c>
       <c r="M130">
-        <v>100</v>
+        <v>2900</v>
       </c>
       <c r="N130" t="s">
         <v>3</v>
@@ -6200,34 +6200,34 @@
         <v>76</v>
       </c>
       <c r="D131" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E131" t="s">
         <v>3</v>
       </c>
       <c r="F131">
-        <v>-53892.9</v>
+        <v>-251500</v>
       </c>
       <c r="G131">
         <v>-15000</v>
       </c>
       <c r="H131">
-        <v>98751.5</v>
+        <v>-10000</v>
       </c>
       <c r="I131">
-        <v>-53892.9</v>
+        <v>-251500</v>
       </c>
       <c r="J131">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="K131">
-        <v>35950</v>
+        <v>-10000</v>
       </c>
       <c r="L131">
-        <v>2285.7</v>
+        <v>3000</v>
       </c>
       <c r="M131">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="N131" t="s">
         <v>3</v>
@@ -6244,34 +6244,34 @@
         <v>76</v>
       </c>
       <c r="D132" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E132" t="s">
         <v>3</v>
       </c>
       <c r="F132">
-        <v>-53892.9</v>
+        <v>0</v>
       </c>
       <c r="G132">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H132">
-        <v>98751.5</v>
+        <v>118898.7</v>
       </c>
       <c r="I132">
-        <v>-53892.9</v>
+        <v>-17964.3</v>
       </c>
       <c r="J132">
         <v>15000</v>
       </c>
       <c r="K132">
-        <v>35950</v>
+        <v>118154.9</v>
       </c>
       <c r="L132">
-        <v>2285.7</v>
+        <v>2913.9</v>
       </c>
       <c r="M132">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N132" t="s">
         <v>3</v>
@@ -6288,34 +6288,34 @@
         <v>76</v>
       </c>
       <c r="D133" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E133" t="s">
         <v>3</v>
       </c>
       <c r="F133">
-        <v>-71857.1</v>
+        <v>-17964.3</v>
       </c>
       <c r="G133">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H133">
-        <v>93834.3</v>
+        <v>118154.9</v>
       </c>
       <c r="I133">
-        <v>-71857.1</v>
+        <v>-35928.6</v>
       </c>
       <c r="J133">
         <v>-15000</v>
       </c>
       <c r="K133">
-        <v>35950</v>
+        <v>116453</v>
       </c>
       <c r="L133">
-        <v>2343.4</v>
+        <v>2913.9</v>
       </c>
       <c r="M133">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N133" t="s">
         <v>3</v>
@@ -6332,34 +6332,34 @@
         <v>76</v>
       </c>
       <c r="D134" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E134" t="s">
         <v>3</v>
       </c>
       <c r="F134">
-        <v>-71857.1</v>
+        <v>-35928.6</v>
       </c>
       <c r="G134">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H134">
-        <v>93834.3</v>
+        <v>116453</v>
       </c>
       <c r="I134">
-        <v>-71857.1</v>
+        <v>-53892.9</v>
       </c>
       <c r="J134">
         <v>15000</v>
       </c>
       <c r="K134">
-        <v>35950</v>
+        <v>114016.3</v>
       </c>
       <c r="L134">
-        <v>2343.4</v>
+        <v>2913.9</v>
       </c>
       <c r="M134">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N134" t="s">
         <v>3</v>
@@ -6376,34 +6376,34 @@
         <v>76</v>
       </c>
       <c r="D135" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E135" t="s">
         <v>3</v>
       </c>
       <c r="F135">
-        <v>-89821.4</v>
+        <v>-53892.9</v>
       </c>
       <c r="G135">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H135">
-        <v>87820.9</v>
+        <v>114016.3</v>
       </c>
       <c r="I135">
-        <v>-89821.4</v>
+        <v>-71857.1</v>
       </c>
       <c r="J135">
         <v>-15000</v>
       </c>
       <c r="K135">
-        <v>35950</v>
+        <v>110946.9</v>
       </c>
       <c r="L135">
-        <v>2403.5</v>
+        <v>2913.9</v>
       </c>
       <c r="M135">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N135" t="s">
         <v>3</v>
@@ -6420,19 +6420,19 @@
         <v>76</v>
       </c>
       <c r="D136" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E136" t="s">
         <v>3</v>
       </c>
       <c r="F136">
-        <v>-89821.4</v>
+        <v>-71857.1</v>
       </c>
       <c r="G136">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H136">
-        <v>87820.9</v>
+        <v>110946.9</v>
       </c>
       <c r="I136">
         <v>-89821.4</v>
@@ -6441,13 +6441,13 @@
         <v>15000</v>
       </c>
       <c r="K136">
-        <v>35950</v>
+        <v>107311.5</v>
       </c>
       <c r="L136">
-        <v>2403.5</v>
+        <v>2913.9</v>
       </c>
       <c r="M136">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N136" t="s">
         <v>3</v>
@@ -6464,19 +6464,19 @@
         <v>76</v>
       </c>
       <c r="D137" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E137" t="s">
         <v>3</v>
       </c>
       <c r="F137">
-        <v>-107785.7</v>
+        <v>-89821.4</v>
       </c>
       <c r="G137">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H137">
-        <v>80759.4</v>
+        <v>107311.5</v>
       </c>
       <c r="I137">
         <v>-107785.7</v>
@@ -6485,13 +6485,13 @@
         <v>-15000</v>
       </c>
       <c r="K137">
-        <v>35950</v>
+        <v>103158</v>
       </c>
       <c r="L137">
-        <v>2465.9</v>
+        <v>2913.9</v>
       </c>
       <c r="M137">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N137" t="s">
         <v>3</v>
@@ -6508,7 +6508,7 @@
         <v>76</v>
       </c>
       <c r="D138" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E138" t="s">
         <v>3</v>
@@ -6517,25 +6517,25 @@
         <v>-107785.7</v>
       </c>
       <c r="G138">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H138">
-        <v>80759.4</v>
+        <v>103158</v>
       </c>
       <c r="I138">
-        <v>-107785.7</v>
+        <v>-125750</v>
       </c>
       <c r="J138">
         <v>15000</v>
       </c>
       <c r="K138">
-        <v>35950</v>
+        <v>98522.7</v>
       </c>
       <c r="L138">
-        <v>2465.9</v>
+        <v>2913.9</v>
       </c>
       <c r="M138">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N138" t="s">
         <v>3</v>
@@ -6552,7 +6552,7 @@
         <v>76</v>
       </c>
       <c r="D139" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E139" t="s">
         <v>3</v>
@@ -6561,25 +6561,25 @@
         <v>-125750</v>
       </c>
       <c r="G139">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H139">
-        <v>72687.7</v>
+        <v>98522.7</v>
       </c>
       <c r="I139">
-        <v>-125750</v>
+        <v>-143714.3</v>
       </c>
       <c r="J139">
         <v>-15000</v>
       </c>
       <c r="K139">
-        <v>35950</v>
+        <v>93425.6</v>
       </c>
       <c r="L139">
-        <v>2530.3</v>
+        <v>2913.9</v>
       </c>
       <c r="M139">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N139" t="s">
         <v>3</v>
@@ -6596,34 +6596,34 @@
         <v>76</v>
       </c>
       <c r="D140" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E140" t="s">
         <v>3</v>
       </c>
       <c r="F140">
-        <v>-125750</v>
+        <v>-143714.3</v>
       </c>
       <c r="G140">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H140">
-        <v>72687.7</v>
+        <v>93425.6</v>
       </c>
       <c r="I140">
-        <v>-125750</v>
+        <v>-161678.6</v>
       </c>
       <c r="J140">
         <v>15000</v>
       </c>
       <c r="K140">
-        <v>35950</v>
+        <v>87842.1</v>
       </c>
       <c r="L140">
-        <v>2530.3</v>
+        <v>2913.9</v>
       </c>
       <c r="M140">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N140" t="s">
         <v>3</v>
@@ -6640,34 +6640,34 @@
         <v>76</v>
       </c>
       <c r="D141" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E141" t="s">
         <v>3</v>
       </c>
       <c r="F141">
-        <v>-143714.3</v>
+        <v>-161678.6</v>
       </c>
       <c r="G141">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H141">
-        <v>63636.7</v>
+        <v>87842.1</v>
       </c>
       <c r="I141">
-        <v>-143714.3</v>
+        <v>-179642.9</v>
       </c>
       <c r="J141">
         <v>-15000</v>
       </c>
       <c r="K141">
-        <v>35950</v>
+        <v>81598.1</v>
       </c>
       <c r="L141">
-        <v>2596.5</v>
+        <v>2913.9</v>
       </c>
       <c r="M141">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N141" t="s">
         <v>3</v>
@@ -6684,34 +6684,34 @@
         <v>76</v>
       </c>
       <c r="D142" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E142" t="s">
         <v>3</v>
       </c>
       <c r="F142">
-        <v>-143714.3</v>
+        <v>-179642.9</v>
       </c>
       <c r="G142">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H142">
-        <v>63636.7</v>
+        <v>81598.1</v>
       </c>
       <c r="I142">
-        <v>-143714.3</v>
+        <v>-197607.1</v>
       </c>
       <c r="J142">
         <v>15000</v>
       </c>
       <c r="K142">
-        <v>35950</v>
+        <v>74043.9</v>
       </c>
       <c r="L142">
-        <v>2596.5</v>
+        <v>2913.9</v>
       </c>
       <c r="M142">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N142" t="s">
         <v>3</v>
@@ -6728,34 +6728,34 @@
         <v>76</v>
       </c>
       <c r="D143" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E143" t="s">
         <v>3</v>
       </c>
       <c r="F143">
-        <v>-161678.6</v>
+        <v>-197607.1</v>
       </c>
       <c r="G143">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H143">
-        <v>53632.2</v>
+        <v>74043.9</v>
       </c>
       <c r="I143">
-        <v>-161678.6</v>
+        <v>-215571.4</v>
       </c>
       <c r="J143">
         <v>-15000</v>
       </c>
       <c r="K143">
-        <v>35950</v>
+        <v>63326.2</v>
       </c>
       <c r="L143">
-        <v>2664.2</v>
+        <v>2913.9</v>
       </c>
       <c r="M143">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N143" t="s">
         <v>3</v>
@@ -6772,34 +6772,34 @@
         <v>76</v>
       </c>
       <c r="D144" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E144" t="s">
         <v>3</v>
       </c>
       <c r="F144">
-        <v>-161678.6</v>
+        <v>-215571.4</v>
       </c>
       <c r="G144">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H144">
-        <v>53632.2</v>
+        <v>63326.2</v>
       </c>
       <c r="I144">
-        <v>-161678.6</v>
+        <v>-224553.6</v>
       </c>
       <c r="J144">
         <v>15000</v>
       </c>
       <c r="K144">
-        <v>35950</v>
+        <v>55256.9</v>
       </c>
       <c r="L144">
-        <v>2664.2</v>
+        <v>2913.9</v>
       </c>
       <c r="M144">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N144" t="s">
         <v>3</v>
@@ -6816,34 +6816,34 @@
         <v>76</v>
       </c>
       <c r="D145" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E145" t="s">
         <v>3</v>
       </c>
       <c r="F145">
-        <v>-179642.9</v>
+        <v>-224553.6</v>
       </c>
       <c r="G145">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H145">
-        <v>42696.5</v>
+        <v>55256.9</v>
       </c>
       <c r="I145">
-        <v>-179642.9</v>
+        <v>-233535.7</v>
       </c>
       <c r="J145">
         <v>-15000</v>
       </c>
       <c r="K145">
-        <v>35950</v>
+        <v>44004.6</v>
       </c>
       <c r="L145">
-        <v>2733.2</v>
+        <v>2913.9</v>
       </c>
       <c r="M145">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N145" t="s">
         <v>3</v>
@@ -6860,34 +6860,34 @@
         <v>76</v>
       </c>
       <c r="D146" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E146" t="s">
         <v>3</v>
       </c>
       <c r="F146">
-        <v>-179642.9</v>
+        <v>-239523.8</v>
       </c>
       <c r="G146">
         <v>15000</v>
       </c>
       <c r="H146">
-        <v>42696.5</v>
+        <v>33674.2</v>
       </c>
       <c r="I146">
-        <v>-179642.9</v>
+        <v>-245511.9</v>
       </c>
       <c r="J146">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K146">
-        <v>35950</v>
+        <v>20207.4</v>
       </c>
       <c r="L146">
-        <v>2733.2</v>
+        <v>2913.9</v>
       </c>
       <c r="M146">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N146" t="s">
         <v>3</v>
@@ -6904,34 +6904,34 @@
         <v>76</v>
       </c>
       <c r="D147" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E147" t="s">
         <v>3</v>
       </c>
       <c r="F147">
-        <v>-215571.4</v>
+        <v>-245511.9</v>
       </c>
       <c r="G147">
         <v>-15000</v>
       </c>
       <c r="H147">
-        <v>18107.1</v>
+        <v>20207.4</v>
       </c>
       <c r="I147">
-        <v>-215571.4</v>
+        <v>-251500</v>
       </c>
       <c r="J147">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="K147">
-        <v>33550</v>
+        <v>3844.3</v>
       </c>
       <c r="L147">
-        <v>3064.2</v>
+        <v>2913.9</v>
       </c>
       <c r="M147">
-        <v>100</v>
+        <v>2913.9</v>
       </c>
       <c r="N147" t="s">
         <v>3</v>
@@ -6948,31 +6948,31 @@
         <v>76</v>
       </c>
       <c r="D148" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E148" t="s">
         <v>3</v>
       </c>
       <c r="F148">
-        <v>-215571.4</v>
+        <v>-17964.3</v>
       </c>
       <c r="G148">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H148">
-        <v>18107.1</v>
+        <v>104996.7</v>
       </c>
       <c r="I148">
-        <v>-215571.4</v>
+        <v>-17964.3</v>
       </c>
       <c r="J148">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K148">
-        <v>33550</v>
+        <v>35950</v>
       </c>
       <c r="L148">
-        <v>3064.2</v>
+        <v>2153.8</v>
       </c>
       <c r="M148">
         <v>100</v>
@@ -6998,25 +6998,25 @@
         <v>3</v>
       </c>
       <c r="F149">
-        <v>-233535.7</v>
+        <v>-17964.3</v>
       </c>
       <c r="G149">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H149">
-        <v>48541.2</v>
+        <v>104996.7</v>
       </c>
       <c r="I149">
-        <v>-233535.7</v>
+        <v>-17964.3</v>
       </c>
       <c r="J149">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="K149">
         <v>35950</v>
       </c>
       <c r="L149">
-        <v>5152.7</v>
+        <v>2153.8</v>
       </c>
       <c r="M149">
         <v>100</v>
@@ -7042,25 +7042,25 @@
         <v>3</v>
       </c>
       <c r="F150">
-        <v>-233535.7</v>
+        <v>-35928.6</v>
       </c>
       <c r="G150">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H150">
-        <v>48541.2</v>
+        <v>102506.3</v>
       </c>
       <c r="I150">
-        <v>-233535.7</v>
+        <v>-35928.6</v>
       </c>
       <c r="J150">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K150">
         <v>35950</v>
       </c>
       <c r="L150">
-        <v>5152.7</v>
+        <v>2204.6</v>
       </c>
       <c r="M150">
         <v>100</v>
@@ -7080,31 +7080,31 @@
         <v>76</v>
       </c>
       <c r="D151" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E151" t="s">
         <v>3</v>
       </c>
       <c r="F151">
-        <v>-251500</v>
+        <v>-35928.6</v>
       </c>
       <c r="G151">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H151">
-        <v>10000</v>
+        <v>102506.3</v>
       </c>
       <c r="I151">
-        <v>-251500</v>
+        <v>-35928.6</v>
       </c>
       <c r="J151">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="K151">
-        <v>33550</v>
+        <v>35950</v>
       </c>
       <c r="L151">
-        <v>5689.1</v>
+        <v>2204.6</v>
       </c>
       <c r="M151">
         <v>100</v>
@@ -7124,31 +7124,31 @@
         <v>76</v>
       </c>
       <c r="D152" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E152" t="s">
         <v>3</v>
       </c>
       <c r="F152">
-        <v>-251500</v>
+        <v>-53892.9</v>
       </c>
       <c r="G152">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="H152">
-        <v>10000</v>
+        <v>98751.5</v>
       </c>
       <c r="I152">
-        <v>-251500</v>
+        <v>-53892.9</v>
       </c>
       <c r="J152">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K152">
-        <v>33550</v>
+        <v>35950</v>
       </c>
       <c r="L152">
-        <v>5689.1</v>
+        <v>2258.1</v>
       </c>
       <c r="M152">
         <v>100</v>
@@ -7157,57 +7157,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B153" s="3" t="s">
-        <v>48</v>
+      <c r="B153" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C153" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="D153" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E153" t="s">
-        <v>50</v>
-      </c>
-      <c r="F153" t="s">
-        <v>66</v>
-      </c>
-      <c r="G153" t="s">
-        <v>67</v>
-      </c>
-      <c r="H153" t="s">
-        <v>68</v>
-      </c>
-      <c r="I153" t="s">
-        <v>69</v>
-      </c>
-      <c r="J153" t="s">
-        <v>70</v>
-      </c>
-      <c r="K153" t="s">
-        <v>71</v>
-      </c>
-      <c r="L153" t="s">
-        <v>72</v>
-      </c>
-      <c r="M153" t="s">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="F153">
+        <v>-53892.9</v>
+      </c>
+      <c r="G153">
+        <v>15000</v>
+      </c>
+      <c r="H153">
+        <v>98751.5</v>
+      </c>
+      <c r="I153">
+        <v>-53892.9</v>
+      </c>
+      <c r="J153">
+        <v>15000</v>
+      </c>
+      <c r="K153">
+        <v>35950</v>
+      </c>
+      <c r="L153">
+        <v>2258.1</v>
+      </c>
+      <c r="M153">
+        <v>100</v>
       </c>
       <c r="N153" t="s">
-        <v>61</v>
-      </c>
-      <c r="O153" t="s">
-        <v>62</v>
-      </c>
-      <c r="P153" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>3</v>
       </c>
@@ -7218,80 +7212,169 @@
         <v>76</v>
       </c>
       <c r="D154" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="E154" t="s">
-        <v>77</v>
-      </c>
-      <c r="F154" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="F154">
+        <v>-71857.1</v>
+      </c>
+      <c r="G154">
+        <v>-15000</v>
+      </c>
+      <c r="H154">
+        <v>93834.3</v>
+      </c>
+      <c r="I154">
+        <v>-71857.1</v>
+      </c>
+      <c r="J154">
+        <v>-15000</v>
+      </c>
+      <c r="K154">
+        <v>35950</v>
+      </c>
+      <c r="L154">
+        <v>2314.3</v>
+      </c>
+      <c r="M154">
+        <v>100</v>
+      </c>
+      <c r="N154" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C155" t="s">
+        <v>76</v>
+      </c>
+      <c r="D155" t="s">
+        <v>31</v>
+      </c>
+      <c r="E155" t="s">
+        <v>3</v>
+      </c>
+      <c r="F155">
+        <v>-71857.1</v>
+      </c>
+      <c r="G155">
+        <v>15000</v>
+      </c>
+      <c r="H155">
+        <v>93834.3</v>
+      </c>
+      <c r="I155">
+        <v>-71857.1</v>
+      </c>
+      <c r="J155">
+        <v>15000</v>
+      </c>
+      <c r="K155">
+        <v>35950</v>
+      </c>
+      <c r="L155">
+        <v>2314.3</v>
+      </c>
+      <c r="M155">
+        <v>100</v>
+      </c>
+      <c r="N155" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B156" s="3" t="s">
-        <v>45</v>
+      <c r="B156" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C156" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="D156" t="s">
+        <v>31</v>
+      </c>
+      <c r="E156" t="s">
+        <v>3</v>
+      </c>
+      <c r="F156">
+        <v>-89821.4</v>
+      </c>
+      <c r="G156">
+        <v>-15000</v>
+      </c>
+      <c r="H156">
+        <v>87820.9</v>
+      </c>
+      <c r="I156">
+        <v>-89821.4</v>
+      </c>
+      <c r="J156">
+        <v>-15000</v>
+      </c>
+      <c r="K156">
+        <v>35950</v>
+      </c>
+      <c r="L156">
+        <v>2373.2</v>
+      </c>
+      <c r="M156">
+        <v>100</v>
+      </c>
+      <c r="N156" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>48</v>
+        <v>3</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C157" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="D157" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E157" t="s">
-        <v>50</v>
-      </c>
-      <c r="F157" t="s">
-        <v>51</v>
-      </c>
-      <c r="G157" t="s">
-        <v>52</v>
-      </c>
-      <c r="H157" t="s">
-        <v>53</v>
-      </c>
-      <c r="I157" t="s">
-        <v>54</v>
-      </c>
-      <c r="J157" t="s">
-        <v>55</v>
-      </c>
-      <c r="K157" t="s">
-        <v>56</v>
-      </c>
-      <c r="L157" t="s">
-        <v>57</v>
-      </c>
-      <c r="M157" t="s">
-        <v>58</v>
+        <v>3</v>
+      </c>
+      <c r="F157">
+        <v>-89821.4</v>
+      </c>
+      <c r="G157">
+        <v>15000</v>
+      </c>
+      <c r="H157">
+        <v>87820.9</v>
+      </c>
+      <c r="I157">
+        <v>-89821.4</v>
+      </c>
+      <c r="J157">
+        <v>15000</v>
+      </c>
+      <c r="K157">
+        <v>35950</v>
+      </c>
+      <c r="L157">
+        <v>2373.2</v>
+      </c>
+      <c r="M157">
+        <v>100</v>
       </c>
       <c r="N157" t="s">
-        <v>59</v>
-      </c>
-      <c r="O157" t="s">
-        <v>60</v>
-      </c>
-      <c r="P157" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>62</v>
-      </c>
-      <c r="R157" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.25">
@@ -7302,37 +7385,37 @@
         <v>64</v>
       </c>
       <c r="C158" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D158" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E158" t="s">
         <v>3</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>-107785.7</v>
       </c>
       <c r="G158">
         <v>-15000</v>
       </c>
       <c r="H158">
-        <v>106000</v>
+        <v>80759.4</v>
       </c>
       <c r="I158">
-        <v>0</v>
+        <v>-107785.7</v>
       </c>
       <c r="J158">
         <v>-15000</v>
       </c>
       <c r="K158">
-        <v>122000</v>
+        <v>35950</v>
       </c>
       <c r="L158">
-        <v>2147.3</v>
+        <v>2434.5</v>
       </c>
       <c r="M158">
-        <v>2034.2</v>
+        <v>100</v>
       </c>
       <c r="N158" t="s">
         <v>3</v>
@@ -7346,37 +7429,37 @@
         <v>64</v>
       </c>
       <c r="C159" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D159" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E159" t="s">
         <v>3</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>-107785.7</v>
       </c>
       <c r="G159">
         <v>15000</v>
       </c>
       <c r="H159">
-        <v>106000</v>
+        <v>80759.4</v>
       </c>
       <c r="I159">
-        <v>0</v>
+        <v>-107785.7</v>
       </c>
       <c r="J159">
         <v>15000</v>
       </c>
       <c r="K159">
-        <v>122000</v>
+        <v>35950</v>
       </c>
       <c r="L159">
-        <v>2147.3</v>
+        <v>2434.5</v>
       </c>
       <c r="M159">
-        <v>2034.2</v>
+        <v>100</v>
       </c>
       <c r="N159" t="s">
         <v>3</v>
@@ -7390,37 +7473,37 @@
         <v>64</v>
       </c>
       <c r="C160" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D160" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E160" t="s">
         <v>3</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>-125750</v>
       </c>
       <c r="G160">
         <v>-15000</v>
       </c>
       <c r="H160">
-        <v>122000</v>
+        <v>72687.7</v>
       </c>
       <c r="I160">
-        <v>0</v>
+        <v>-125750</v>
       </c>
       <c r="J160">
-        <v>15000</v>
+        <v>-15000</v>
       </c>
       <c r="K160">
-        <v>122000</v>
+        <v>35950</v>
       </c>
       <c r="L160">
-        <v>2900</v>
+        <v>2498</v>
       </c>
       <c r="M160">
-        <v>2900</v>
+        <v>100</v>
       </c>
       <c r="N160" t="s">
         <v>3</v>
@@ -7434,37 +7517,37 @@
         <v>64</v>
       </c>
       <c r="C161" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D161" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E161" t="s">
         <v>3</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>-125750</v>
       </c>
       <c r="G161">
-        <v>-15000</v>
+        <v>15000</v>
       </c>
       <c r="H161">
-        <v>106000</v>
+        <v>72687.7</v>
       </c>
       <c r="I161">
-        <v>0</v>
+        <v>-125750</v>
       </c>
       <c r="J161">
         <v>15000</v>
       </c>
       <c r="K161">
-        <v>106000</v>
+        <v>35950</v>
       </c>
       <c r="L161">
-        <v>3000</v>
+        <v>2498</v>
       </c>
       <c r="M161">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="N161" t="s">
         <v>3</v>
@@ -7478,7 +7561,7 @@
         <v>64</v>
       </c>
       <c r="C162" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D162" t="s">
         <v>31</v>
@@ -7487,16 +7570,16 @@
         <v>3</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>-143714.3</v>
       </c>
       <c r="G162">
         <v>-15000</v>
       </c>
       <c r="H162">
-        <v>106000</v>
+        <v>63636.7</v>
       </c>
       <c r="I162">
-        <v>0</v>
+        <v>-143714.3</v>
       </c>
       <c r="J162">
         <v>-15000</v>
@@ -7505,7 +7588,7 @@
         <v>35950</v>
       </c>
       <c r="L162">
-        <v>2127.8</v>
+        <v>2563.2</v>
       </c>
       <c r="M162">
         <v>100</v>
@@ -7522,7 +7605,7 @@
         <v>64</v>
       </c>
       <c r="C163" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D163" t="s">
         <v>31</v>
@@ -7531,16 +7614,16 @@
         <v>3</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>-143714.3</v>
       </c>
       <c r="G163">
         <v>15000</v>
       </c>
       <c r="H163">
-        <v>106000</v>
+        <v>63636.7</v>
       </c>
       <c r="I163">
-        <v>0</v>
+        <v>-143714.3</v>
       </c>
       <c r="J163">
         <v>15000</v>
@@ -7549,7 +7632,7 @@
         <v>35950</v>
       </c>
       <c r="L163">
-        <v>2127.8</v>
+        <v>2563.2</v>
       </c>
       <c r="M163">
         <v>100</v>
@@ -7558,57 +7641,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B164" s="3" t="s">
-        <v>48</v>
+      <c r="B164" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C164" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="D164" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E164" t="s">
-        <v>50</v>
-      </c>
-      <c r="F164" t="s">
-        <v>66</v>
-      </c>
-      <c r="G164" t="s">
-        <v>67</v>
-      </c>
-      <c r="H164" t="s">
-        <v>68</v>
-      </c>
-      <c r="I164" t="s">
-        <v>69</v>
-      </c>
-      <c r="J164" t="s">
-        <v>70</v>
-      </c>
-      <c r="K164" t="s">
-        <v>71</v>
-      </c>
-      <c r="L164" t="s">
-        <v>72</v>
-      </c>
-      <c r="M164" t="s">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="F164">
+        <v>-161678.6</v>
+      </c>
+      <c r="G164">
+        <v>-15000</v>
+      </c>
+      <c r="H164">
+        <v>53632.2</v>
+      </c>
+      <c r="I164">
+        <v>-161678.6</v>
+      </c>
+      <c r="J164">
+        <v>-15000</v>
+      </c>
+      <c r="K164">
+        <v>35950</v>
+      </c>
+      <c r="L164">
+        <v>2630.2</v>
+      </c>
+      <c r="M164">
+        <v>100</v>
       </c>
       <c r="N164" t="s">
-        <v>61</v>
-      </c>
-      <c r="O164" t="s">
-        <v>62</v>
-      </c>
-      <c r="P164" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>3</v>
       </c>
@@ -7616,83 +7693,172 @@
         <v>64</v>
       </c>
       <c r="C165" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D165" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="E165" t="s">
-        <v>81</v>
-      </c>
-      <c r="F165" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="F165">
+        <v>-161678.6</v>
+      </c>
+      <c r="G165">
+        <v>15000</v>
+      </c>
+      <c r="H165">
+        <v>53632.2</v>
+      </c>
+      <c r="I165">
+        <v>-161678.6</v>
+      </c>
+      <c r="J165">
+        <v>15000</v>
+      </c>
+      <c r="K165">
+        <v>35950</v>
+      </c>
+      <c r="L165">
+        <v>2630.2</v>
+      </c>
+      <c r="M165">
+        <v>100</v>
+      </c>
+      <c r="N165" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C166" t="s">
+        <v>76</v>
+      </c>
+      <c r="D166" t="s">
+        <v>31</v>
+      </c>
+      <c r="E166" t="s">
+        <v>3</v>
+      </c>
+      <c r="F166">
+        <v>-179642.9</v>
+      </c>
+      <c r="G166">
+        <v>-15000</v>
+      </c>
+      <c r="H166">
+        <v>42696.5</v>
+      </c>
+      <c r="I166">
+        <v>-179642.9</v>
+      </c>
+      <c r="J166">
+        <v>-15000</v>
+      </c>
+      <c r="K166">
+        <v>35950</v>
+      </c>
+      <c r="L166">
+        <v>2698.6</v>
+      </c>
+      <c r="M166">
+        <v>100</v>
+      </c>
+      <c r="N166" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B167" s="3" t="s">
-        <v>45</v>
+      <c r="B167" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C167" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="D167" t="s">
+        <v>31</v>
+      </c>
+      <c r="E167" t="s">
+        <v>3</v>
+      </c>
+      <c r="F167">
+        <v>-179642.9</v>
+      </c>
+      <c r="G167">
+        <v>15000</v>
+      </c>
+      <c r="H167">
+        <v>42696.5</v>
+      </c>
+      <c r="I167">
+        <v>-179642.9</v>
+      </c>
+      <c r="J167">
+        <v>15000</v>
+      </c>
+      <c r="K167">
+        <v>35950</v>
+      </c>
+      <c r="L167">
+        <v>2698.6</v>
+      </c>
+      <c r="M167">
+        <v>100</v>
+      </c>
+      <c r="N167" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>48</v>
+        <v>3</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C168" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="D168" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E168" t="s">
-        <v>50</v>
-      </c>
-      <c r="F168" t="s">
-        <v>51</v>
-      </c>
-      <c r="G168" t="s">
-        <v>52</v>
-      </c>
-      <c r="H168" t="s">
-        <v>53</v>
-      </c>
-      <c r="I168" t="s">
-        <v>54</v>
-      </c>
-      <c r="J168" t="s">
-        <v>55</v>
-      </c>
-      <c r="K168" t="s">
-        <v>56</v>
-      </c>
-      <c r="L168" t="s">
-        <v>57</v>
-      </c>
-      <c r="M168" t="s">
-        <v>58</v>
+        <v>3</v>
+      </c>
+      <c r="F168">
+        <v>-215571.4</v>
+      </c>
+      <c r="G168">
+        <v>-15000</v>
+      </c>
+      <c r="H168">
+        <v>18107.1</v>
+      </c>
+      <c r="I168">
+        <v>-215571.4</v>
+      </c>
+      <c r="J168">
+        <v>-15000</v>
+      </c>
+      <c r="K168">
+        <v>33550</v>
+      </c>
+      <c r="L168">
+        <v>3022.4</v>
+      </c>
+      <c r="M168">
+        <v>100</v>
       </c>
       <c r="N168" t="s">
-        <v>59</v>
-      </c>
-      <c r="O168" t="s">
-        <v>60</v>
-      </c>
-      <c r="P168" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q168" t="s">
-        <v>62</v>
-      </c>
-      <c r="R168" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
@@ -7703,37 +7869,37 @@
         <v>64</v>
       </c>
       <c r="C169" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D169" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E169" t="s">
         <v>3</v>
       </c>
       <c r="F169">
-        <v>-574857.1</v>
+        <v>-215571.4</v>
       </c>
       <c r="G169">
-        <v>-13000</v>
+        <v>15000</v>
       </c>
       <c r="H169">
-        <v>34750</v>
+        <v>18107.1</v>
       </c>
       <c r="I169">
-        <v>-574857.1</v>
+        <v>-215571.4</v>
       </c>
       <c r="J169">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="K169">
-        <v>34750</v>
-      </c>
-      <c r="L169" t="s">
-        <v>3</v>
-      </c>
-      <c r="M169" t="s">
-        <v>3</v>
+        <v>33550</v>
+      </c>
+      <c r="L169">
+        <v>3022.4</v>
+      </c>
+      <c r="M169">
+        <v>100</v>
       </c>
       <c r="N169" t="s">
         <v>3</v>
@@ -7747,37 +7913,37 @@
         <v>64</v>
       </c>
       <c r="C170" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D170" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E170" t="s">
         <v>3</v>
       </c>
       <c r="F170">
-        <v>-574857.1</v>
+        <v>-233535.7</v>
       </c>
       <c r="G170">
-        <v>-19200</v>
+        <v>-15000</v>
       </c>
       <c r="H170">
-        <v>34750</v>
+        <v>48541.2</v>
       </c>
       <c r="I170">
-        <v>-574857.1</v>
+        <v>-233535.7</v>
       </c>
       <c r="J170">
-        <v>-24400</v>
+        <v>-15000</v>
       </c>
       <c r="K170">
-        <v>34750</v>
-      </c>
-      <c r="L170" t="s">
-        <v>3</v>
-      </c>
-      <c r="M170" t="s">
-        <v>3</v>
+        <v>35950</v>
+      </c>
+      <c r="L170">
+        <v>3816.2</v>
+      </c>
+      <c r="M170">
+        <v>100</v>
       </c>
       <c r="N170" t="s">
         <v>3</v>
@@ -7791,37 +7957,37 @@
         <v>64</v>
       </c>
       <c r="C171" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D171" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E171" t="s">
         <v>3</v>
       </c>
       <c r="F171">
-        <v>-574857.1</v>
+        <v>-233535.7</v>
       </c>
       <c r="G171">
-        <v>19200</v>
+        <v>15000</v>
       </c>
       <c r="H171">
-        <v>34750</v>
+        <v>48541.2</v>
       </c>
       <c r="I171">
-        <v>-574857.1</v>
+        <v>-233535.7</v>
       </c>
       <c r="J171">
-        <v>24400</v>
+        <v>15000</v>
       </c>
       <c r="K171">
-        <v>34750</v>
-      </c>
-      <c r="L171" t="s">
-        <v>3</v>
-      </c>
-      <c r="M171" t="s">
-        <v>3</v>
+        <v>35950</v>
+      </c>
+      <c r="L171">
+        <v>3816.2</v>
+      </c>
+      <c r="M171">
+        <v>100</v>
       </c>
       <c r="N171" t="s">
         <v>3</v>
@@ -7835,37 +8001,37 @@
         <v>64</v>
       </c>
       <c r="C172" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D172" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E172" t="s">
         <v>3</v>
       </c>
       <c r="F172">
-        <v>-574857.1</v>
+        <v>-251500</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="H172">
-        <v>36500</v>
+        <v>10000</v>
       </c>
       <c r="I172">
-        <v>-556892.9</v>
+        <v>-251500</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="K172">
-        <v>36500</v>
-      </c>
-      <c r="L172" t="s">
-        <v>3</v>
-      </c>
-      <c r="M172" t="s">
-        <v>3</v>
+        <v>33550</v>
+      </c>
+      <c r="L172">
+        <v>7670.7</v>
+      </c>
+      <c r="M172">
+        <v>100</v>
       </c>
       <c r="N172" t="s">
         <v>3</v>
@@ -7879,87 +8045,93 @@
         <v>64</v>
       </c>
       <c r="C173" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D173" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E173" t="s">
         <v>3</v>
       </c>
       <c r="F173">
-        <v>-574857.1</v>
+        <v>-251500</v>
       </c>
       <c r="G173">
-        <v>-6500</v>
+        <v>15000</v>
       </c>
       <c r="H173">
-        <v>36500</v>
+        <v>10000</v>
       </c>
       <c r="I173">
-        <v>-556892.9</v>
+        <v>-251500</v>
       </c>
       <c r="J173">
-        <v>-6500</v>
+        <v>15000</v>
       </c>
       <c r="K173">
-        <v>36500</v>
-      </c>
-      <c r="L173" t="s">
-        <v>3</v>
-      </c>
-      <c r="M173" t="s">
-        <v>3</v>
+        <v>33550</v>
+      </c>
+      <c r="L173">
+        <v>7670.7</v>
+      </c>
+      <c r="M173">
+        <v>100</v>
       </c>
       <c r="N173" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>64</v>
+      <c r="B174" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C174" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E174" t="s">
-        <v>3</v>
-      </c>
-      <c r="F174">
-        <v>-574857.1</v>
-      </c>
-      <c r="G174">
-        <v>6500</v>
-      </c>
-      <c r="H174">
-        <v>36500</v>
-      </c>
-      <c r="I174">
-        <v>-556892.9</v>
-      </c>
-      <c r="J174">
-        <v>6500</v>
-      </c>
-      <c r="K174">
-        <v>36500</v>
+        <v>50</v>
+      </c>
+      <c r="F174" t="s">
+        <v>66</v>
+      </c>
+      <c r="G174" t="s">
+        <v>67</v>
+      </c>
+      <c r="H174" t="s">
+        <v>68</v>
+      </c>
+      <c r="I174" t="s">
+        <v>69</v>
+      </c>
+      <c r="J174" t="s">
+        <v>70</v>
+      </c>
+      <c r="K174" t="s">
+        <v>71</v>
       </c>
       <c r="L174" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="M174" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="N174" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="O174" t="s">
+        <v>62</v>
+      </c>
+      <c r="P174" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>3</v>
       </c>
@@ -7967,172 +8139,83 @@
         <v>64</v>
       </c>
       <c r="C175" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D175" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E175" t="s">
-        <v>3</v>
-      </c>
-      <c r="F175">
-        <v>-574857.1</v>
-      </c>
-      <c r="G175">
-        <v>-12500</v>
-      </c>
-      <c r="H175">
-        <v>36500</v>
-      </c>
-      <c r="I175">
-        <v>-556892.9</v>
-      </c>
-      <c r="J175">
-        <v>-12500</v>
-      </c>
-      <c r="K175">
-        <v>36500</v>
-      </c>
-      <c r="L175" t="s">
-        <v>3</v>
-      </c>
-      <c r="M175" t="s">
-        <v>3</v>
-      </c>
-      <c r="N175" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C176" t="s">
-        <v>84</v>
-      </c>
-      <c r="D176" t="s">
-        <v>36</v>
-      </c>
-      <c r="E176" t="s">
-        <v>3</v>
-      </c>
-      <c r="F176">
-        <v>-574857.1</v>
-      </c>
-      <c r="G176">
-        <v>12500</v>
-      </c>
-      <c r="H176">
-        <v>36500</v>
-      </c>
-      <c r="I176">
-        <v>-556892.9</v>
-      </c>
-      <c r="J176">
-        <v>12500</v>
-      </c>
-      <c r="K176">
-        <v>36500</v>
-      </c>
-      <c r="L176" t="s">
-        <v>3</v>
-      </c>
-      <c r="M176" t="s">
-        <v>3</v>
-      </c>
-      <c r="N176" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="F175" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>64</v>
+      <c r="B177" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C177" t="s">
-        <v>84</v>
-      </c>
-      <c r="D177" t="s">
-        <v>36</v>
-      </c>
-      <c r="E177" t="s">
-        <v>3</v>
-      </c>
-      <c r="F177">
-        <v>-574857.1</v>
-      </c>
-      <c r="G177">
-        <v>-20500</v>
-      </c>
-      <c r="H177">
-        <v>36500</v>
-      </c>
-      <c r="I177">
-        <v>-556892.9</v>
-      </c>
-      <c r="J177">
-        <v>-20500</v>
-      </c>
-      <c r="K177">
-        <v>36500</v>
-      </c>
-      <c r="L177" t="s">
-        <v>3</v>
-      </c>
-      <c r="M177" t="s">
-        <v>3</v>
-      </c>
-      <c r="N177" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>64</v>
+        <v>79</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C178" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="D178" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E178" t="s">
-        <v>3</v>
-      </c>
-      <c r="F178">
-        <v>-574857.1</v>
-      </c>
-      <c r="G178">
-        <v>20500</v>
-      </c>
-      <c r="H178">
-        <v>36500</v>
-      </c>
-      <c r="I178">
-        <v>-556892.9</v>
-      </c>
-      <c r="J178">
-        <v>20500</v>
-      </c>
-      <c r="K178">
-        <v>36500</v>
+        <v>50</v>
+      </c>
+      <c r="F178" t="s">
+        <v>51</v>
+      </c>
+      <c r="G178" t="s">
+        <v>52</v>
+      </c>
+      <c r="H178" t="s">
+        <v>53</v>
+      </c>
+      <c r="I178" t="s">
+        <v>54</v>
+      </c>
+      <c r="J178" t="s">
+        <v>55</v>
+      </c>
+      <c r="K178" t="s">
+        <v>56</v>
       </c>
       <c r="L178" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="M178" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="N178" t="s">
-        <v>3</v>
+        <v>59</v>
+      </c>
+      <c r="O178" t="s">
+        <v>60</v>
+      </c>
+      <c r="P178" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>62</v>
+      </c>
+      <c r="R178" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
@@ -8143,37 +8226,37 @@
         <v>64</v>
       </c>
       <c r="C179" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D179" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E179" t="s">
         <v>3</v>
       </c>
       <c r="F179">
-        <v>-574857.1</v>
+        <v>0</v>
       </c>
       <c r="G179">
-        <v>-24400</v>
+        <v>-15000</v>
       </c>
       <c r="H179">
-        <v>36500</v>
+        <v>106000</v>
       </c>
       <c r="I179">
-        <v>-556892.9</v>
+        <v>0</v>
       </c>
       <c r="J179">
-        <v>-24400</v>
+        <v>-15000</v>
       </c>
       <c r="K179">
-        <v>36500</v>
-      </c>
-      <c r="L179" t="s">
-        <v>3</v>
-      </c>
-      <c r="M179" t="s">
-        <v>3</v>
+        <v>122000</v>
+      </c>
+      <c r="L179">
+        <v>2147.3</v>
+      </c>
+      <c r="M179">
+        <v>2034.2</v>
       </c>
       <c r="N179" t="s">
         <v>3</v>
@@ -8187,93 +8270,87 @@
         <v>64</v>
       </c>
       <c r="C180" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D180" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E180" t="s">
         <v>3</v>
       </c>
       <c r="F180">
-        <v>-574857.1</v>
+        <v>0</v>
       </c>
       <c r="G180">
-        <v>24400</v>
+        <v>15000</v>
       </c>
       <c r="H180">
-        <v>36500</v>
+        <v>106000</v>
       </c>
       <c r="I180">
-        <v>-556892.9</v>
+        <v>0</v>
       </c>
       <c r="J180">
-        <v>24400</v>
+        <v>15000</v>
       </c>
       <c r="K180">
-        <v>36500</v>
-      </c>
-      <c r="L180" t="s">
-        <v>3</v>
-      </c>
-      <c r="M180" t="s">
-        <v>3</v>
+        <v>122000</v>
+      </c>
+      <c r="L180">
+        <v>2147.3</v>
+      </c>
+      <c r="M180">
+        <v>2034.2</v>
       </c>
       <c r="N180" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B181" s="3" t="s">
-        <v>48</v>
+      <c r="B181" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C181" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="D181" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E181" t="s">
-        <v>50</v>
-      </c>
-      <c r="F181" t="s">
-        <v>66</v>
-      </c>
-      <c r="G181" t="s">
-        <v>67</v>
-      </c>
-      <c r="H181" t="s">
-        <v>68</v>
-      </c>
-      <c r="I181" t="s">
-        <v>69</v>
-      </c>
-      <c r="J181" t="s">
-        <v>70</v>
-      </c>
-      <c r="K181" t="s">
-        <v>71</v>
-      </c>
-      <c r="L181" t="s">
-        <v>72</v>
-      </c>
-      <c r="M181" t="s">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="F181">
+        <v>0</v>
+      </c>
+      <c r="G181">
+        <v>-15000</v>
+      </c>
+      <c r="H181">
+        <v>122000</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>15000</v>
+      </c>
+      <c r="K181">
+        <v>122000</v>
+      </c>
+      <c r="L181">
+        <v>2900</v>
+      </c>
+      <c r="M181">
+        <v>2900</v>
       </c>
       <c r="N181" t="s">
-        <v>61</v>
-      </c>
-      <c r="O181" t="s">
-        <v>62</v>
-      </c>
-      <c r="P181" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>3</v>
       </c>
@@ -8281,30 +8358,131 @@
         <v>64</v>
       </c>
       <c r="C182" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D182" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="E182" t="s">
-        <v>85</v>
-      </c>
-      <c r="F182" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="F182">
+        <v>0</v>
+      </c>
+      <c r="G182">
+        <v>-15000</v>
+      </c>
+      <c r="H182">
+        <v>106000</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>15000</v>
+      </c>
+      <c r="K182">
+        <v>106000</v>
+      </c>
+      <c r="L182">
+        <v>3000</v>
+      </c>
+      <c r="M182">
+        <v>3000</v>
+      </c>
+      <c r="N182" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C183" t="s">
+        <v>80</v>
+      </c>
+      <c r="D183" t="s">
+        <v>31</v>
+      </c>
+      <c r="E183" t="s">
+        <v>3</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+      <c r="G183">
+        <v>-15000</v>
+      </c>
+      <c r="H183">
+        <v>106000</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>-15000</v>
+      </c>
+      <c r="K183">
+        <v>35950</v>
+      </c>
+      <c r="L183">
+        <v>2127.8</v>
+      </c>
+      <c r="M183">
+        <v>100</v>
+      </c>
+      <c r="N183" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B184" s="3" t="s">
-        <v>45</v>
+      <c r="B184" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C184" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="D184" t="s">
+        <v>31</v>
+      </c>
+      <c r="E184" t="s">
+        <v>3</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>15000</v>
+      </c>
+      <c r="H184">
+        <v>106000</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>15000</v>
+      </c>
+      <c r="K184">
+        <v>35950</v>
+      </c>
+      <c r="L184">
+        <v>2127.8</v>
+      </c>
+      <c r="M184">
+        <v>100</v>
+      </c>
+      <c r="N184" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>3</v>
       </c>
@@ -8321,219 +8499,124 @@
         <v>50</v>
       </c>
       <c r="F185" t="s">
+        <v>66</v>
+      </c>
+      <c r="G185" t="s">
+        <v>67</v>
+      </c>
+      <c r="H185" t="s">
+        <v>68</v>
+      </c>
+      <c r="I185" t="s">
+        <v>69</v>
+      </c>
+      <c r="J185" t="s">
+        <v>70</v>
+      </c>
+      <c r="K185" t="s">
+        <v>71</v>
+      </c>
+      <c r="L185" t="s">
+        <v>72</v>
+      </c>
+      <c r="M185" t="s">
+        <v>60</v>
+      </c>
+      <c r="N185" t="s">
+        <v>61</v>
+      </c>
+      <c r="O185" t="s">
+        <v>62</v>
+      </c>
+      <c r="P185" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C186" t="s">
+        <v>80</v>
+      </c>
+      <c r="D186" t="s">
+        <v>73</v>
+      </c>
+      <c r="E186" t="s">
+        <v>81</v>
+      </c>
+      <c r="F186" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C188" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C189" t="s">
+        <v>5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>49</v>
+      </c>
+      <c r="E189" t="s">
+        <v>50</v>
+      </c>
+      <c r="F189" t="s">
         <v>51</v>
       </c>
-      <c r="G185" t="s">
+      <c r="G189" t="s">
         <v>52</v>
       </c>
-      <c r="H185" t="s">
+      <c r="H189" t="s">
         <v>53</v>
       </c>
-      <c r="I185" t="s">
+      <c r="I189" t="s">
         <v>54</v>
       </c>
-      <c r="J185" t="s">
+      <c r="J189" t="s">
         <v>55</v>
       </c>
-      <c r="K185" t="s">
+      <c r="K189" t="s">
         <v>56</v>
       </c>
-      <c r="L185" t="s">
+      <c r="L189" t="s">
         <v>57</v>
       </c>
-      <c r="M185" t="s">
+      <c r="M189" t="s">
         <v>58</v>
       </c>
-      <c r="N185" t="s">
+      <c r="N189" t="s">
         <v>59</v>
       </c>
-      <c r="O185" t="s">
+      <c r="O189" t="s">
         <v>60</v>
       </c>
-      <c r="P185" t="s">
+      <c r="P189" t="s">
         <v>61</v>
       </c>
-      <c r="Q185" t="s">
+      <c r="Q189" t="s">
         <v>62</v>
       </c>
-      <c r="R185" t="s">
+      <c r="R189" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C186" t="s">
-        <v>87</v>
-      </c>
-      <c r="D186" t="s">
-        <v>38</v>
-      </c>
-      <c r="E186" t="s">
-        <v>3</v>
-      </c>
-      <c r="F186">
-        <v>-267500</v>
-      </c>
-      <c r="G186">
-        <v>-33500</v>
-      </c>
-      <c r="H186">
-        <v>-12000</v>
-      </c>
-      <c r="I186">
-        <v>-267500</v>
-      </c>
-      <c r="J186">
-        <v>-33500</v>
-      </c>
-      <c r="K186">
-        <v>5800</v>
-      </c>
-      <c r="L186" t="s">
-        <v>3</v>
-      </c>
-      <c r="M186" t="s">
-        <v>3</v>
-      </c>
-      <c r="N186" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C187" t="s">
-        <v>87</v>
-      </c>
-      <c r="D187" t="s">
-        <v>39</v>
-      </c>
-      <c r="E187" t="s">
-        <v>3</v>
-      </c>
-      <c r="F187">
-        <v>-267500</v>
-      </c>
-      <c r="G187">
-        <v>-33500</v>
-      </c>
-      <c r="H187">
-        <v>5800</v>
-      </c>
-      <c r="I187">
-        <v>-267500</v>
-      </c>
-      <c r="J187">
-        <v>-33500</v>
-      </c>
-      <c r="K187">
-        <v>23600</v>
-      </c>
-      <c r="L187" t="s">
-        <v>3</v>
-      </c>
-      <c r="M187" t="s">
-        <v>3</v>
-      </c>
-      <c r="N187" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C188" t="s">
-        <v>87</v>
-      </c>
-      <c r="D188" t="s">
-        <v>40</v>
-      </c>
-      <c r="E188" t="s">
-        <v>3</v>
-      </c>
-      <c r="F188">
-        <v>-267500</v>
-      </c>
-      <c r="G188">
-        <v>-33500</v>
-      </c>
-      <c r="H188">
-        <v>23600</v>
-      </c>
-      <c r="I188">
-        <v>-267500</v>
-      </c>
-      <c r="J188">
-        <v>-33500</v>
-      </c>
-      <c r="K188">
-        <v>41400</v>
-      </c>
-      <c r="L188" t="s">
-        <v>3</v>
-      </c>
-      <c r="M188" t="s">
-        <v>3</v>
-      </c>
-      <c r="N188" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C189" t="s">
-        <v>87</v>
-      </c>
-      <c r="D189" t="s">
-        <v>41</v>
-      </c>
-      <c r="E189" t="s">
-        <v>3</v>
-      </c>
-      <c r="F189">
-        <v>-267500</v>
-      </c>
-      <c r="G189">
-        <v>-33500</v>
-      </c>
-      <c r="H189">
-        <v>41400</v>
-      </c>
-      <c r="I189">
-        <v>-267500</v>
-      </c>
-      <c r="J189">
-        <v>-33500</v>
-      </c>
-      <c r="K189">
-        <v>59200</v>
-      </c>
-      <c r="L189" t="s">
-        <v>3</v>
-      </c>
-      <c r="M189" t="s">
-        <v>3</v>
-      </c>
-      <c r="N189" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
@@ -8544,31 +8627,31 @@
         <v>64</v>
       </c>
       <c r="C190" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D190" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E190" t="s">
         <v>3</v>
       </c>
       <c r="F190">
-        <v>-267500</v>
+        <v>-574857.1</v>
       </c>
       <c r="G190">
-        <v>-33500</v>
+        <v>-13000</v>
       </c>
       <c r="H190">
-        <v>59200</v>
+        <v>34750</v>
       </c>
       <c r="I190">
-        <v>-267500</v>
+        <v>-574857.1</v>
       </c>
       <c r="J190">
-        <v>-33500</v>
+        <v>13000</v>
       </c>
       <c r="K190">
-        <v>77000</v>
+        <v>34750</v>
       </c>
       <c r="L190" t="s">
         <v>3</v>
@@ -8580,57 +8663,51 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B191" s="3" t="s">
-        <v>48</v>
+      <c r="B191" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C191" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="D191" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E191" t="s">
-        <v>50</v>
-      </c>
-      <c r="F191" t="s">
-        <v>66</v>
-      </c>
-      <c r="G191" t="s">
-        <v>67</v>
-      </c>
-      <c r="H191" t="s">
-        <v>68</v>
-      </c>
-      <c r="I191" t="s">
-        <v>69</v>
-      </c>
-      <c r="J191" t="s">
-        <v>70</v>
-      </c>
-      <c r="K191" t="s">
-        <v>71</v>
+        <v>3</v>
+      </c>
+      <c r="F191">
+        <v>-574857.1</v>
+      </c>
+      <c r="G191">
+        <v>-19200</v>
+      </c>
+      <c r="H191">
+        <v>34750</v>
+      </c>
+      <c r="I191">
+        <v>-574857.1</v>
+      </c>
+      <c r="J191">
+        <v>-24400</v>
+      </c>
+      <c r="K191">
+        <v>34750</v>
       </c>
       <c r="L191" t="s">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="M191" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="N191" t="s">
-        <v>61</v>
-      </c>
-      <c r="O191" t="s">
-        <v>62</v>
-      </c>
-      <c r="P191" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>3</v>
       </c>
@@ -8638,83 +8715,172 @@
         <v>64</v>
       </c>
       <c r="C192" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D192" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="E192" t="s">
-        <v>38</v>
-      </c>
-      <c r="F192" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="F192">
+        <v>-574857.1</v>
+      </c>
+      <c r="G192">
+        <v>19200</v>
+      </c>
+      <c r="H192">
+        <v>34750</v>
+      </c>
+      <c r="I192">
+        <v>-574857.1</v>
+      </c>
+      <c r="J192">
+        <v>24400</v>
+      </c>
+      <c r="K192">
+        <v>34750</v>
+      </c>
+      <c r="L192" t="s">
+        <v>3</v>
+      </c>
+      <c r="M192" t="s">
+        <v>3</v>
+      </c>
+      <c r="N192" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C193" t="s">
+        <v>84</v>
+      </c>
+      <c r="D193" t="s">
+        <v>36</v>
+      </c>
+      <c r="E193" t="s">
+        <v>3</v>
+      </c>
+      <c r="F193">
+        <v>-574857.1</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>36500</v>
+      </c>
+      <c r="I193">
+        <v>-556892.9</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>36500</v>
+      </c>
+      <c r="L193" t="s">
+        <v>3</v>
+      </c>
+      <c r="M193" t="s">
+        <v>3</v>
+      </c>
+      <c r="N193" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B194" s="3" t="s">
-        <v>45</v>
+      <c r="B194" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C194" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="D194" t="s">
+        <v>36</v>
+      </c>
+      <c r="E194" t="s">
+        <v>3</v>
+      </c>
+      <c r="F194">
+        <v>-574857.1</v>
+      </c>
+      <c r="G194">
+        <v>-6500</v>
+      </c>
+      <c r="H194">
+        <v>36500</v>
+      </c>
+      <c r="I194">
+        <v>-556892.9</v>
+      </c>
+      <c r="J194">
+        <v>-6500</v>
+      </c>
+      <c r="K194">
+        <v>36500</v>
+      </c>
+      <c r="L194" t="s">
+        <v>3</v>
+      </c>
+      <c r="M194" t="s">
+        <v>3</v>
+      </c>
+      <c r="N194" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B195" s="3" t="s">
-        <v>48</v>
+      <c r="B195" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C195" t="s">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="D195" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E195" t="s">
-        <v>50</v>
-      </c>
-      <c r="F195" t="s">
-        <v>51</v>
-      </c>
-      <c r="G195" t="s">
-        <v>52</v>
-      </c>
-      <c r="H195" t="s">
-        <v>53</v>
-      </c>
-      <c r="I195" t="s">
-        <v>54</v>
-      </c>
-      <c r="J195" t="s">
-        <v>55</v>
-      </c>
-      <c r="K195" t="s">
-        <v>56</v>
+        <v>3</v>
+      </c>
+      <c r="F195">
+        <v>-574857.1</v>
+      </c>
+      <c r="G195">
+        <v>6500</v>
+      </c>
+      <c r="H195">
+        <v>36500</v>
+      </c>
+      <c r="I195">
+        <v>-556892.9</v>
+      </c>
+      <c r="J195">
+        <v>6500</v>
+      </c>
+      <c r="K195">
+        <v>36500</v>
       </c>
       <c r="L195" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="M195" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="N195" t="s">
-        <v>59</v>
-      </c>
-      <c r="O195" t="s">
-        <v>60</v>
-      </c>
-      <c r="P195" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q195" t="s">
-        <v>62</v>
-      </c>
-      <c r="R195" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -8725,37 +8891,37 @@
         <v>64</v>
       </c>
       <c r="C196" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D196" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E196" t="s">
         <v>3</v>
       </c>
       <c r="F196">
-        <v>-311392.9</v>
+        <v>-574857.1</v>
       </c>
       <c r="G196">
-        <v>-17000</v>
+        <v>-12500</v>
       </c>
       <c r="H196">
-        <v>-12000</v>
+        <v>36500</v>
       </c>
       <c r="I196">
-        <v>-311392.9</v>
+        <v>-556892.9</v>
       </c>
       <c r="J196">
-        <v>-17000</v>
+        <v>-12500</v>
       </c>
       <c r="K196">
-        <v>33550</v>
+        <v>36500</v>
       </c>
       <c r="L196" t="s">
         <v>3</v>
       </c>
-      <c r="M196">
-        <v>100</v>
+      <c r="M196" t="s">
+        <v>3</v>
       </c>
       <c r="N196" t="s">
         <v>3</v>
@@ -8769,37 +8935,37 @@
         <v>64</v>
       </c>
       <c r="C197" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D197" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E197" t="s">
         <v>3</v>
       </c>
       <c r="F197">
-        <v>-299392.9</v>
+        <v>-574857.1</v>
       </c>
       <c r="G197">
-        <v>-17000</v>
+        <v>12500</v>
       </c>
       <c r="H197">
-        <v>-12000</v>
+        <v>36500</v>
       </c>
       <c r="I197">
-        <v>-299392.9</v>
+        <v>-556892.9</v>
       </c>
       <c r="J197">
-        <v>-17000</v>
+        <v>12500</v>
       </c>
       <c r="K197">
-        <v>33550</v>
+        <v>36500</v>
       </c>
       <c r="L197" t="s">
         <v>3</v>
       </c>
-      <c r="M197">
-        <v>100</v>
+      <c r="M197" t="s">
+        <v>3</v>
       </c>
       <c r="N197" t="s">
         <v>3</v>
@@ -8813,37 +8979,37 @@
         <v>64</v>
       </c>
       <c r="C198" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D198" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E198" t="s">
         <v>3</v>
       </c>
       <c r="F198">
-        <v>-299392.9</v>
+        <v>-574857.1</v>
       </c>
       <c r="G198">
-        <v>17000</v>
+        <v>-20500</v>
       </c>
       <c r="H198">
-        <v>-12000</v>
+        <v>36500</v>
       </c>
       <c r="I198">
-        <v>-299392.9</v>
+        <v>-556892.9</v>
       </c>
       <c r="J198">
-        <v>17000</v>
+        <v>-20500</v>
       </c>
       <c r="K198">
-        <v>33550</v>
+        <v>36500</v>
       </c>
       <c r="L198" t="s">
         <v>3</v>
       </c>
-      <c r="M198">
-        <v>100</v>
+      <c r="M198" t="s">
+        <v>3</v>
       </c>
       <c r="N198" t="s">
         <v>3</v>
@@ -8857,37 +9023,37 @@
         <v>64</v>
       </c>
       <c r="C199" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D199" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E199" t="s">
         <v>3</v>
       </c>
       <c r="F199">
-        <v>-311392.9</v>
+        <v>-574857.1</v>
       </c>
       <c r="G199">
-        <v>17000</v>
+        <v>20500</v>
       </c>
       <c r="H199">
-        <v>-12000</v>
+        <v>36500</v>
       </c>
       <c r="I199">
-        <v>-311392.9</v>
+        <v>-556892.9</v>
       </c>
       <c r="J199">
-        <v>17000</v>
+        <v>20500</v>
       </c>
       <c r="K199">
-        <v>33550</v>
+        <v>36500</v>
       </c>
       <c r="L199" t="s">
         <v>3</v>
       </c>
-      <c r="M199">
-        <v>100</v>
+      <c r="M199" t="s">
+        <v>3</v>
       </c>
       <c r="N199" t="s">
         <v>3</v>
@@ -8901,37 +9067,37 @@
         <v>64</v>
       </c>
       <c r="C200" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D200" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E200" t="s">
         <v>3</v>
       </c>
       <c r="F200">
-        <v>-311392.9</v>
+        <v>-574857.1</v>
       </c>
       <c r="G200">
-        <v>-17000</v>
+        <v>-24400</v>
       </c>
       <c r="H200">
-        <v>-12000</v>
+        <v>36500</v>
       </c>
       <c r="I200">
-        <v>-299392.9</v>
+        <v>-556892.9</v>
       </c>
       <c r="J200">
-        <v>-17000</v>
+        <v>-24400</v>
       </c>
       <c r="K200">
-        <v>-12000</v>
-      </c>
-      <c r="L200">
-        <v>1500</v>
-      </c>
-      <c r="M200">
-        <v>1500</v>
+        <v>36500</v>
+      </c>
+      <c r="L200" t="s">
+        <v>3</v>
+      </c>
+      <c r="M200" t="s">
+        <v>3</v>
       </c>
       <c r="N200" t="s">
         <v>3</v>
@@ -8945,87 +9111,93 @@
         <v>64</v>
       </c>
       <c r="C201" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D201" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E201" t="s">
         <v>3</v>
       </c>
       <c r="F201">
-        <v>-299392.9</v>
+        <v>-574857.1</v>
       </c>
       <c r="G201">
-        <v>-17000</v>
+        <v>24400</v>
       </c>
       <c r="H201">
-        <v>-12000</v>
+        <v>36500</v>
       </c>
       <c r="I201">
-        <v>-299392.9</v>
+        <v>-556892.9</v>
       </c>
       <c r="J201">
-        <v>17000</v>
+        <v>24400</v>
       </c>
       <c r="K201">
-        <v>-12000</v>
-      </c>
-      <c r="L201">
-        <v>1500</v>
-      </c>
-      <c r="M201">
-        <v>1500</v>
+        <v>36500</v>
+      </c>
+      <c r="L201" t="s">
+        <v>3</v>
+      </c>
+      <c r="M201" t="s">
+        <v>3</v>
       </c>
       <c r="N201" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>64</v>
+      <c r="B202" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C202" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="D202" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E202" t="s">
-        <v>3</v>
-      </c>
-      <c r="F202">
-        <v>-299392.9</v>
-      </c>
-      <c r="G202">
-        <v>17000</v>
-      </c>
-      <c r="H202">
-        <v>-12000</v>
-      </c>
-      <c r="I202">
-        <v>-311392.9</v>
-      </c>
-      <c r="J202">
-        <v>17000</v>
-      </c>
-      <c r="K202">
-        <v>-12000</v>
-      </c>
-      <c r="L202">
-        <v>1500</v>
-      </c>
-      <c r="M202">
-        <v>1500</v>
+        <v>50</v>
+      </c>
+      <c r="F202" t="s">
+        <v>66</v>
+      </c>
+      <c r="G202" t="s">
+        <v>67</v>
+      </c>
+      <c r="H202" t="s">
+        <v>68</v>
+      </c>
+      <c r="I202" t="s">
+        <v>69</v>
+      </c>
+      <c r="J202" t="s">
+        <v>70</v>
+      </c>
+      <c r="K202" t="s">
+        <v>71</v>
+      </c>
+      <c r="L202" t="s">
+        <v>72</v>
+      </c>
+      <c r="M202" t="s">
+        <v>60</v>
       </c>
       <c r="N202" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="O202" t="s">
+        <v>62</v>
+      </c>
+      <c r="P202" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>3</v>
       </c>
@@ -9033,172 +9205,83 @@
         <v>64</v>
       </c>
       <c r="C203" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D203" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="E203" t="s">
-        <v>3</v>
-      </c>
-      <c r="F203">
-        <v>-311392.9</v>
-      </c>
-      <c r="G203">
-        <v>17000</v>
-      </c>
-      <c r="H203">
-        <v>-12000</v>
-      </c>
-      <c r="I203">
-        <v>-311392.9</v>
-      </c>
-      <c r="J203">
-        <v>-17000</v>
-      </c>
-      <c r="K203">
-        <v>-12000</v>
-      </c>
-      <c r="L203">
-        <v>1500</v>
-      </c>
-      <c r="M203">
-        <v>1500</v>
-      </c>
-      <c r="N203" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C204" t="s">
-        <v>89</v>
-      </c>
-      <c r="D204" t="s">
-        <v>44</v>
-      </c>
-      <c r="E204" t="s">
-        <v>3</v>
-      </c>
-      <c r="F204">
-        <v>-311392.9</v>
-      </c>
-      <c r="G204">
-        <v>-17000</v>
-      </c>
-      <c r="H204">
-        <v>10775</v>
-      </c>
-      <c r="I204">
-        <v>-299392.9</v>
-      </c>
-      <c r="J204">
-        <v>-17000</v>
-      </c>
-      <c r="K204">
-        <v>10775</v>
-      </c>
-      <c r="L204">
-        <v>1500</v>
-      </c>
-      <c r="M204">
-        <v>1500</v>
-      </c>
-      <c r="N204" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="F203" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>64</v>
+      <c r="B205" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C205" t="s">
-        <v>89</v>
-      </c>
-      <c r="D205" t="s">
-        <v>44</v>
-      </c>
-      <c r="E205" t="s">
-        <v>3</v>
-      </c>
-      <c r="F205">
-        <v>-299392.9</v>
-      </c>
-      <c r="G205">
-        <v>-17000</v>
-      </c>
-      <c r="H205">
-        <v>10775</v>
-      </c>
-      <c r="I205">
-        <v>-299392.9</v>
-      </c>
-      <c r="J205">
-        <v>17000</v>
-      </c>
-      <c r="K205">
-        <v>10775</v>
-      </c>
-      <c r="L205">
-        <v>1500</v>
-      </c>
-      <c r="M205">
-        <v>1500</v>
-      </c>
-      <c r="N205" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>64</v>
+      <c r="B206" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="C206" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="D206" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E206" t="s">
-        <v>3</v>
-      </c>
-      <c r="F206">
-        <v>-299392.9</v>
-      </c>
-      <c r="G206">
-        <v>17000</v>
-      </c>
-      <c r="H206">
-        <v>10775</v>
-      </c>
-      <c r="I206">
-        <v>-311392.9</v>
-      </c>
-      <c r="J206">
-        <v>17000</v>
-      </c>
-      <c r="K206">
-        <v>10775</v>
-      </c>
-      <c r="L206">
-        <v>1500</v>
-      </c>
-      <c r="M206">
-        <v>1500</v>
+        <v>50</v>
+      </c>
+      <c r="F206" t="s">
+        <v>51</v>
+      </c>
+      <c r="G206" t="s">
+        <v>52</v>
+      </c>
+      <c r="H206" t="s">
+        <v>53</v>
+      </c>
+      <c r="I206" t="s">
+        <v>54</v>
+      </c>
+      <c r="J206" t="s">
+        <v>55</v>
+      </c>
+      <c r="K206" t="s">
+        <v>56</v>
+      </c>
+      <c r="L206" t="s">
+        <v>57</v>
+      </c>
+      <c r="M206" t="s">
+        <v>58</v>
       </c>
       <c r="N206" t="s">
-        <v>3</v>
+        <v>59</v>
+      </c>
+      <c r="O206" t="s">
+        <v>60</v>
+      </c>
+      <c r="P206" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>62</v>
+      </c>
+      <c r="R206" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
@@ -9209,626 +9292,1029 @@
         <v>64</v>
       </c>
       <c r="C207" t="s">
+        <v>87</v>
+      </c>
+      <c r="D207" t="s">
+        <v>38</v>
+      </c>
+      <c r="E207" t="s">
+        <v>3</v>
+      </c>
+      <c r="F207">
+        <v>-267500</v>
+      </c>
+      <c r="G207">
+        <v>-33500</v>
+      </c>
+      <c r="H207">
+        <v>-12000</v>
+      </c>
+      <c r="I207">
+        <v>-267500</v>
+      </c>
+      <c r="J207">
+        <v>-33500</v>
+      </c>
+      <c r="K207">
+        <v>5800</v>
+      </c>
+      <c r="L207" t="s">
+        <v>3</v>
+      </c>
+      <c r="M207" t="s">
+        <v>3</v>
+      </c>
+      <c r="N207" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C208" t="s">
+        <v>87</v>
+      </c>
+      <c r="D208" t="s">
+        <v>39</v>
+      </c>
+      <c r="E208" t="s">
+        <v>3</v>
+      </c>
+      <c r="F208">
+        <v>-267500</v>
+      </c>
+      <c r="G208">
+        <v>-33500</v>
+      </c>
+      <c r="H208">
+        <v>5800</v>
+      </c>
+      <c r="I208">
+        <v>-267500</v>
+      </c>
+      <c r="J208">
+        <v>-33500</v>
+      </c>
+      <c r="K208">
+        <v>23600</v>
+      </c>
+      <c r="L208" t="s">
+        <v>3</v>
+      </c>
+      <c r="M208" t="s">
+        <v>3</v>
+      </c>
+      <c r="N208" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C209" t="s">
+        <v>87</v>
+      </c>
+      <c r="D209" t="s">
+        <v>40</v>
+      </c>
+      <c r="E209" t="s">
+        <v>3</v>
+      </c>
+      <c r="F209">
+        <v>-267500</v>
+      </c>
+      <c r="G209">
+        <v>-33500</v>
+      </c>
+      <c r="H209">
+        <v>23600</v>
+      </c>
+      <c r="I209">
+        <v>-267500</v>
+      </c>
+      <c r="J209">
+        <v>-33500</v>
+      </c>
+      <c r="K209">
+        <v>41400</v>
+      </c>
+      <c r="L209" t="s">
+        <v>3</v>
+      </c>
+      <c r="M209" t="s">
+        <v>3</v>
+      </c>
+      <c r="N209" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C210" t="s">
+        <v>87</v>
+      </c>
+      <c r="D210" t="s">
+        <v>41</v>
+      </c>
+      <c r="E210" t="s">
+        <v>3</v>
+      </c>
+      <c r="F210">
+        <v>-267500</v>
+      </c>
+      <c r="G210">
+        <v>-33500</v>
+      </c>
+      <c r="H210">
+        <v>41400</v>
+      </c>
+      <c r="I210">
+        <v>-267500</v>
+      </c>
+      <c r="J210">
+        <v>-33500</v>
+      </c>
+      <c r="K210">
+        <v>59200</v>
+      </c>
+      <c r="L210" t="s">
+        <v>3</v>
+      </c>
+      <c r="M210" t="s">
+        <v>3</v>
+      </c>
+      <c r="N210" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C211" t="s">
+        <v>87</v>
+      </c>
+      <c r="D211" t="s">
+        <v>42</v>
+      </c>
+      <c r="E211" t="s">
+        <v>3</v>
+      </c>
+      <c r="F211">
+        <v>-267500</v>
+      </c>
+      <c r="G211">
+        <v>-33500</v>
+      </c>
+      <c r="H211">
+        <v>59200</v>
+      </c>
+      <c r="I211">
+        <v>-267500</v>
+      </c>
+      <c r="J211">
+        <v>-33500</v>
+      </c>
+      <c r="K211">
+        <v>77000</v>
+      </c>
+      <c r="L211" t="s">
+        <v>3</v>
+      </c>
+      <c r="M211" t="s">
+        <v>3</v>
+      </c>
+      <c r="N211" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C212" t="s">
+        <v>5</v>
+      </c>
+      <c r="D212" t="s">
+        <v>49</v>
+      </c>
+      <c r="E212" t="s">
+        <v>50</v>
+      </c>
+      <c r="F212" t="s">
+        <v>66</v>
+      </c>
+      <c r="G212" t="s">
+        <v>67</v>
+      </c>
+      <c r="H212" t="s">
+        <v>68</v>
+      </c>
+      <c r="I212" t="s">
+        <v>69</v>
+      </c>
+      <c r="J212" t="s">
+        <v>70</v>
+      </c>
+      <c r="K212" t="s">
+        <v>71</v>
+      </c>
+      <c r="L212" t="s">
+        <v>72</v>
+      </c>
+      <c r="M212" t="s">
+        <v>60</v>
+      </c>
+      <c r="N212" t="s">
+        <v>61</v>
+      </c>
+      <c r="O212" t="s">
+        <v>62</v>
+      </c>
+      <c r="P212" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C213" t="s">
+        <v>87</v>
+      </c>
+      <c r="D213" t="s">
+        <v>73</v>
+      </c>
+      <c r="E213" t="s">
+        <v>38</v>
+      </c>
+      <c r="F213" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C215" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C216" t="s">
+        <v>5</v>
+      </c>
+      <c r="D216" t="s">
+        <v>49</v>
+      </c>
+      <c r="E216" t="s">
+        <v>50</v>
+      </c>
+      <c r="F216" t="s">
+        <v>51</v>
+      </c>
+      <c r="G216" t="s">
+        <v>52</v>
+      </c>
+      <c r="H216" t="s">
+        <v>53</v>
+      </c>
+      <c r="I216" t="s">
+        <v>54</v>
+      </c>
+      <c r="J216" t="s">
+        <v>55</v>
+      </c>
+      <c r="K216" t="s">
+        <v>56</v>
+      </c>
+      <c r="L216" t="s">
+        <v>57</v>
+      </c>
+      <c r="M216" t="s">
+        <v>58</v>
+      </c>
+      <c r="N216" t="s">
+        <v>59</v>
+      </c>
+      <c r="O216" t="s">
+        <v>60</v>
+      </c>
+      <c r="P216" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>62</v>
+      </c>
+      <c r="R216" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C217" t="s">
         <v>89</v>
       </c>
-      <c r="D207" t="s">
-        <v>44</v>
-      </c>
-      <c r="E207" t="s">
-        <v>3</v>
-      </c>
-      <c r="F207">
+      <c r="D217" t="s">
+        <v>43</v>
+      </c>
+      <c r="E217" t="s">
+        <v>3</v>
+      </c>
+      <c r="F217">
         <v>-311392.9</v>
       </c>
-      <c r="G207">
+      <c r="G217">
+        <v>-17000</v>
+      </c>
+      <c r="H217">
+        <v>-12000</v>
+      </c>
+      <c r="I217">
+        <v>-311392.9</v>
+      </c>
+      <c r="J217">
+        <v>-17000</v>
+      </c>
+      <c r="K217">
+        <v>33550</v>
+      </c>
+      <c r="L217" t="s">
+        <v>3</v>
+      </c>
+      <c r="M217">
+        <v>100</v>
+      </c>
+      <c r="N217" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C218" t="s">
+        <v>89</v>
+      </c>
+      <c r="D218" t="s">
+        <v>43</v>
+      </c>
+      <c r="E218" t="s">
+        <v>3</v>
+      </c>
+      <c r="F218">
+        <v>-299392.9</v>
+      </c>
+      <c r="G218">
+        <v>-17000</v>
+      </c>
+      <c r="H218">
+        <v>-12000</v>
+      </c>
+      <c r="I218">
+        <v>-299392.9</v>
+      </c>
+      <c r="J218">
+        <v>-17000</v>
+      </c>
+      <c r="K218">
+        <v>33550</v>
+      </c>
+      <c r="L218" t="s">
+        <v>3</v>
+      </c>
+      <c r="M218">
+        <v>100</v>
+      </c>
+      <c r="N218" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C219" t="s">
+        <v>89</v>
+      </c>
+      <c r="D219" t="s">
+        <v>43</v>
+      </c>
+      <c r="E219" t="s">
+        <v>3</v>
+      </c>
+      <c r="F219">
+        <v>-299392.9</v>
+      </c>
+      <c r="G219">
         <v>17000</v>
       </c>
-      <c r="H207">
-        <v>10775</v>
-      </c>
-      <c r="I207">
-        <v>-311392.9</v>
-      </c>
-      <c r="J207">
-        <v>-17000</v>
-      </c>
-      <c r="K207">
-        <v>10775</v>
-      </c>
-      <c r="L207">
-        <v>1500</v>
-      </c>
-      <c r="M207">
-        <v>1500</v>
-      </c>
-      <c r="N207" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C208" t="s">
-        <v>5</v>
-      </c>
-      <c r="D208" t="s">
-        <v>49</v>
-      </c>
-      <c r="E208" t="s">
-        <v>50</v>
-      </c>
-      <c r="F208" t="s">
-        <v>66</v>
-      </c>
-      <c r="G208" t="s">
-        <v>67</v>
-      </c>
-      <c r="H208" t="s">
-        <v>68</v>
-      </c>
-      <c r="I208" t="s">
-        <v>69</v>
-      </c>
-      <c r="J208" t="s">
-        <v>70</v>
-      </c>
-      <c r="K208" t="s">
-        <v>71</v>
-      </c>
-      <c r="L208" t="s">
-        <v>72</v>
-      </c>
-      <c r="M208" t="s">
-        <v>60</v>
-      </c>
-      <c r="N208" t="s">
-        <v>61</v>
-      </c>
-      <c r="O208" t="s">
-        <v>62</v>
-      </c>
-      <c r="P208" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C209" t="s">
-        <v>89</v>
-      </c>
-      <c r="D209" t="s">
-        <v>73</v>
-      </c>
-      <c r="E209" t="s">
-        <v>90</v>
-      </c>
-      <c r="F209" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B211" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C211" t="s">
-        <v>93</v>
-      </c>
-      <c r="D211" t="s">
-        <v>94</v>
-      </c>
-      <c r="E211" t="s">
-        <v>95</v>
-      </c>
-      <c r="F211" t="s">
-        <v>96</v>
-      </c>
-      <c r="G211" t="s">
-        <v>97</v>
-      </c>
-      <c r="H211" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C212" t="s">
+      <c r="H219">
+        <v>-12000</v>
+      </c>
+      <c r="I219">
+        <v>-299392.9</v>
+      </c>
+      <c r="J219">
+        <v>17000</v>
+      </c>
+      <c r="K219">
+        <v>33550</v>
+      </c>
+      <c r="L219" t="s">
+        <v>3</v>
+      </c>
+      <c r="M219">
         <v>100</v>
       </c>
-      <c r="D212" t="s">
-        <v>101</v>
-      </c>
-      <c r="E212" t="s">
-        <v>3</v>
-      </c>
-      <c r="F212" t="s">
-        <v>3</v>
-      </c>
-      <c r="G212">
-        <v>2000</v>
-      </c>
-      <c r="H212" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C213" t="s">
-        <v>100</v>
-      </c>
-      <c r="D213" t="s">
-        <v>103</v>
-      </c>
-      <c r="E213" t="s">
-        <v>3</v>
-      </c>
-      <c r="F213" t="s">
-        <v>3</v>
-      </c>
-      <c r="G213">
-        <v>2000</v>
-      </c>
-      <c r="H213" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C214" t="s">
-        <v>65</v>
-      </c>
-      <c r="D214" t="s">
-        <v>101</v>
-      </c>
-      <c r="E214" t="s">
-        <v>3</v>
-      </c>
-      <c r="F214" t="s">
-        <v>3</v>
-      </c>
-      <c r="G214">
-        <v>1000</v>
-      </c>
-      <c r="H214" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C215" t="s">
-        <v>76</v>
-      </c>
-      <c r="D215" t="s">
-        <v>103</v>
-      </c>
-      <c r="E215" t="s">
-        <v>3</v>
-      </c>
-      <c r="F215" t="s">
-        <v>3</v>
-      </c>
-      <c r="G215">
-        <v>1000</v>
-      </c>
-      <c r="H215" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C216" t="s">
-        <v>80</v>
-      </c>
-      <c r="D216" t="s">
-        <v>107</v>
-      </c>
-      <c r="E216" t="s">
-        <v>3</v>
-      </c>
-      <c r="F216" t="s">
-        <v>3</v>
-      </c>
-      <c r="G216">
-        <v>200</v>
-      </c>
-      <c r="H216" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C217" t="s">
-        <v>76</v>
-      </c>
-      <c r="D217" t="s">
-        <v>101</v>
-      </c>
-      <c r="E217" t="s">
-        <v>3</v>
-      </c>
-      <c r="F217" t="s">
-        <v>3</v>
-      </c>
-      <c r="G217">
-        <v>1000</v>
-      </c>
-      <c r="H217" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C218" t="s">
-        <v>84</v>
-      </c>
-      <c r="D218" t="s">
-        <v>107</v>
-      </c>
-      <c r="E218" t="s">
-        <v>3</v>
-      </c>
-      <c r="F218" t="s">
-        <v>3</v>
-      </c>
-      <c r="G218">
-        <v>100</v>
-      </c>
-      <c r="H218" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C219" t="s">
-        <v>87</v>
-      </c>
-      <c r="D219" t="s">
-        <v>107</v>
-      </c>
-      <c r="E219" t="s">
-        <v>3</v>
-      </c>
-      <c r="F219" t="s">
-        <v>3</v>
-      </c>
-      <c r="G219">
-        <v>300</v>
-      </c>
-      <c r="H219" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="N219" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C220" t="s">
         <v>89</v>
       </c>
       <c r="D220" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="E220" t="s">
         <v>3</v>
       </c>
-      <c r="F220" t="s">
-        <v>3</v>
+      <c r="F220">
+        <v>-311392.9</v>
       </c>
       <c r="G220">
-        <v>200</v>
-      </c>
-      <c r="H220" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17000</v>
+      </c>
+      <c r="H220">
+        <v>-12000</v>
+      </c>
+      <c r="I220">
+        <v>-311392.9</v>
+      </c>
+      <c r="J220">
+        <v>17000</v>
+      </c>
+      <c r="K220">
+        <v>33550</v>
+      </c>
+      <c r="L220" t="s">
+        <v>3</v>
+      </c>
+      <c r="M220">
+        <v>100</v>
+      </c>
+      <c r="N220" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C221" t="s">
+        <v>89</v>
+      </c>
+      <c r="D221" t="s">
+        <v>44</v>
+      </c>
+      <c r="E221" t="s">
+        <v>3</v>
+      </c>
+      <c r="F221">
+        <v>-311392.9</v>
+      </c>
+      <c r="G221">
+        <v>-17000</v>
+      </c>
+      <c r="H221">
+        <v>-12000</v>
+      </c>
+      <c r="I221">
+        <v>-299392.9</v>
+      </c>
+      <c r="J221">
+        <v>-17000</v>
+      </c>
+      <c r="K221">
+        <v>-12000</v>
+      </c>
+      <c r="L221">
+        <v>1500</v>
+      </c>
+      <c r="M221">
+        <v>1500</v>
+      </c>
+      <c r="N221" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>114</v>
+        <v>3</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C222" t="s">
+        <v>89</v>
+      </c>
+      <c r="D222" t="s">
+        <v>44</v>
+      </c>
+      <c r="E222" t="s">
+        <v>3</v>
+      </c>
+      <c r="F222">
+        <v>-299392.9</v>
+      </c>
+      <c r="G222">
+        <v>-17000</v>
+      </c>
+      <c r="H222">
+        <v>-12000</v>
+      </c>
+      <c r="I222">
+        <v>-299392.9</v>
+      </c>
+      <c r="J222">
+        <v>17000</v>
+      </c>
+      <c r="K222">
+        <v>-12000</v>
+      </c>
+      <c r="L222">
+        <v>1500</v>
+      </c>
+      <c r="M222">
+        <v>1500</v>
+      </c>
+      <c r="N222" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C223" t="s">
+        <v>89</v>
+      </c>
+      <c r="D223" t="s">
+        <v>44</v>
+      </c>
+      <c r="E223" t="s">
+        <v>3</v>
+      </c>
+      <c r="F223">
+        <v>-299392.9</v>
+      </c>
+      <c r="G223">
+        <v>17000</v>
+      </c>
+      <c r="H223">
+        <v>-12000</v>
+      </c>
+      <c r="I223">
+        <v>-311392.9</v>
+      </c>
+      <c r="J223">
+        <v>17000</v>
+      </c>
+      <c r="K223">
+        <v>-12000</v>
+      </c>
+      <c r="L223">
+        <v>1500</v>
+      </c>
+      <c r="M223">
+        <v>1500</v>
+      </c>
+      <c r="N223" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C224" t="s">
+        <v>89</v>
+      </c>
+      <c r="D224" t="s">
+        <v>44</v>
+      </c>
+      <c r="E224" t="s">
+        <v>3</v>
+      </c>
+      <c r="F224">
+        <v>-311392.9</v>
+      </c>
+      <c r="G224">
+        <v>17000</v>
+      </c>
+      <c r="H224">
+        <v>-12000</v>
+      </c>
+      <c r="I224">
+        <v>-311392.9</v>
+      </c>
+      <c r="J224">
+        <v>-17000</v>
+      </c>
+      <c r="K224">
+        <v>-12000</v>
+      </c>
+      <c r="L224">
+        <v>1500</v>
+      </c>
+      <c r="M224">
+        <v>1500</v>
+      </c>
+      <c r="N224" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C225" t="s">
+        <v>89</v>
+      </c>
+      <c r="D225" t="s">
+        <v>44</v>
+      </c>
+      <c r="E225" t="s">
+        <v>3</v>
+      </c>
+      <c r="F225">
+        <v>-311392.9</v>
+      </c>
+      <c r="G225">
+        <v>-17000</v>
+      </c>
+      <c r="H225">
+        <v>10775</v>
+      </c>
+      <c r="I225">
+        <v>-299392.9</v>
+      </c>
+      <c r="J225">
+        <v>-17000</v>
+      </c>
+      <c r="K225">
+        <v>10775</v>
+      </c>
+      <c r="L225">
+        <v>1500</v>
+      </c>
+      <c r="M225">
+        <v>1500</v>
+      </c>
+      <c r="N225" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C226" t="s">
+        <v>89</v>
+      </c>
+      <c r="D226" t="s">
+        <v>44</v>
+      </c>
+      <c r="E226" t="s">
+        <v>3</v>
+      </c>
+      <c r="F226">
+        <v>-299392.9</v>
+      </c>
+      <c r="G226">
+        <v>-17000</v>
+      </c>
+      <c r="H226">
+        <v>10775</v>
+      </c>
+      <c r="I226">
+        <v>-299392.9</v>
+      </c>
+      <c r="J226">
+        <v>17000</v>
+      </c>
+      <c r="K226">
+        <v>10775</v>
+      </c>
+      <c r="L226">
+        <v>1500</v>
+      </c>
+      <c r="M226">
+        <v>1500</v>
+      </c>
+      <c r="N226" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C227" t="s">
+        <v>89</v>
+      </c>
+      <c r="D227" t="s">
+        <v>44</v>
+      </c>
+      <c r="E227" t="s">
+        <v>3</v>
+      </c>
+      <c r="F227">
+        <v>-299392.9</v>
+      </c>
+      <c r="G227">
+        <v>17000</v>
+      </c>
+      <c r="H227">
+        <v>10775</v>
+      </c>
+      <c r="I227">
+        <v>-311392.9</v>
+      </c>
+      <c r="J227">
+        <v>17000</v>
+      </c>
+      <c r="K227">
+        <v>10775</v>
+      </c>
+      <c r="L227">
+        <v>1500</v>
+      </c>
+      <c r="M227">
+        <v>1500</v>
+      </c>
+      <c r="N227" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C228" t="s">
+        <v>89</v>
+      </c>
+      <c r="D228" t="s">
+        <v>44</v>
+      </c>
+      <c r="E228" t="s">
+        <v>3</v>
+      </c>
+      <c r="F228">
+        <v>-311392.9</v>
+      </c>
+      <c r="G228">
+        <v>17000</v>
+      </c>
+      <c r="H228">
+        <v>10775</v>
+      </c>
+      <c r="I228">
+        <v>-311392.9</v>
+      </c>
+      <c r="J228">
+        <v>-17000</v>
+      </c>
+      <c r="K228">
+        <v>10775</v>
+      </c>
+      <c r="L228">
+        <v>1500</v>
+      </c>
+      <c r="M228">
+        <v>1500</v>
+      </c>
+      <c r="N228" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C229" t="s">
         <v>5</v>
       </c>
-      <c r="D222" t="s">
-        <v>115</v>
-      </c>
-      <c r="E222" t="s">
-        <v>116</v>
-      </c>
-      <c r="F222" t="s">
-        <v>117</v>
-      </c>
-      <c r="G222" t="s">
-        <v>118</v>
-      </c>
-      <c r="H222" t="s">
-        <v>119</v>
-      </c>
-      <c r="I222" t="s">
+      <c r="D229" t="s">
+        <v>49</v>
+      </c>
+      <c r="E229" t="s">
+        <v>50</v>
+      </c>
+      <c r="F229" t="s">
+        <v>66</v>
+      </c>
+      <c r="G229" t="s">
+        <v>67</v>
+      </c>
+      <c r="H229" t="s">
+        <v>68</v>
+      </c>
+      <c r="I229" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C223" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C224" t="s">
-        <v>122</v>
-      </c>
-      <c r="D224" t="s">
-        <v>65</v>
-      </c>
-      <c r="E224" t="s">
-        <v>123</v>
-      </c>
-      <c r="F224">
-        <v>0</v>
-      </c>
-      <c r="G224">
-        <v>-15000</v>
-      </c>
-      <c r="H224">
-        <v>122000</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C225" t="s">
-        <v>122</v>
-      </c>
-      <c r="D225" t="s">
-        <v>122</v>
-      </c>
-      <c r="E225" t="s">
-        <v>124</v>
-      </c>
-      <c r="F225">
-        <v>0</v>
-      </c>
-      <c r="G225">
-        <v>0</v>
-      </c>
-      <c r="H225">
-        <v>0</v>
-      </c>
-      <c r="I225" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C226" t="s">
-        <v>122</v>
-      </c>
-      <c r="D226" t="s">
-        <v>122</v>
-      </c>
-      <c r="E226" t="s">
-        <v>124</v>
-      </c>
-      <c r="F226">
-        <v>0</v>
-      </c>
-      <c r="G226">
-        <v>0</v>
-      </c>
-      <c r="H226">
-        <v>0</v>
-      </c>
-      <c r="I226" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C228" t="s">
-        <v>5</v>
-      </c>
-      <c r="D228" t="s">
-        <v>115</v>
-      </c>
-      <c r="E228" t="s">
-        <v>116</v>
-      </c>
-      <c r="F228" t="s">
-        <v>117</v>
-      </c>
-      <c r="G228" t="s">
-        <v>118</v>
-      </c>
-      <c r="H228" t="s">
-        <v>119</v>
-      </c>
-      <c r="I228" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C229" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J229" t="s">
+        <v>70</v>
+      </c>
+      <c r="K229" t="s">
+        <v>71</v>
+      </c>
+      <c r="L229" t="s">
+        <v>72</v>
+      </c>
+      <c r="M229" t="s">
+        <v>60</v>
+      </c>
+      <c r="N229" t="s">
+        <v>61</v>
+      </c>
+      <c r="O229" t="s">
+        <v>62</v>
+      </c>
+      <c r="P229" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="C230" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="D230" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E230" t="s">
-        <v>123</v>
-      </c>
-      <c r="F230">
-        <v>-17964.3</v>
-      </c>
-      <c r="G230">
-        <v>-15000</v>
-      </c>
-      <c r="H230">
-        <v>121262</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C231" t="s">
-        <v>128</v>
-      </c>
-      <c r="D231" t="s">
-        <v>128</v>
-      </c>
-      <c r="E231" t="s">
-        <v>124</v>
-      </c>
-      <c r="F231">
-        <v>0</v>
-      </c>
-      <c r="G231">
-        <v>0</v>
-      </c>
-      <c r="H231">
-        <v>0</v>
-      </c>
-      <c r="I231" t="s">
-        <v>125</v>
+        <v>90</v>
+      </c>
+      <c r="F230" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C232" t="s">
+        <v>93</v>
+      </c>
+      <c r="D232" t="s">
+        <v>94</v>
+      </c>
+      <c r="E232" t="s">
+        <v>95</v>
+      </c>
+      <c r="F232" t="s">
+        <v>96</v>
+      </c>
+      <c r="G232" t="s">
+        <v>97</v>
+      </c>
+      <c r="H232" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B233" s="3" t="s">
-        <v>114</v>
+      <c r="B233" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="C233" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D233" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E233" t="s">
-        <v>116</v>
+        <v>3</v>
       </c>
       <c r="F233" t="s">
-        <v>117</v>
-      </c>
-      <c r="G233" t="s">
-        <v>118</v>
+        <v>3</v>
+      </c>
+      <c r="G233">
+        <v>2000</v>
       </c>
       <c r="H233" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B234" s="3" t="s">
-        <v>45</v>
+      <c r="B234" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="C234" t="s">
-        <v>129</v>
+        <v>100</v>
+      </c>
+      <c r="D234" t="s">
+        <v>103</v>
+      </c>
+      <c r="E234" t="s">
+        <v>3</v>
+      </c>
+      <c r="F234" t="s">
+        <v>3</v>
+      </c>
+      <c r="G234">
+        <v>2000</v>
+      </c>
+      <c r="H234" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
@@ -9836,65 +10322,103 @@
         <v>3</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="C235" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="D235" t="s">
+        <v>101</v>
+      </c>
+      <c r="E235" t="s">
+        <v>3</v>
+      </c>
+      <c r="F235" t="s">
+        <v>3</v>
+      </c>
+      <c r="G235">
+        <v>1000</v>
+      </c>
+      <c r="H235" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C236" t="s">
+        <v>76</v>
+      </c>
+      <c r="D236" t="s">
+        <v>103</v>
+      </c>
+      <c r="E236" t="s">
+        <v>3</v>
+      </c>
+      <c r="F236" t="s">
+        <v>3</v>
+      </c>
+      <c r="G236">
+        <v>1000</v>
+      </c>
+      <c r="H236" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C237" t="s">
         <v>80</v>
       </c>
-      <c r="E235" t="s">
-        <v>123</v>
-      </c>
-      <c r="F235">
-        <v>0</v>
-      </c>
-      <c r="G235">
-        <v>-15000</v>
-      </c>
-      <c r="H235">
-        <v>106000</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C237" t="s">
-        <v>5</v>
-      </c>
       <c r="D237" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E237" t="s">
-        <v>116</v>
+        <v>3</v>
       </c>
       <c r="F237" t="s">
-        <v>117</v>
-      </c>
-      <c r="G237" t="s">
-        <v>118</v>
+        <v>3</v>
+      </c>
+      <c r="G237">
+        <v>200</v>
       </c>
       <c r="H237" t="s">
-        <v>119</v>
-      </c>
-      <c r="I237" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B238" s="3" t="s">
-        <v>45</v>
+      <c r="B238" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="C238" t="s">
-        <v>131</v>
+        <v>76</v>
+      </c>
+      <c r="D238" t="s">
+        <v>101</v>
+      </c>
+      <c r="E238" t="s">
+        <v>3</v>
+      </c>
+      <c r="F238" t="s">
+        <v>3</v>
+      </c>
+      <c r="G238">
+        <v>1000</v>
+      </c>
+      <c r="H238" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
@@ -9902,123 +10426,120 @@
         <v>3</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="C239" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="D239" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E239" t="s">
-        <v>123</v>
-      </c>
-      <c r="F239">
-        <v>-574857.1</v>
+        <v>3</v>
+      </c>
+      <c r="F239" t="s">
+        <v>3</v>
       </c>
       <c r="G239">
-        <v>-13000</v>
-      </c>
-      <c r="H239">
-        <v>34750</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="H239" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="C240" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="D240" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E240" t="s">
-        <v>133</v>
-      </c>
-      <c r="F240">
-        <v>17964.3</v>
+        <v>3</v>
+      </c>
+      <c r="F240" t="s">
+        <v>3</v>
       </c>
       <c r="G240">
-        <v>0</v>
-      </c>
-      <c r="H240">
-        <v>0</v>
-      </c>
-      <c r="I240">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A242" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B242" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="H240" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C241" t="s">
+        <v>89</v>
+      </c>
+      <c r="D241" t="s">
+        <v>107</v>
+      </c>
+      <c r="E241" t="s">
+        <v>3</v>
+      </c>
+      <c r="F241" t="s">
+        <v>3</v>
+      </c>
+      <c r="G241">
+        <v>200</v>
+      </c>
+      <c r="H241" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B243" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C242" t="s">
+      <c r="C243" t="s">
         <v>5</v>
       </c>
-      <c r="D242" t="s">
+      <c r="D243" t="s">
         <v>115</v>
       </c>
-      <c r="E242" t="s">
+      <c r="E243" t="s">
         <v>116</v>
       </c>
-      <c r="F242" t="s">
+      <c r="F243" t="s">
         <v>117</v>
       </c>
-      <c r="G242" t="s">
+      <c r="G243" t="s">
         <v>118</v>
       </c>
-      <c r="H242" t="s">
+      <c r="H243" t="s">
         <v>119</v>
       </c>
-      <c r="I242" t="s">
+      <c r="I243" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B243" s="3" t="s">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B244" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C243" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="C244" t="s">
-        <v>135</v>
-      </c>
-      <c r="D244" t="s">
-        <v>87</v>
-      </c>
-      <c r="E244" t="s">
-        <v>123</v>
-      </c>
-      <c r="F244">
-        <v>-267500</v>
-      </c>
-      <c r="G244">
-        <v>-33500</v>
-      </c>
-      <c r="H244">
-        <v>-12000</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>3</v>
       </c>
@@ -10026,25 +10547,22 @@
         <v>121</v>
       </c>
       <c r="C245" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D245" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="E245" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F245">
         <v>0</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="H245">
-        <v>0</v>
-      </c>
-      <c r="I245" t="s">
-        <v>125</v>
+        <v>122000</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
@@ -10055,10 +10573,10 @@
         <v>121</v>
       </c>
       <c r="C246" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D246" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E246" t="s">
         <v>124</v>
@@ -10073,76 +10591,79 @@
         <v>0</v>
       </c>
       <c r="I246" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C247" t="s">
+        <v>122</v>
+      </c>
+      <c r="D247" t="s">
+        <v>122</v>
+      </c>
+      <c r="E247" t="s">
+        <v>124</v>
+      </c>
+      <c r="F247">
+        <v>0</v>
+      </c>
+      <c r="G247">
+        <v>0</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A248" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B248" s="3" t="s">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B249" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C249" t="s">
         <v>5</v>
       </c>
-      <c r="D248" t="s">
+      <c r="D249" t="s">
         <v>115</v>
       </c>
-      <c r="E248" t="s">
+      <c r="E249" t="s">
         <v>116</v>
       </c>
-      <c r="F248" t="s">
+      <c r="F249" t="s">
         <v>117</v>
       </c>
-      <c r="G248" t="s">
+      <c r="G249" t="s">
         <v>118</v>
       </c>
-      <c r="H248" t="s">
+      <c r="H249" t="s">
         <v>119</v>
       </c>
-      <c r="I248" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B249" s="3" t="s">
+      <c r="I249" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B250" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C249" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A250" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="C250" t="s">
-        <v>137</v>
-      </c>
-      <c r="D250" t="s">
-        <v>89</v>
-      </c>
-      <c r="E250" t="s">
-        <v>123</v>
-      </c>
-      <c r="F250">
-        <v>-311392.9</v>
-      </c>
-      <c r="G250">
-        <v>-17000</v>
-      </c>
-      <c r="H250">
-        <v>-12000</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>3</v>
       </c>
@@ -10150,25 +10671,22 @@
         <v>121</v>
       </c>
       <c r="C251" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D251" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="E251" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F251">
-        <v>-53892.9</v>
+        <v>-17964.3</v>
       </c>
       <c r="G251">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="H251">
-        <v>0</v>
-      </c>
-      <c r="I251">
-        <v>5</v>
+        <v>121262</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
@@ -10179,10 +10697,10 @@
         <v>121</v>
       </c>
       <c r="C252" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D252" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E252" t="s">
         <v>124</v>
@@ -10200,11 +10718,417 @@
         <v>125</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B253" s="2" t="s">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C254" t="s">
+        <v>5</v>
+      </c>
+      <c r="D254" t="s">
+        <v>115</v>
+      </c>
+      <c r="E254" t="s">
+        <v>116</v>
+      </c>
+      <c r="F254" t="s">
+        <v>117</v>
+      </c>
+      <c r="G254" t="s">
+        <v>118</v>
+      </c>
+      <c r="H254" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C255" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C256" t="s">
+        <v>130</v>
+      </c>
+      <c r="D256" t="s">
+        <v>80</v>
+      </c>
+      <c r="E256" t="s">
+        <v>123</v>
+      </c>
+      <c r="F256">
+        <v>0</v>
+      </c>
+      <c r="G256">
+        <v>-15000</v>
+      </c>
+      <c r="H256">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C258" t="s">
+        <v>5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>115</v>
+      </c>
+      <c r="E258" t="s">
+        <v>116</v>
+      </c>
+      <c r="F258" t="s">
+        <v>117</v>
+      </c>
+      <c r="G258" t="s">
+        <v>118</v>
+      </c>
+      <c r="H258" t="s">
+        <v>119</v>
+      </c>
+      <c r="I258" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C259" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C260" t="s">
+        <v>132</v>
+      </c>
+      <c r="D260" t="s">
+        <v>84</v>
+      </c>
+      <c r="E260" t="s">
+        <v>123</v>
+      </c>
+      <c r="F260">
+        <v>-574857.1</v>
+      </c>
+      <c r="G260">
+        <v>-13000</v>
+      </c>
+      <c r="H260">
+        <v>34750</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C261" t="s">
+        <v>132</v>
+      </c>
+      <c r="D261" t="s">
+        <v>132</v>
+      </c>
+      <c r="E261" t="s">
+        <v>133</v>
+      </c>
+      <c r="F261">
+        <v>17964.3</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C263" t="s">
+        <v>5</v>
+      </c>
+      <c r="D263" t="s">
+        <v>115</v>
+      </c>
+      <c r="E263" t="s">
+        <v>116</v>
+      </c>
+      <c r="F263" t="s">
+        <v>117</v>
+      </c>
+      <c r="G263" t="s">
+        <v>118</v>
+      </c>
+      <c r="H263" t="s">
+        <v>119</v>
+      </c>
+      <c r="I263" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C264" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C265" t="s">
+        <v>135</v>
+      </c>
+      <c r="D265" t="s">
+        <v>87</v>
+      </c>
+      <c r="E265" t="s">
+        <v>123</v>
+      </c>
+      <c r="F265">
+        <v>-267500</v>
+      </c>
+      <c r="G265">
+        <v>-33500</v>
+      </c>
+      <c r="H265">
+        <v>-12000</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C266" t="s">
+        <v>135</v>
+      </c>
+      <c r="D266" t="s">
+        <v>135</v>
+      </c>
+      <c r="E266" t="s">
+        <v>124</v>
+      </c>
+      <c r="F266">
+        <v>0</v>
+      </c>
+      <c r="G266">
+        <v>0</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+      <c r="I266" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C267" t="s">
+        <v>135</v>
+      </c>
+      <c r="D267" t="s">
+        <v>135</v>
+      </c>
+      <c r="E267" t="s">
+        <v>124</v>
+      </c>
+      <c r="F267">
+        <v>0</v>
+      </c>
+      <c r="G267">
+        <v>0</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C269" t="s">
+        <v>5</v>
+      </c>
+      <c r="D269" t="s">
+        <v>115</v>
+      </c>
+      <c r="E269" t="s">
+        <v>116</v>
+      </c>
+      <c r="F269" t="s">
+        <v>117</v>
+      </c>
+      <c r="G269" t="s">
+        <v>118</v>
+      </c>
+      <c r="H269" t="s">
+        <v>119</v>
+      </c>
+      <c r="I269" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C270" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C271" t="s">
+        <v>137</v>
+      </c>
+      <c r="D271" t="s">
+        <v>89</v>
+      </c>
+      <c r="E271" t="s">
+        <v>123</v>
+      </c>
+      <c r="F271">
+        <v>-311392.9</v>
+      </c>
+      <c r="G271">
+        <v>-17000</v>
+      </c>
+      <c r="H271">
+        <v>-12000</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C272" t="s">
+        <v>137</v>
+      </c>
+      <c r="D272" t="s">
+        <v>137</v>
+      </c>
+      <c r="E272" t="s">
+        <v>133</v>
+      </c>
+      <c r="F272">
+        <v>-53892.9</v>
+      </c>
+      <c r="G272">
+        <v>0</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+      <c r="I272">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C273" t="s">
+        <v>137</v>
+      </c>
+      <c r="D273" t="s">
+        <v>137</v>
+      </c>
+      <c r="E273" t="s">
+        <v>124</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
+      <c r="G273">
+        <v>0</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+      <c r="I273" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B274" s="2" t="s">
         <v>138</v>
       </c>
     </row>
